--- a/Excel Files IPEDS/Trimmed/c2015_trimmed_file.xlsx
+++ b/Excel Files IPEDS/Trimmed/c2015_trimmed_file.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L422"/>
+  <dimension ref="A1:M422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,35 +456,40 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>CTOTALW</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>CUNKNT</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>CBKAAT</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>CASIAT</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>CNHPIT</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>CHISPT</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>CWHITT</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
@@ -510,10 +515,10 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -525,6 +530,9 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -560,9 +568,12 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -598,9 +609,12 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -621,7 +635,7 @@
         <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -636,9 +650,12 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
         <v>4</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -659,24 +676,27 @@
         <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -697,7 +717,7 @@
         <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -712,9 +732,12 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -735,7 +758,7 @@
         <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -750,9 +773,12 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -788,9 +814,12 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>9</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -826,9 +855,12 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -867,6 +899,9 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -905,6 +940,9 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -925,7 +963,7 @@
         <v>3</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -937,12 +975,15 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
         <v>4</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -963,24 +1004,27 @@
         <v>14</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>8</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1004,21 +1048,24 @@
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>3</v>
+      </c>
+      <c r="M15" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1054,9 +1101,12 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>6</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1077,7 +1127,7 @@
         <v>4</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1092,9 +1142,12 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>5</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1115,7 +1168,7 @@
         <v>7</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1130,9 +1183,12 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>6</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1168,9 +1224,12 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1191,24 +1250,27 @@
         <v>11</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
         <v>6</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1229,7 +1291,7 @@
         <v>13</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1241,12 +1303,15 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
+        <v>7</v>
+      </c>
+      <c r="M21" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1285,6 +1350,9 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1323,6 +1391,9 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1358,9 +1429,12 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>2</v>
+      </c>
+      <c r="M24" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1381,10 +1455,10 @@
         <v>6</v>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1393,12 +1467,15 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
+        <v>2</v>
+      </c>
+      <c r="M25" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1419,24 +1496,27 @@
         <v>8</v>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M26" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1469,12 +1549,15 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1495,16 +1578,16 @@
         <v>6</v>
       </c>
       <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="n">
         <v>5</v>
       </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1513,6 +1596,9 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1533,24 +1619,27 @@
         <v>26</v>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
+        <v>2</v>
+      </c>
+      <c r="L29" t="n">
         <v>19</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1571,11 +1660,11 @@
         <v>27</v>
       </c>
       <c r="F30" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" t="n">
         <v>4</v>
       </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
@@ -1583,12 +1672,15 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="n">
         <v>11</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1612,7 +1704,7 @@
         <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1624,9 +1716,12 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
         <v>6</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1650,7 +1745,7 @@
         <v>2</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1662,9 +1757,12 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
         <v>16</v>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1691,18 +1789,21 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L33" t="n">
+        <v>7</v>
+      </c>
+      <c r="M33" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1723,24 +1824,27 @@
         <v>10</v>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
+        <v>3</v>
+      </c>
+      <c r="M34" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1761,24 +1865,27 @@
         <v>26</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
         <v>5</v>
       </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
       <c r="J35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
+        <v>2</v>
+      </c>
+      <c r="L35" t="n">
         <v>21</v>
       </c>
-      <c r="L35" t="n">
+      <c r="M35" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1799,24 +1906,27 @@
         <v>14</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
         <v>9</v>
       </c>
-      <c r="L36" t="n">
+      <c r="M36" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1837,10 +1947,10 @@
         <v>15</v>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1849,12 +1959,15 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
+        <v>3</v>
+      </c>
+      <c r="L37" t="n">
         <v>4</v>
       </c>
-      <c r="L37" t="n">
+      <c r="M37" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1875,24 +1988,27 @@
         <v>12</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
+        <v>3</v>
+      </c>
+      <c r="M38" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1916,7 +2032,7 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -1925,12 +2041,15 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
+        <v>2</v>
+      </c>
+      <c r="L39" t="n">
         <v>8</v>
       </c>
-      <c r="L39" t="n">
+      <c r="M39" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1951,10 +2070,10 @@
         <v>18</v>
       </c>
       <c r="F40" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1966,9 +2085,12 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
         <v>14</v>
       </c>
-      <c r="L40" t="n">
+      <c r="M40" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1989,24 +2111,27 @@
         <v>24</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
         <v>5</v>
       </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" t="n">
         <v>16</v>
       </c>
-      <c r="L41" t="n">
+      <c r="M41" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2027,11 +2152,11 @@
         <v>13</v>
       </c>
       <c r="F42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G42" t="n">
         <v>11</v>
       </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
@@ -2042,9 +2167,12 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
         <v>6</v>
       </c>
-      <c r="L42" t="n">
+      <c r="M42" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2065,7 +2193,7 @@
         <v>8</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -2080,9 +2208,12 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
         <v>9</v>
       </c>
-      <c r="L43" t="n">
+      <c r="M43" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2103,24 +2234,27 @@
         <v>5</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
+        <v>2</v>
+      </c>
+      <c r="L44" t="n">
         <v>4</v>
       </c>
-      <c r="L44" t="n">
+      <c r="M44" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2156,9 +2290,12 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
+        <v>2</v>
+      </c>
+      <c r="M45" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2197,6 +2334,9 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2217,10 +2357,10 @@
         <v>4</v>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -2232,9 +2372,12 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
         <v>4</v>
       </c>
-      <c r="L47" t="n">
+      <c r="M47" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2255,24 +2398,27 @@
         <v>6</v>
       </c>
       <c r="F48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
+        <v>3</v>
+      </c>
+      <c r="M48" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2293,10 +2439,10 @@
         <v>8</v>
       </c>
       <c r="F49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -2305,12 +2451,15 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L49" t="n">
+        <v>3</v>
+      </c>
+      <c r="M49" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2331,7 +2480,7 @@
         <v>4</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -2349,6 +2498,9 @@
         <v>0</v>
       </c>
       <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2369,7 +2521,7 @@
         <v>7</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -2384,9 +2536,12 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L51" t="n">
+        <v>3</v>
+      </c>
+      <c r="M51" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2410,7 +2565,7 @@
         <v>3</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -2422,9 +2577,12 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
         <v>15</v>
       </c>
-      <c r="L52" t="n">
+      <c r="M52" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2445,24 +2603,27 @@
         <v>23</v>
       </c>
       <c r="F53" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" t="n">
         <v>13</v>
       </c>
-      <c r="L53" t="n">
+      <c r="M53" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2498,9 +2659,12 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
         <v>6</v>
       </c>
-      <c r="L54" t="n">
+      <c r="M54" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2536,9 +2700,12 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
+        <v>7</v>
+      </c>
+      <c r="M55" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2559,24 +2726,27 @@
         <v>4</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
+        <v>3</v>
+      </c>
+      <c r="M56" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2597,7 +2767,7 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -2612,9 +2782,12 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M57" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2635,7 +2808,7 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -2650,9 +2823,12 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
+        <v>1</v>
+      </c>
+      <c r="M58" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2673,10 +2849,10 @@
         <v>11</v>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2688,9 +2864,12 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L59" t="n">
+        <v>7</v>
+      </c>
+      <c r="M59" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2711,24 +2890,27 @@
         <v>5</v>
       </c>
       <c r="F60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
         <v>4</v>
       </c>
-      <c r="L60" t="n">
+      <c r="M60" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2767,6 +2949,9 @@
         <v>0</v>
       </c>
       <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2805,6 +2990,9 @@
         <v>0</v>
       </c>
       <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2825,24 +3013,27 @@
         <v>19</v>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G63" t="n">
         <v>1</v>
       </c>
       <c r="H63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L63" t="n">
         <v>9</v>
       </c>
-      <c r="L63" t="n">
+      <c r="M63" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2863,7 +3054,7 @@
         <v>8</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2875,12 +3066,15 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
+        <v>1</v>
+      </c>
+      <c r="L64" t="n">
         <v>4</v>
       </c>
-      <c r="L64" t="n">
+      <c r="M64" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2916,9 +3110,12 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
+        <v>1</v>
+      </c>
+      <c r="M65" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2954,9 +3151,12 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66" t="n">
+        <v>1</v>
+      </c>
+      <c r="M66" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2977,24 +3177,27 @@
         <v>5</v>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
+        <v>1</v>
+      </c>
+      <c r="M67" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3015,7 +3218,7 @@
         <v>2</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -3027,12 +3230,15 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L68" t="n">
+        <v>3</v>
+      </c>
+      <c r="M68" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3056,7 +3262,7 @@
         <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -3068,9 +3274,12 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
+        <v>1</v>
+      </c>
+      <c r="M69" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3109,6 +3318,9 @@
         <v>0</v>
       </c>
       <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3138,15 +3350,18 @@
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
       </c>
       <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3167,24 +3382,27 @@
         <v>4</v>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
         <v>1</v>
       </c>
       <c r="L72" t="n">
+        <v>1</v>
+      </c>
+      <c r="M72" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3205,16 +3423,16 @@
         <v>4</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -3223,6 +3441,9 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3246,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I74" t="n">
         <v>0</v>
@@ -3261,6 +3482,9 @@
         <v>0</v>
       </c>
       <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3284,10 +3508,10 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
@@ -3299,6 +3523,9 @@
         <v>0</v>
       </c>
       <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3319,7 +3546,7 @@
         <v>2</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -3337,6 +3564,9 @@
         <v>0</v>
       </c>
       <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3357,7 +3587,7 @@
         <v>18</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -3369,12 +3599,15 @@
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
+        <v>1</v>
+      </c>
+      <c r="L77" t="n">
         <v>6</v>
       </c>
-      <c r="L77" t="n">
+      <c r="M77" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3413,6 +3646,9 @@
         <v>0</v>
       </c>
       <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3433,13 +3669,13 @@
         <v>1</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G79" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
@@ -3451,6 +3687,9 @@
         <v>0</v>
       </c>
       <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3474,7 +3713,7 @@
         <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -3489,6 +3728,9 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3524,9 +3766,12 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M81" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3547,7 +3792,7 @@
         <v>2</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -3562,9 +3807,12 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L82" t="n">
+        <v>2</v>
+      </c>
+      <c r="M82" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3585,16 +3833,16 @@
         <v>3</v>
       </c>
       <c r="F83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -3603,6 +3851,9 @@
         <v>0</v>
       </c>
       <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3623,24 +3874,27 @@
         <v>1</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3661,7 +3915,7 @@
         <v>3</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -3676,9 +3930,12 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L85" t="n">
+        <v>2</v>
+      </c>
+      <c r="M85" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3699,7 +3956,7 @@
         <v>22</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -3711,12 +3968,15 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K86" t="n">
+        <v>3</v>
+      </c>
+      <c r="L86" t="n">
         <v>12</v>
       </c>
-      <c r="L86" t="n">
+      <c r="M86" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3737,24 +3997,27 @@
         <v>14</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
       </c>
       <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
         <v>9</v>
       </c>
-      <c r="L87" t="n">
+      <c r="M87" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3775,7 +4038,7 @@
         <v>6</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -3787,12 +4050,15 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
+        <v>1</v>
+      </c>
+      <c r="L88" t="n">
         <v>6</v>
       </c>
-      <c r="L88" t="n">
+      <c r="M88" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3813,7 +4079,7 @@
         <v>16</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -3825,12 +4091,15 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L89" t="n">
+        <v>7</v>
+      </c>
+      <c r="M89" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3869,6 +4138,9 @@
         <v>0</v>
       </c>
       <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3889,24 +4161,27 @@
         <v>10</v>
       </c>
       <c r="F91" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L91" t="n">
+        <v>7</v>
+      </c>
+      <c r="M91" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3927,7 +4202,7 @@
         <v>6</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -3942,9 +4217,12 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
         <v>5</v>
       </c>
-      <c r="L92" t="n">
+      <c r="M92" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3965,13 +4243,13 @@
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
@@ -3983,6 +4261,9 @@
         <v>0</v>
       </c>
       <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4021,6 +4302,9 @@
         <v>0</v>
       </c>
       <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4041,7 +4325,7 @@
         <v>2</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -4056,9 +4340,12 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" t="n">
+        <v>1</v>
+      </c>
+      <c r="M95" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4079,24 +4366,27 @@
         <v>5</v>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L96" t="n">
+        <v>3</v>
+      </c>
+      <c r="M96" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4117,7 +4407,7 @@
         <v>12</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -4132,9 +4422,12 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
         <v>4</v>
       </c>
-      <c r="L97" t="n">
+      <c r="M97" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4155,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -4167,12 +4460,15 @@
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K98" t="n">
         <v>2</v>
       </c>
       <c r="L98" t="n">
+        <v>2</v>
+      </c>
+      <c r="M98" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4193,7 +4489,7 @@
         <v>3</v>
       </c>
       <c r="F99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -4211,6 +4507,9 @@
         <v>0</v>
       </c>
       <c r="L99" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4231,7 +4530,7 @@
         <v>2</v>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -4246,9 +4545,12 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L100" t="n">
+        <v>2</v>
+      </c>
+      <c r="M100" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4269,24 +4571,27 @@
         <v>5</v>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L101" t="n">
+        <v>2</v>
+      </c>
+      <c r="M101" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4322,9 +4627,12 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L102" t="n">
+        <v>1</v>
+      </c>
+      <c r="M102" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4351,18 +4659,21 @@
         <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L103" t="n">
+        <v>2</v>
+      </c>
+      <c r="M103" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4383,7 +4694,7 @@
         <v>3</v>
       </c>
       <c r="F104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -4398,9 +4709,12 @@
         <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L104" t="n">
+        <v>3</v>
+      </c>
+      <c r="M104" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4436,9 +4750,12 @@
         <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L105" t="n">
+        <v>2</v>
+      </c>
+      <c r="M105" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4462,10 +4779,10 @@
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I106" t="n">
         <v>0</v>
@@ -4477,6 +4794,9 @@
         <v>0</v>
       </c>
       <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4497,10 +4817,10 @@
         <v>2</v>
       </c>
       <c r="F107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -4515,6 +4835,9 @@
         <v>0</v>
       </c>
       <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4553,6 +4876,9 @@
         <v>0</v>
       </c>
       <c r="L108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4591,6 +4917,9 @@
         <v>0</v>
       </c>
       <c r="L109" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4611,10 +4940,10 @@
         <v>9</v>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -4626,9 +4955,12 @@
         <v>0</v>
       </c>
       <c r="K110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" t="n">
         <v>5</v>
       </c>
-      <c r="L110" t="n">
+      <c r="M110" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4649,13 +4981,13 @@
         <v>15</v>
       </c>
       <c r="F111" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I111" t="n">
         <v>0</v>
@@ -4664,9 +4996,12 @@
         <v>0</v>
       </c>
       <c r="K111" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" t="n">
         <v>10</v>
       </c>
-      <c r="L111" t="n">
+      <c r="M111" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4705,6 +5040,9 @@
         <v>0</v>
       </c>
       <c r="L112" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4725,24 +5063,27 @@
         <v>7</v>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L113" t="n">
+        <v>1</v>
+      </c>
+      <c r="M113" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4769,18 +5110,21 @@
         <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
       </c>
       <c r="K114" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" t="n">
         <v>4</v>
       </c>
-      <c r="L114" t="n">
+      <c r="M114" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4801,24 +5145,27 @@
         <v>11</v>
       </c>
       <c r="F115" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
       </c>
       <c r="K115" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" t="n">
         <v>6</v>
       </c>
-      <c r="L115" t="n">
+      <c r="M115" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4839,24 +5186,27 @@
         <v>25</v>
       </c>
       <c r="F116" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
       </c>
       <c r="H116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" t="n">
         <v>5</v>
       </c>
-      <c r="I116" t="n">
-        <v>0</v>
-      </c>
       <c r="J116" t="n">
         <v>0</v>
       </c>
       <c r="K116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" t="n">
         <v>12</v>
       </c>
-      <c r="L116" t="n">
+      <c r="M116" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4877,7 +5227,7 @@
         <v>2</v>
       </c>
       <c r="F117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -4895,6 +5245,9 @@
         <v>0</v>
       </c>
       <c r="L117" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4915,10 +5268,10 @@
         <v>7</v>
       </c>
       <c r="F118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -4927,12 +5280,15 @@
         <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L118" t="n">
+        <v>3</v>
+      </c>
+      <c r="M118" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4953,10 +5309,10 @@
         <v>4</v>
       </c>
       <c r="F119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -4965,12 +5321,15 @@
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L119" t="n">
+        <v>2</v>
+      </c>
+      <c r="M119" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5006,9 +5365,12 @@
         <v>0</v>
       </c>
       <c r="K120" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L120" t="n">
+        <v>3</v>
+      </c>
+      <c r="M120" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5029,7 +5391,7 @@
         <v>7</v>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -5041,12 +5403,15 @@
         <v>0</v>
       </c>
       <c r="J121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K121" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L121" t="n">
+        <v>3</v>
+      </c>
+      <c r="M121" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5085,6 +5450,9 @@
         <v>0</v>
       </c>
       <c r="L122" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5105,24 +5473,27 @@
         <v>12</v>
       </c>
       <c r="F123" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
       </c>
       <c r="K123" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L123" t="n">
+        <v>2</v>
+      </c>
+      <c r="M123" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5146,7 +5517,7 @@
         <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -5158,9 +5529,12 @@
         <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L124" t="n">
+        <v>3</v>
+      </c>
+      <c r="M124" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5193,12 +5567,15 @@
         <v>0</v>
       </c>
       <c r="J125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L125" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5219,7 +5596,7 @@
         <v>11</v>
       </c>
       <c r="F126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -5234,9 +5611,12 @@
         <v>0</v>
       </c>
       <c r="K126" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" t="n">
         <v>5</v>
       </c>
-      <c r="L126" t="n">
+      <c r="M126" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5257,24 +5637,27 @@
         <v>12</v>
       </c>
       <c r="F127" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K127" t="n">
+        <v>1</v>
+      </c>
+      <c r="L127" t="n">
         <v>6</v>
       </c>
-      <c r="L127" t="n">
+      <c r="M127" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5295,10 +5678,10 @@
         <v>10</v>
       </c>
       <c r="F128" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -5307,12 +5690,15 @@
         <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K128" t="n">
+        <v>1</v>
+      </c>
+      <c r="L128" t="n">
         <v>10</v>
       </c>
-      <c r="L128" t="n">
+      <c r="M128" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5333,10 +5719,10 @@
         <v>7</v>
       </c>
       <c r="F129" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -5348,9 +5734,12 @@
         <v>0</v>
       </c>
       <c r="K129" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" t="n">
         <v>5</v>
       </c>
-      <c r="L129" t="n">
+      <c r="M129" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5371,7 +5760,7 @@
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -5389,6 +5778,9 @@
         <v>0</v>
       </c>
       <c r="L130" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5409,7 +5801,7 @@
         <v>2</v>
       </c>
       <c r="F131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -5421,12 +5813,15 @@
         <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K131" t="n">
         <v>1</v>
       </c>
       <c r="L131" t="n">
+        <v>1</v>
+      </c>
+      <c r="M131" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5447,24 +5842,27 @@
         <v>9</v>
       </c>
       <c r="F132" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
       </c>
       <c r="K132" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" t="n">
         <v>5</v>
       </c>
-      <c r="L132" t="n">
+      <c r="M132" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5485,7 +5883,7 @@
         <v>2</v>
       </c>
       <c r="F133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -5500,9 +5898,12 @@
         <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L133" t="n">
+        <v>3</v>
+      </c>
+      <c r="M133" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5523,10 +5924,10 @@
         <v>6</v>
       </c>
       <c r="F134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -5538,9 +5939,12 @@
         <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L134" t="n">
+        <v>3</v>
+      </c>
+      <c r="M134" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5561,7 +5965,7 @@
         <v>5</v>
       </c>
       <c r="F135" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -5576,9 +5980,12 @@
         <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L135" t="n">
+        <v>2</v>
+      </c>
+      <c r="M135" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5599,24 +6006,27 @@
         <v>5</v>
       </c>
       <c r="F136" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
       </c>
       <c r="K136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L136" t="n">
+        <v>1</v>
+      </c>
+      <c r="M136" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5637,7 +6047,7 @@
         <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -5655,6 +6065,9 @@
         <v>0</v>
       </c>
       <c r="L137" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5678,7 +6091,7 @@
         <v>1</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -5690,9 +6103,12 @@
         <v>0</v>
       </c>
       <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
         <v>4</v>
       </c>
-      <c r="L138" t="n">
+      <c r="M138" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5713,7 +6129,7 @@
         <v>9</v>
       </c>
       <c r="F139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -5728,9 +6144,12 @@
         <v>0</v>
       </c>
       <c r="K139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" t="n">
         <v>4</v>
       </c>
-      <c r="L139" t="n">
+      <c r="M139" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5763,12 +6182,15 @@
         <v>0</v>
       </c>
       <c r="J140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K140" t="n">
+        <v>1</v>
+      </c>
+      <c r="L140" t="n">
         <v>6</v>
       </c>
-      <c r="L140" t="n">
+      <c r="M140" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5789,7 +6211,7 @@
         <v>1</v>
       </c>
       <c r="F141" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -5804,9 +6226,12 @@
         <v>0</v>
       </c>
       <c r="K141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L141" t="n">
+        <v>1</v>
+      </c>
+      <c r="M141" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5827,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="F142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -5839,12 +6264,15 @@
         <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L142" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5865,13 +6293,13 @@
         <v>7</v>
       </c>
       <c r="F143" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I143" t="n">
         <v>0</v>
@@ -5880,9 +6308,12 @@
         <v>0</v>
       </c>
       <c r="K143" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L143" t="n">
+        <v>3</v>
+      </c>
+      <c r="M143" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5903,7 +6334,7 @@
         <v>2</v>
       </c>
       <c r="F144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -5918,9 +6349,12 @@
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L144" t="n">
+        <v>2</v>
+      </c>
+      <c r="M144" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5941,13 +6375,13 @@
         <v>6</v>
       </c>
       <c r="F145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G145" t="n">
         <v>1</v>
       </c>
       <c r="H145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I145" t="n">
         <v>0</v>
@@ -5956,9 +6390,12 @@
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L145" t="n">
+        <v>3</v>
+      </c>
+      <c r="M145" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5997,6 +6434,9 @@
         <v>0</v>
       </c>
       <c r="L146" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6032,9 +6472,12 @@
         <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L147" t="n">
+        <v>1</v>
+      </c>
+      <c r="M147" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6073,6 +6516,9 @@
         <v>0</v>
       </c>
       <c r="L148" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6108,9 +6554,12 @@
         <v>0</v>
       </c>
       <c r="K149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L149" t="n">
+        <v>1</v>
+      </c>
+      <c r="M149" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6149,6 +6598,9 @@
         <v>0</v>
       </c>
       <c r="L150" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6172,7 +6624,7 @@
         <v>1</v>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -6184,9 +6636,12 @@
         <v>0</v>
       </c>
       <c r="K151" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L151" t="n">
+        <v>2</v>
+      </c>
+      <c r="M151" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6225,6 +6680,9 @@
         <v>0</v>
       </c>
       <c r="L152" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6245,24 +6703,27 @@
         <v>16</v>
       </c>
       <c r="F153" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I153" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J153" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K153" t="n">
+        <v>2</v>
+      </c>
+      <c r="L153" t="n">
         <v>11</v>
       </c>
-      <c r="L153" t="n">
+      <c r="M153" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6283,7 +6744,7 @@
         <v>13</v>
       </c>
       <c r="F154" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -6298,9 +6759,12 @@
         <v>0</v>
       </c>
       <c r="K154" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L154" t="n">
+        <v>7</v>
+      </c>
+      <c r="M154" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6321,24 +6785,27 @@
         <v>6</v>
       </c>
       <c r="F155" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
       </c>
       <c r="H155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
       </c>
       <c r="K155" t="n">
+        <v>0</v>
+      </c>
+      <c r="L155" t="n">
         <v>5</v>
       </c>
-      <c r="L155" t="n">
+      <c r="M155" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6359,24 +6826,27 @@
         <v>2</v>
       </c>
       <c r="F156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
       </c>
       <c r="K156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L156" t="n">
+        <v>1</v>
+      </c>
+      <c r="M156" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6397,7 +6867,7 @@
         <v>3</v>
       </c>
       <c r="F157" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -6412,9 +6882,12 @@
         <v>0</v>
       </c>
       <c r="K157" t="n">
+        <v>0</v>
+      </c>
+      <c r="L157" t="n">
         <v>5</v>
       </c>
-      <c r="L157" t="n">
+      <c r="M157" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6435,24 +6908,27 @@
         <v>34</v>
       </c>
       <c r="F158" t="n">
+        <v>3</v>
+      </c>
+      <c r="G158" t="n">
         <v>4</v>
       </c>
-      <c r="G158" t="n">
-        <v>0</v>
-      </c>
       <c r="H158" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I158" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
       </c>
       <c r="K158" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" t="n">
         <v>19</v>
       </c>
-      <c r="L158" t="n">
+      <c r="M158" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6473,10 +6949,10 @@
         <v>7</v>
       </c>
       <c r="F159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -6488,9 +6964,12 @@
         <v>0</v>
       </c>
       <c r="K159" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" t="n">
         <v>5</v>
       </c>
-      <c r="L159" t="n">
+      <c r="M159" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6511,7 +6990,7 @@
         <v>5</v>
       </c>
       <c r="F160" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -6526,9 +7005,12 @@
         <v>0</v>
       </c>
       <c r="K160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L160" t="n">
+        <v>1</v>
+      </c>
+      <c r="M160" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6549,7 +7031,7 @@
         <v>6</v>
       </c>
       <c r="F161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -6561,12 +7043,15 @@
         <v>0</v>
       </c>
       <c r="J161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K161" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L161" t="n">
+        <v>2</v>
+      </c>
+      <c r="M161" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6587,7 +7072,7 @@
         <v>14</v>
       </c>
       <c r="F162" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -6602,9 +7087,12 @@
         <v>0</v>
       </c>
       <c r="K162" t="n">
+        <v>0</v>
+      </c>
+      <c r="L162" t="n">
         <v>8</v>
       </c>
-      <c r="L162" t="n">
+      <c r="M162" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6640,9 +7128,12 @@
         <v>0</v>
       </c>
       <c r="K163" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L163" t="n">
+        <v>2</v>
+      </c>
+      <c r="M163" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6666,21 +7157,24 @@
         <v>3</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
       </c>
       <c r="K164" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L164" t="n">
+        <v>3</v>
+      </c>
+      <c r="M164" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6719,6 +7213,9 @@
         <v>0</v>
       </c>
       <c r="L165" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6757,6 +7254,9 @@
         <v>0</v>
       </c>
       <c r="L166" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6777,24 +7277,27 @@
         <v>15</v>
       </c>
       <c r="F167" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
       </c>
       <c r="K167" t="n">
+        <v>0</v>
+      </c>
+      <c r="L167" t="n">
         <v>10</v>
       </c>
-      <c r="L167" t="n">
+      <c r="M167" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6815,10 +7318,10 @@
         <v>20</v>
       </c>
       <c r="F168" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G168" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -6830,9 +7333,12 @@
         <v>0</v>
       </c>
       <c r="K168" t="n">
+        <v>0</v>
+      </c>
+      <c r="L168" t="n">
         <v>16</v>
       </c>
-      <c r="L168" t="n">
+      <c r="M168" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6853,7 +7359,7 @@
         <v>14</v>
       </c>
       <c r="F169" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -6868,9 +7374,12 @@
         <v>0</v>
       </c>
       <c r="K169" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L169" t="n">
+        <v>7</v>
+      </c>
+      <c r="M169" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6891,7 +7400,7 @@
         <v>5</v>
       </c>
       <c r="F170" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -6906,9 +7415,12 @@
         <v>0</v>
       </c>
       <c r="K170" t="n">
+        <v>0</v>
+      </c>
+      <c r="L170" t="n">
         <v>4</v>
       </c>
-      <c r="L170" t="n">
+      <c r="M170" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6929,7 +7441,7 @@
         <v>2</v>
       </c>
       <c r="F171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -6944,9 +7456,12 @@
         <v>0</v>
       </c>
       <c r="K171" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L171" t="n">
+        <v>3</v>
+      </c>
+      <c r="M171" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6967,7 +7482,7 @@
         <v>4</v>
       </c>
       <c r="F172" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -6982,9 +7497,12 @@
         <v>0</v>
       </c>
       <c r="K172" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L172" t="n">
+        <v>2</v>
+      </c>
+      <c r="M172" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7008,21 +7526,24 @@
         <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H173" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I173" t="n">
         <v>0</v>
       </c>
       <c r="J173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K173" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L173" t="n">
+        <v>3</v>
+      </c>
+      <c r="M173" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7046,7 +7567,7 @@
         <v>1</v>
       </c>
       <c r="G174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -7058,9 +7579,12 @@
         <v>0</v>
       </c>
       <c r="K174" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L174" t="n">
+        <v>3</v>
+      </c>
+      <c r="M174" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7081,24 +7605,27 @@
         <v>31</v>
       </c>
       <c r="F175" t="n">
+        <v>8</v>
+      </c>
+      <c r="G175" t="n">
         <v>4</v>
       </c>
-      <c r="G175" t="n">
-        <v>1</v>
-      </c>
       <c r="H175" t="n">
         <v>1</v>
       </c>
       <c r="I175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J175" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K175" t="n">
+        <v>2</v>
+      </c>
+      <c r="L175" t="n">
         <v>13</v>
       </c>
-      <c r="L175" t="n">
+      <c r="M175" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7119,7 +7646,7 @@
         <v>6</v>
       </c>
       <c r="F176" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -7134,9 +7661,12 @@
         <v>0</v>
       </c>
       <c r="K176" t="n">
+        <v>0</v>
+      </c>
+      <c r="L176" t="n">
         <v>4</v>
       </c>
-      <c r="L176" t="n">
+      <c r="M176" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7157,10 +7687,10 @@
         <v>7</v>
       </c>
       <c r="F177" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G177" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -7172,9 +7702,12 @@
         <v>0</v>
       </c>
       <c r="K177" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L177" t="n">
+        <v>2</v>
+      </c>
+      <c r="M177" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7195,7 +7728,7 @@
         <v>3</v>
       </c>
       <c r="F178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -7210,9 +7743,12 @@
         <v>0</v>
       </c>
       <c r="K178" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L178" t="n">
+        <v>2</v>
+      </c>
+      <c r="M178" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7236,7 +7772,7 @@
         <v>1</v>
       </c>
       <c r="G179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -7248,9 +7784,12 @@
         <v>0</v>
       </c>
       <c r="K179" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L179" t="n">
+        <v>2</v>
+      </c>
+      <c r="M179" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7271,10 +7810,10 @@
         <v>3</v>
       </c>
       <c r="F180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G180" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -7286,9 +7825,12 @@
         <v>0</v>
       </c>
       <c r="K180" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L180" t="n">
+        <v>2</v>
+      </c>
+      <c r="M180" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7309,7 +7851,7 @@
         <v>1</v>
       </c>
       <c r="F181" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -7324,9 +7866,12 @@
         <v>0</v>
       </c>
       <c r="K181" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L181" t="n">
+        <v>2</v>
+      </c>
+      <c r="M181" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7365,6 +7910,9 @@
         <v>0</v>
       </c>
       <c r="L182" t="n">
+        <v>0</v>
+      </c>
+      <c r="M182" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7385,10 +7933,10 @@
         <v>5</v>
       </c>
       <c r="F183" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G183" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -7403,6 +7951,9 @@
         <v>0</v>
       </c>
       <c r="L183" t="n">
+        <v>0</v>
+      </c>
+      <c r="M183" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7426,7 +7977,7 @@
         <v>1</v>
       </c>
       <c r="G184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -7438,9 +7989,12 @@
         <v>0</v>
       </c>
       <c r="K184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L184" t="n">
+        <v>1</v>
+      </c>
+      <c r="M184" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7461,24 +8015,27 @@
         <v>7</v>
       </c>
       <c r="F185" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G185" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H185" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I185" t="n">
         <v>0</v>
       </c>
       <c r="J185" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K185" t="n">
+        <v>2</v>
+      </c>
+      <c r="L185" t="n">
         <v>4</v>
       </c>
-      <c r="L185" t="n">
+      <c r="M185" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7499,24 +8056,27 @@
         <v>27</v>
       </c>
       <c r="F186" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H186" t="n">
         <v>1</v>
       </c>
       <c r="I186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J186" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K186" t="n">
+        <v>2</v>
+      </c>
+      <c r="L186" t="n">
         <v>16</v>
       </c>
-      <c r="L186" t="n">
+      <c r="M186" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7537,10 +8097,10 @@
         <v>15</v>
       </c>
       <c r="F187" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -7549,12 +8109,15 @@
         <v>0</v>
       </c>
       <c r="J187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K187" t="n">
+        <v>1</v>
+      </c>
+      <c r="L187" t="n">
         <v>12</v>
       </c>
-      <c r="L187" t="n">
+      <c r="M187" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7575,24 +8138,27 @@
         <v>17</v>
       </c>
       <c r="F188" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
       </c>
       <c r="K188" t="n">
+        <v>0</v>
+      </c>
+      <c r="L188" t="n">
         <v>8</v>
       </c>
-      <c r="L188" t="n">
+      <c r="M188" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7613,10 +8179,10 @@
         <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -7628,9 +8194,12 @@
         <v>0</v>
       </c>
       <c r="K189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L189" t="n">
+        <v>1</v>
+      </c>
+      <c r="M189" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7651,10 +8220,10 @@
         <v>2</v>
       </c>
       <c r="F190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -7666,9 +8235,12 @@
         <v>0</v>
       </c>
       <c r="K190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L190" t="n">
+        <v>1</v>
+      </c>
+      <c r="M190" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7707,6 +8279,9 @@
         <v>0</v>
       </c>
       <c r="L191" t="n">
+        <v>0</v>
+      </c>
+      <c r="M191" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7727,7 +8302,7 @@
         <v>9</v>
       </c>
       <c r="F192" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -7742,9 +8317,12 @@
         <v>0</v>
       </c>
       <c r="K192" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L192" t="n">
+        <v>7</v>
+      </c>
+      <c r="M192" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7765,7 +8343,7 @@
         <v>5</v>
       </c>
       <c r="F193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -7780,9 +8358,12 @@
         <v>0</v>
       </c>
       <c r="K193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L193" t="n">
+        <v>1</v>
+      </c>
+      <c r="M193" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7803,10 +8384,10 @@
         <v>1</v>
       </c>
       <c r="F194" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -7821,6 +8402,9 @@
         <v>0</v>
       </c>
       <c r="L194" t="n">
+        <v>0</v>
+      </c>
+      <c r="M194" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7841,7 +8425,7 @@
         <v>1</v>
       </c>
       <c r="F195" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -7859,6 +8443,9 @@
         <v>0</v>
       </c>
       <c r="L195" t="n">
+        <v>0</v>
+      </c>
+      <c r="M195" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7894,9 +8481,12 @@
         <v>0</v>
       </c>
       <c r="K196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L196" t="n">
+        <v>1</v>
+      </c>
+      <c r="M196" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7920,7 +8510,7 @@
         <v>1</v>
       </c>
       <c r="G197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -7932,9 +8522,12 @@
         <v>0</v>
       </c>
       <c r="K197" t="n">
+        <v>0</v>
+      </c>
+      <c r="L197" t="n">
         <v>10</v>
       </c>
-      <c r="L197" t="n">
+      <c r="M197" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7955,10 +8548,10 @@
         <v>15</v>
       </c>
       <c r="F198" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -7970,9 +8563,12 @@
         <v>0</v>
       </c>
       <c r="K198" t="n">
+        <v>0</v>
+      </c>
+      <c r="L198" t="n">
         <v>13</v>
       </c>
-      <c r="L198" t="n">
+      <c r="M198" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7993,7 +8589,7 @@
         <v>2</v>
       </c>
       <c r="F199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -8008,9 +8604,12 @@
         <v>0</v>
       </c>
       <c r="K199" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L199" t="n">
+        <v>2</v>
+      </c>
+      <c r="M199" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8031,7 +8630,7 @@
         <v>8</v>
       </c>
       <c r="F200" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -8049,6 +8648,9 @@
         <v>0</v>
       </c>
       <c r="L200" t="n">
+        <v>0</v>
+      </c>
+      <c r="M200" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8069,7 +8671,7 @@
         <v>1</v>
       </c>
       <c r="F201" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -8087,6 +8689,9 @@
         <v>0</v>
       </c>
       <c r="L201" t="n">
+        <v>0</v>
+      </c>
+      <c r="M201" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8107,7 +8712,7 @@
         <v>7</v>
       </c>
       <c r="F202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -8122,9 +8727,12 @@
         <v>0</v>
       </c>
       <c r="K202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L202" t="n">
+        <v>1</v>
+      </c>
+      <c r="M202" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8145,7 +8753,7 @@
         <v>0</v>
       </c>
       <c r="F203" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -8160,9 +8768,12 @@
         <v>0</v>
       </c>
       <c r="K203" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L203" t="n">
+        <v>2</v>
+      </c>
+      <c r="M203" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8183,24 +8794,27 @@
         <v>7</v>
       </c>
       <c r="F204" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
       </c>
       <c r="H204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
       </c>
       <c r="K204" t="n">
+        <v>0</v>
+      </c>
+      <c r="L204" t="n">
         <v>5</v>
       </c>
-      <c r="L204" t="n">
+      <c r="M204" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8221,7 +8835,7 @@
         <v>10</v>
       </c>
       <c r="F205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -8236,9 +8850,12 @@
         <v>0</v>
       </c>
       <c r="K205" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L205" t="n">
+        <v>3</v>
+      </c>
+      <c r="M205" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8259,24 +8876,27 @@
         <v>12</v>
       </c>
       <c r="F206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
       </c>
       <c r="H206" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
       </c>
       <c r="K206" t="n">
+        <v>0</v>
+      </c>
+      <c r="L206" t="n">
         <v>8</v>
       </c>
-      <c r="L206" t="n">
+      <c r="M206" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8312,9 +8932,12 @@
         <v>0</v>
       </c>
       <c r="K207" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L207" t="n">
+        <v>3</v>
+      </c>
+      <c r="M207" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8353,6 +8976,9 @@
         <v>0</v>
       </c>
       <c r="L208" t="n">
+        <v>0</v>
+      </c>
+      <c r="M208" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8373,7 +8999,7 @@
         <v>1</v>
       </c>
       <c r="F209" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -8388,9 +9014,12 @@
         <v>0</v>
       </c>
       <c r="K209" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L209" t="n">
+        <v>2</v>
+      </c>
+      <c r="M209" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8429,6 +9058,9 @@
         <v>0</v>
       </c>
       <c r="L210" t="n">
+        <v>0</v>
+      </c>
+      <c r="M210" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8449,7 +9081,7 @@
         <v>3</v>
       </c>
       <c r="F211" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -8464,9 +9096,12 @@
         <v>0</v>
       </c>
       <c r="K211" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L211" t="n">
+        <v>3</v>
+      </c>
+      <c r="M211" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8487,7 +9122,7 @@
         <v>12</v>
       </c>
       <c r="F212" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -8499,12 +9134,15 @@
         <v>0</v>
       </c>
       <c r="J212" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K212" t="n">
+        <v>1</v>
+      </c>
+      <c r="L212" t="n">
         <v>8</v>
       </c>
-      <c r="L212" t="n">
+      <c r="M212" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8537,12 +9175,15 @@
         <v>0</v>
       </c>
       <c r="J213" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K213" t="n">
+        <v>1</v>
+      </c>
+      <c r="L213" t="n">
         <v>5</v>
       </c>
-      <c r="L213" t="n">
+      <c r="M213" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8566,21 +9207,24 @@
         <v>1</v>
       </c>
       <c r="G214" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H214" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I214" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
       </c>
       <c r="K214" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L214" t="n">
+        <v>1</v>
+      </c>
+      <c r="M214" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8601,7 +9245,7 @@
         <v>2</v>
       </c>
       <c r="F215" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -8616,9 +9260,12 @@
         <v>0</v>
       </c>
       <c r="K215" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L215" t="n">
+        <v>3</v>
+      </c>
+      <c r="M215" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8639,7 +9286,7 @@
         <v>6</v>
       </c>
       <c r="F216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -8654,9 +9301,12 @@
         <v>0</v>
       </c>
       <c r="K216" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L216" t="n">
+        <v>3</v>
+      </c>
+      <c r="M216" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8677,7 +9327,7 @@
         <v>3</v>
       </c>
       <c r="F217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -8692,9 +9342,12 @@
         <v>0</v>
       </c>
       <c r="K217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L217" t="n">
+        <v>1</v>
+      </c>
+      <c r="M217" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8733,6 +9386,9 @@
         <v>0</v>
       </c>
       <c r="L218" t="n">
+        <v>0</v>
+      </c>
+      <c r="M218" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8753,7 +9409,7 @@
         <v>1</v>
       </c>
       <c r="F219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -8768,9 +9424,12 @@
         <v>0</v>
       </c>
       <c r="K219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L219" t="n">
+        <v>1</v>
+      </c>
+      <c r="M219" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8791,24 +9450,27 @@
         <v>5</v>
       </c>
       <c r="F220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
       </c>
       <c r="H220" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
       </c>
       <c r="K220" t="n">
+        <v>0</v>
+      </c>
+      <c r="L220" t="n">
         <v>4</v>
       </c>
-      <c r="L220" t="n">
+      <c r="M220" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8835,18 +9497,21 @@
         <v>0</v>
       </c>
       <c r="H221" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
       </c>
       <c r="K221" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L221" t="n">
+        <v>3</v>
+      </c>
+      <c r="M221" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8867,7 +9532,7 @@
         <v>1</v>
       </c>
       <c r="F222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -8882,9 +9547,12 @@
         <v>0</v>
       </c>
       <c r="K222" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L222" t="n">
+        <v>1</v>
+      </c>
+      <c r="M222" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8905,7 +9573,7 @@
         <v>5</v>
       </c>
       <c r="F223" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -8917,12 +9585,15 @@
         <v>0</v>
       </c>
       <c r="J223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K223" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L223" t="n">
+        <v>2</v>
+      </c>
+      <c r="M223" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8943,7 +9614,7 @@
         <v>1</v>
       </c>
       <c r="F224" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -8958,9 +9629,12 @@
         <v>0</v>
       </c>
       <c r="K224" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L224" t="n">
+        <v>2</v>
+      </c>
+      <c r="M224" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8984,7 +9658,7 @@
         <v>1</v>
       </c>
       <c r="G225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -8996,9 +9670,12 @@
         <v>0</v>
       </c>
       <c r="K225" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L225" t="n">
+        <v>3</v>
+      </c>
+      <c r="M225" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9019,7 +9696,7 @@
         <v>1</v>
       </c>
       <c r="F226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -9037,6 +9714,9 @@
         <v>0</v>
       </c>
       <c r="L226" t="n">
+        <v>0</v>
+      </c>
+      <c r="M226" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9075,6 +9755,9 @@
         <v>0</v>
       </c>
       <c r="L227" t="n">
+        <v>0</v>
+      </c>
+      <c r="M227" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9095,24 +9778,27 @@
         <v>20</v>
       </c>
       <c r="F228" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H228" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I228" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K228" t="n">
+        <v>1</v>
+      </c>
+      <c r="L228" t="n">
         <v>6</v>
       </c>
-      <c r="L228" t="n">
+      <c r="M228" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9133,24 +9819,27 @@
         <v>28</v>
       </c>
       <c r="F229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K229" t="n">
+        <v>1</v>
+      </c>
+      <c r="L229" t="n">
         <v>10</v>
       </c>
-      <c r="L229" t="n">
+      <c r="M229" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9189,6 +9878,9 @@
         <v>0</v>
       </c>
       <c r="L230" t="n">
+        <v>0</v>
+      </c>
+      <c r="M230" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9227,6 +9919,9 @@
         <v>0</v>
       </c>
       <c r="L231" t="n">
+        <v>0</v>
+      </c>
+      <c r="M231" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9247,13 +9942,13 @@
         <v>2</v>
       </c>
       <c r="F232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G232" t="n">
         <v>1</v>
       </c>
       <c r="H232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I232" t="n">
         <v>0</v>
@@ -9265,6 +9960,9 @@
         <v>0</v>
       </c>
       <c r="L232" t="n">
+        <v>0</v>
+      </c>
+      <c r="M232" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9285,7 +9983,7 @@
         <v>5</v>
       </c>
       <c r="F233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -9303,6 +10001,9 @@
         <v>0</v>
       </c>
       <c r="L233" t="n">
+        <v>0</v>
+      </c>
+      <c r="M233" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9323,7 +10024,7 @@
         <v>0</v>
       </c>
       <c r="F234" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -9338,9 +10039,12 @@
         <v>0</v>
       </c>
       <c r="K234" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L234" t="n">
+        <v>1</v>
+      </c>
+      <c r="M234" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9361,7 +10065,7 @@
         <v>3</v>
       </c>
       <c r="F235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -9376,9 +10080,12 @@
         <v>0</v>
       </c>
       <c r="K235" t="n">
+        <v>0</v>
+      </c>
+      <c r="L235" t="n">
         <v>4</v>
       </c>
-      <c r="L235" t="n">
+      <c r="M235" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9399,10 +10106,10 @@
         <v>11</v>
       </c>
       <c r="F236" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G236" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -9411,12 +10118,15 @@
         <v>0</v>
       </c>
       <c r="J236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K236" t="n">
+        <v>1</v>
+      </c>
+      <c r="L236" t="n">
         <v>8</v>
       </c>
-      <c r="L236" t="n">
+      <c r="M236" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9437,10 +10147,10 @@
         <v>6</v>
       </c>
       <c r="F237" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G237" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -9449,12 +10159,15 @@
         <v>0</v>
       </c>
       <c r="J237" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K237" t="n">
+        <v>1</v>
+      </c>
+      <c r="L237" t="n">
         <v>5</v>
       </c>
-      <c r="L237" t="n">
+      <c r="M237" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9475,7 +10188,7 @@
         <v>2</v>
       </c>
       <c r="F238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -9490,9 +10203,12 @@
         <v>0</v>
       </c>
       <c r="K238" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L238" t="n">
+        <v>2</v>
+      </c>
+      <c r="M238" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9513,16 +10229,16 @@
         <v>3</v>
       </c>
       <c r="F239" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H239" t="n">
         <v>1</v>
       </c>
       <c r="I239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -9531,6 +10247,9 @@
         <v>0</v>
       </c>
       <c r="L239" t="n">
+        <v>0</v>
+      </c>
+      <c r="M239" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9551,7 +10270,7 @@
         <v>3</v>
       </c>
       <c r="F240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -9566,9 +10285,12 @@
         <v>0</v>
       </c>
       <c r="K240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L240" t="n">
+        <v>1</v>
+      </c>
+      <c r="M240" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9604,9 +10326,12 @@
         <v>0</v>
       </c>
       <c r="K241" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L241" t="n">
+        <v>1</v>
+      </c>
+      <c r="M241" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9627,7 +10352,7 @@
         <v>10</v>
       </c>
       <c r="F242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -9639,12 +10364,15 @@
         <v>0</v>
       </c>
       <c r="J242" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K242" t="n">
         <v>1</v>
       </c>
       <c r="L242" t="n">
+        <v>1</v>
+      </c>
+      <c r="M242" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9665,24 +10393,27 @@
         <v>11</v>
       </c>
       <c r="F243" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
       </c>
       <c r="H243" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I243" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
       </c>
       <c r="K243" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L243" t="n">
+        <v>3</v>
+      </c>
+      <c r="M243" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9703,24 +10434,27 @@
         <v>23</v>
       </c>
       <c r="F244" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G244" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H244" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I244" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J244" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K244" t="n">
+        <v>1</v>
+      </c>
+      <c r="L244" t="n">
         <v>10</v>
       </c>
-      <c r="L244" t="n">
+      <c r="M244" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9741,24 +10475,27 @@
         <v>16</v>
       </c>
       <c r="F245" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
       </c>
       <c r="H245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
       </c>
       <c r="K245" t="n">
+        <v>0</v>
+      </c>
+      <c r="L245" t="n">
         <v>12</v>
       </c>
-      <c r="L245" t="n">
+      <c r="M245" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9779,7 +10516,7 @@
         <v>1</v>
       </c>
       <c r="F246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -9794,9 +10531,12 @@
         <v>0</v>
       </c>
       <c r="K246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L246" t="n">
+        <v>1</v>
+      </c>
+      <c r="M246" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9817,24 +10557,27 @@
         <v>8</v>
       </c>
       <c r="F247" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G247" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H247" t="n">
         <v>1</v>
       </c>
       <c r="I247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J247" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K247" t="n">
+        <v>1</v>
+      </c>
+      <c r="L247" t="n">
         <v>5</v>
       </c>
-      <c r="L247" t="n">
+      <c r="M247" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9855,7 +10598,7 @@
         <v>11</v>
       </c>
       <c r="F248" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -9867,12 +10610,15 @@
         <v>0</v>
       </c>
       <c r="J248" t="n">
+        <v>0</v>
+      </c>
+      <c r="K248" t="n">
         <v>6</v>
       </c>
-      <c r="K248" t="n">
-        <v>1</v>
-      </c>
       <c r="L248" t="n">
+        <v>1</v>
+      </c>
+      <c r="M248" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9893,7 +10639,7 @@
         <v>17</v>
       </c>
       <c r="F249" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -9905,12 +10651,15 @@
         <v>0</v>
       </c>
       <c r="J249" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K249" t="n">
+        <v>2</v>
+      </c>
+      <c r="L249" t="n">
         <v>4</v>
       </c>
-      <c r="L249" t="n">
+      <c r="M249" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9931,7 +10680,7 @@
         <v>3</v>
       </c>
       <c r="F250" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -9943,12 +10692,15 @@
         <v>0</v>
       </c>
       <c r="J250" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K250" t="n">
         <v>1</v>
       </c>
       <c r="L250" t="n">
+        <v>1</v>
+      </c>
+      <c r="M250" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9987,6 +10739,9 @@
         <v>0</v>
       </c>
       <c r="L251" t="n">
+        <v>0</v>
+      </c>
+      <c r="M251" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10007,7 +10762,7 @@
         <v>3</v>
       </c>
       <c r="F252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10025,6 +10780,9 @@
         <v>0</v>
       </c>
       <c r="L252" t="n">
+        <v>0</v>
+      </c>
+      <c r="M252" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10045,24 +10803,27 @@
         <v>13</v>
       </c>
       <c r="F253" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G253" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H253" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I253" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J253" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K253" t="n">
+        <v>1</v>
+      </c>
+      <c r="L253" t="n">
         <v>4</v>
       </c>
-      <c r="L253" t="n">
+      <c r="M253" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10083,7 +10844,7 @@
         <v>12</v>
       </c>
       <c r="F254" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G254" t="n">
         <v>0</v>
@@ -10098,9 +10859,12 @@
         <v>0</v>
       </c>
       <c r="K254" t="n">
+        <v>0</v>
+      </c>
+      <c r="L254" t="n">
         <v>4</v>
       </c>
-      <c r="L254" t="n">
+      <c r="M254" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10136,9 +10900,12 @@
         <v>0</v>
       </c>
       <c r="K255" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L255" t="n">
+        <v>7</v>
+      </c>
+      <c r="M255" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10162,7 +10929,7 @@
         <v>1</v>
       </c>
       <c r="G256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -10174,9 +10941,12 @@
         <v>0</v>
       </c>
       <c r="K256" t="n">
+        <v>0</v>
+      </c>
+      <c r="L256" t="n">
         <v>4</v>
       </c>
-      <c r="L256" t="n">
+      <c r="M256" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10197,10 +10967,10 @@
         <v>3</v>
       </c>
       <c r="F257" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G257" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H257" t="n">
         <v>0</v>
@@ -10209,12 +10979,15 @@
         <v>0</v>
       </c>
       <c r="J257" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K257" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L257" t="n">
+        <v>3</v>
+      </c>
+      <c r="M257" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10235,24 +11008,27 @@
         <v>6</v>
       </c>
       <c r="F258" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G258" t="n">
         <v>0</v>
       </c>
       <c r="H258" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I258" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
       </c>
       <c r="K258" t="n">
+        <v>0</v>
+      </c>
+      <c r="L258" t="n">
         <v>5</v>
       </c>
-      <c r="L258" t="n">
+      <c r="M258" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10291,6 +11067,9 @@
         <v>0</v>
       </c>
       <c r="L259" t="n">
+        <v>0</v>
+      </c>
+      <c r="M259" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10311,7 +11090,7 @@
         <v>2</v>
       </c>
       <c r="F260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G260" t="n">
         <v>0</v>
@@ -10326,9 +11105,12 @@
         <v>0</v>
       </c>
       <c r="K260" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L260" t="n">
+        <v>3</v>
+      </c>
+      <c r="M260" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10349,24 +11131,27 @@
         <v>6</v>
       </c>
       <c r="F261" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G261" t="n">
         <v>0</v>
       </c>
       <c r="H261" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
       </c>
       <c r="K261" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L261" t="n">
+        <v>2</v>
+      </c>
+      <c r="M261" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10387,10 +11172,10 @@
         <v>4</v>
       </c>
       <c r="F262" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -10402,9 +11187,12 @@
         <v>0</v>
       </c>
       <c r="K262" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L262" t="n">
+        <v>3</v>
+      </c>
+      <c r="M262" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10425,7 +11213,7 @@
         <v>1</v>
       </c>
       <c r="F263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G263" t="n">
         <v>0</v>
@@ -10440,9 +11228,12 @@
         <v>0</v>
       </c>
       <c r="K263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L263" t="n">
+        <v>1</v>
+      </c>
+      <c r="M263" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10463,10 +11254,10 @@
         <v>8</v>
       </c>
       <c r="F264" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -10478,9 +11269,12 @@
         <v>0</v>
       </c>
       <c r="K264" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L264" t="n">
+        <v>2</v>
+      </c>
+      <c r="M264" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10516,9 +11310,12 @@
         <v>0</v>
       </c>
       <c r="K265" t="n">
+        <v>0</v>
+      </c>
+      <c r="L265" t="n">
         <v>6</v>
       </c>
-      <c r="L265" t="n">
+      <c r="M265" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10539,7 +11336,7 @@
         <v>6</v>
       </c>
       <c r="F266" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G266" t="n">
         <v>0</v>
@@ -10554,9 +11351,12 @@
         <v>0</v>
       </c>
       <c r="K266" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L266" t="n">
+        <v>1</v>
+      </c>
+      <c r="M266" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10577,10 +11377,10 @@
         <v>15</v>
       </c>
       <c r="F267" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -10589,12 +11389,15 @@
         <v>0</v>
       </c>
       <c r="J267" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K267" t="n">
+        <v>1</v>
+      </c>
+      <c r="L267" t="n">
         <v>5</v>
       </c>
-      <c r="L267" t="n">
+      <c r="M267" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10630,9 +11433,12 @@
         <v>0</v>
       </c>
       <c r="K268" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L268" t="n">
+        <v>3</v>
+      </c>
+      <c r="M268" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10656,21 +11462,24 @@
         <v>2</v>
       </c>
       <c r="G269" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H269" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
       </c>
       <c r="K269" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L269" t="n">
+        <v>2</v>
+      </c>
+      <c r="M269" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10691,7 +11500,7 @@
         <v>8</v>
       </c>
       <c r="F270" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G270" t="n">
         <v>0</v>
@@ -10703,12 +11512,15 @@
         <v>0</v>
       </c>
       <c r="J270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K270" t="n">
+        <v>1</v>
+      </c>
+      <c r="L270" t="n">
         <v>10</v>
       </c>
-      <c r="L270" t="n">
+      <c r="M270" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10747,6 +11559,9 @@
         <v>0</v>
       </c>
       <c r="L271" t="n">
+        <v>0</v>
+      </c>
+      <c r="M271" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10767,7 +11582,7 @@
         <v>5</v>
       </c>
       <c r="F272" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G272" t="n">
         <v>0</v>
@@ -10782,9 +11597,12 @@
         <v>0</v>
       </c>
       <c r="K272" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L272" t="n">
+        <v>3</v>
+      </c>
+      <c r="M272" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10805,24 +11623,27 @@
         <v>4</v>
       </c>
       <c r="F273" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H273" t="n">
         <v>1</v>
       </c>
       <c r="I273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
       </c>
       <c r="K273" t="n">
+        <v>0</v>
+      </c>
+      <c r="L273" t="n">
         <v>6</v>
       </c>
-      <c r="L273" t="n">
+      <c r="M273" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10846,21 +11667,24 @@
         <v>0</v>
       </c>
       <c r="G274" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H274" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I274" t="n">
         <v>0</v>
       </c>
       <c r="J274" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K274" t="n">
         <v>2</v>
       </c>
       <c r="L274" t="n">
+        <v>2</v>
+      </c>
+      <c r="M274" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10896,9 +11720,12 @@
         <v>0</v>
       </c>
       <c r="K275" t="n">
+        <v>0</v>
+      </c>
+      <c r="L275" t="n">
         <v>4</v>
       </c>
-      <c r="L275" t="n">
+      <c r="M275" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10928,15 +11755,18 @@
         <v>0</v>
       </c>
       <c r="I276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K276" t="n">
+        <v>0</v>
+      </c>
+      <c r="L276" t="n">
         <v>5</v>
       </c>
-      <c r="L276" t="n">
+      <c r="M276" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10957,13 +11787,13 @@
         <v>3</v>
       </c>
       <c r="F277" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G277" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H277" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I277" t="n">
         <v>0</v>
@@ -10972,9 +11802,12 @@
         <v>0</v>
       </c>
       <c r="K277" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L277" t="n">
+        <v>3</v>
+      </c>
+      <c r="M277" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10995,16 +11828,16 @@
         <v>5</v>
       </c>
       <c r="F278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G278" t="n">
         <v>0</v>
       </c>
       <c r="H278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J278" t="n">
         <v>0</v>
@@ -11013,6 +11846,9 @@
         <v>0</v>
       </c>
       <c r="L278" t="n">
+        <v>0</v>
+      </c>
+      <c r="M278" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11036,7 +11872,7 @@
         <v>1</v>
       </c>
       <c r="G279" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -11048,9 +11884,12 @@
         <v>0</v>
       </c>
       <c r="K279" t="n">
+        <v>0</v>
+      </c>
+      <c r="L279" t="n">
         <v>6</v>
       </c>
-      <c r="L279" t="n">
+      <c r="M279" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11071,7 +11910,7 @@
         <v>7</v>
       </c>
       <c r="F280" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G280" t="n">
         <v>0</v>
@@ -11086,9 +11925,12 @@
         <v>0</v>
       </c>
       <c r="K280" t="n">
+        <v>0</v>
+      </c>
+      <c r="L280" t="n">
         <v>10</v>
       </c>
-      <c r="L280" t="n">
+      <c r="M280" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11127,6 +11969,9 @@
         <v>0</v>
       </c>
       <c r="L281" t="n">
+        <v>0</v>
+      </c>
+      <c r="M281" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11147,7 +11992,7 @@
         <v>1</v>
       </c>
       <c r="F282" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G282" t="n">
         <v>0</v>
@@ -11162,9 +12007,12 @@
         <v>0</v>
       </c>
       <c r="K282" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L282" t="n">
+        <v>2</v>
+      </c>
+      <c r="M282" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11203,6 +12051,9 @@
         <v>0</v>
       </c>
       <c r="L283" t="n">
+        <v>0</v>
+      </c>
+      <c r="M283" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11238,9 +12089,12 @@
         <v>0</v>
       </c>
       <c r="K284" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L284" t="n">
+        <v>2</v>
+      </c>
+      <c r="M284" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11279,6 +12133,9 @@
         <v>0</v>
       </c>
       <c r="L285" t="n">
+        <v>0</v>
+      </c>
+      <c r="M285" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11314,9 +12171,12 @@
         <v>0</v>
       </c>
       <c r="K286" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L286" t="n">
+        <v>1</v>
+      </c>
+      <c r="M286" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11337,16 +12197,16 @@
         <v>2</v>
       </c>
       <c r="F287" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G287" t="n">
         <v>0</v>
       </c>
       <c r="H287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J287" t="n">
         <v>0</v>
@@ -11355,6 +12215,9 @@
         <v>0</v>
       </c>
       <c r="L287" t="n">
+        <v>0</v>
+      </c>
+      <c r="M287" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11375,24 +12238,27 @@
         <v>10</v>
       </c>
       <c r="F288" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H288" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J288" t="n">
         <v>0</v>
       </c>
       <c r="K288" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L288" t="n">
+        <v>3</v>
+      </c>
+      <c r="M288" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11413,7 +12279,7 @@
         <v>2</v>
       </c>
       <c r="F289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G289" t="n">
         <v>0</v>
@@ -11428,9 +12294,12 @@
         <v>0</v>
       </c>
       <c r="K289" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L289" t="n">
+        <v>2</v>
+      </c>
+      <c r="M289" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11466,9 +12335,12 @@
         <v>0</v>
       </c>
       <c r="K290" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L290" t="n">
+        <v>2</v>
+      </c>
+      <c r="M290" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11489,7 +12361,7 @@
         <v>7</v>
       </c>
       <c r="F291" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G291" t="n">
         <v>0</v>
@@ -11504,9 +12376,12 @@
         <v>0</v>
       </c>
       <c r="K291" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L291" t="n">
+        <v>3</v>
+      </c>
+      <c r="M291" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11545,6 +12420,9 @@
         <v>0</v>
       </c>
       <c r="L292" t="n">
+        <v>0</v>
+      </c>
+      <c r="M292" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11565,7 +12443,7 @@
         <v>2</v>
       </c>
       <c r="F293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G293" t="n">
         <v>0</v>
@@ -11580,9 +12458,12 @@
         <v>0</v>
       </c>
       <c r="K293" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L293" t="n">
+        <v>2</v>
+      </c>
+      <c r="M293" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11603,7 +12484,7 @@
         <v>2</v>
       </c>
       <c r="F294" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G294" t="n">
         <v>0</v>
@@ -11621,6 +12502,9 @@
         <v>0</v>
       </c>
       <c r="L294" t="n">
+        <v>0</v>
+      </c>
+      <c r="M294" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11641,7 +12525,7 @@
         <v>2</v>
       </c>
       <c r="F295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G295" t="n">
         <v>0</v>
@@ -11656,9 +12540,12 @@
         <v>0</v>
       </c>
       <c r="K295" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L295" t="n">
+        <v>2</v>
+      </c>
+      <c r="M295" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11694,9 +12581,12 @@
         <v>0</v>
       </c>
       <c r="K296" t="n">
+        <v>0</v>
+      </c>
+      <c r="L296" t="n">
         <v>8</v>
       </c>
-      <c r="L296" t="n">
+      <c r="M296" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11720,21 +12610,24 @@
         <v>3</v>
       </c>
       <c r="G297" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H297" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I297" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J297" t="n">
         <v>0</v>
       </c>
       <c r="K297" t="n">
+        <v>0</v>
+      </c>
+      <c r="L297" t="n">
         <v>15</v>
       </c>
-      <c r="L297" t="n">
+      <c r="M297" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11755,24 +12648,27 @@
         <v>24</v>
       </c>
       <c r="F298" t="n">
+        <v>9</v>
+      </c>
+      <c r="G298" t="n">
         <v>4</v>
       </c>
-      <c r="G298" t="n">
-        <v>0</v>
-      </c>
       <c r="H298" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J298" t="n">
         <v>0</v>
       </c>
       <c r="K298" t="n">
+        <v>0</v>
+      </c>
+      <c r="L298" t="n">
         <v>19</v>
       </c>
-      <c r="L298" t="n">
+      <c r="M298" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11793,7 +12689,7 @@
         <v>7</v>
       </c>
       <c r="F299" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G299" t="n">
         <v>0</v>
@@ -11808,9 +12704,12 @@
         <v>0</v>
       </c>
       <c r="K299" t="n">
+        <v>0</v>
+      </c>
+      <c r="L299" t="n">
         <v>4</v>
       </c>
-      <c r="L299" t="n">
+      <c r="M299" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11831,7 +12730,7 @@
         <v>4</v>
       </c>
       <c r="F300" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G300" t="n">
         <v>0</v>
@@ -11849,6 +12748,9 @@
         <v>0</v>
       </c>
       <c r="L300" t="n">
+        <v>0</v>
+      </c>
+      <c r="M300" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11869,24 +12771,27 @@
         <v>7</v>
       </c>
       <c r="F301" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G301" t="n">
         <v>0</v>
       </c>
       <c r="H301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J301" t="n">
         <v>0</v>
       </c>
       <c r="K301" t="n">
+        <v>0</v>
+      </c>
+      <c r="L301" t="n">
         <v>5</v>
       </c>
-      <c r="L301" t="n">
+      <c r="M301" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11910,7 +12815,7 @@
         <v>1</v>
       </c>
       <c r="G302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H302" t="n">
         <v>0</v>
@@ -11922,9 +12827,12 @@
         <v>0</v>
       </c>
       <c r="K302" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L302" t="n">
+        <v>2</v>
+      </c>
+      <c r="M302" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11963,6 +12871,9 @@
         <v>0</v>
       </c>
       <c r="L303" t="n">
+        <v>0</v>
+      </c>
+      <c r="M303" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11983,7 +12894,7 @@
         <v>1</v>
       </c>
       <c r="F304" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G304" t="n">
         <v>0</v>
@@ -12001,6 +12912,9 @@
         <v>0</v>
       </c>
       <c r="L304" t="n">
+        <v>0</v>
+      </c>
+      <c r="M304" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12039,6 +12953,9 @@
         <v>0</v>
       </c>
       <c r="L305" t="n">
+        <v>0</v>
+      </c>
+      <c r="M305" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12074,9 +12991,12 @@
         <v>0</v>
       </c>
       <c r="K306" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L306" t="n">
+        <v>1</v>
+      </c>
+      <c r="M306" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12097,7 +13017,7 @@
         <v>7</v>
       </c>
       <c r="F307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G307" t="n">
         <v>0</v>
@@ -12112,9 +13032,12 @@
         <v>0</v>
       </c>
       <c r="K307" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L307" t="n">
+        <v>3</v>
+      </c>
+      <c r="M307" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12135,10 +13058,10 @@
         <v>8</v>
       </c>
       <c r="F308" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -12150,9 +13073,12 @@
         <v>0</v>
       </c>
       <c r="K308" t="n">
+        <v>0</v>
+      </c>
+      <c r="L308" t="n">
         <v>8</v>
       </c>
-      <c r="L308" t="n">
+      <c r="M308" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12191,6 +13117,9 @@
         <v>0</v>
       </c>
       <c r="L309" t="n">
+        <v>0</v>
+      </c>
+      <c r="M309" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12211,7 +13140,7 @@
         <v>4</v>
       </c>
       <c r="F310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G310" t="n">
         <v>0</v>
@@ -12226,9 +13155,12 @@
         <v>0</v>
       </c>
       <c r="K310" t="n">
+        <v>0</v>
+      </c>
+      <c r="L310" t="n">
         <v>4</v>
       </c>
-      <c r="L310" t="n">
+      <c r="M310" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12249,7 +13181,7 @@
         <v>4</v>
       </c>
       <c r="F311" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G311" t="n">
         <v>0</v>
@@ -12264,9 +13196,12 @@
         <v>0</v>
       </c>
       <c r="K311" t="n">
+        <v>0</v>
+      </c>
+      <c r="L311" t="n">
         <v>4</v>
       </c>
-      <c r="L311" t="n">
+      <c r="M311" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12287,10 +13222,10 @@
         <v>8</v>
       </c>
       <c r="F312" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G312" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -12299,12 +13234,15 @@
         <v>0</v>
       </c>
       <c r="J312" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K312" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L312" t="n">
+        <v>3</v>
+      </c>
+      <c r="M312" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12325,10 +13263,10 @@
         <v>7</v>
       </c>
       <c r="F313" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G313" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
@@ -12340,9 +13278,12 @@
         <v>0</v>
       </c>
       <c r="K313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L313" t="n">
         <v>4</v>
       </c>
-      <c r="L313" t="n">
+      <c r="M313" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12363,7 +13304,7 @@
         <v>2</v>
       </c>
       <c r="F314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G314" t="n">
         <v>0</v>
@@ -12375,12 +13316,15 @@
         <v>0</v>
       </c>
       <c r="J314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K314" t="n">
         <v>1</v>
       </c>
       <c r="L314" t="n">
+        <v>1</v>
+      </c>
+      <c r="M314" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12401,24 +13345,27 @@
         <v>6</v>
       </c>
       <c r="F315" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H315" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J315" t="n">
         <v>0</v>
       </c>
       <c r="K315" t="n">
+        <v>0</v>
+      </c>
+      <c r="L315" t="n">
         <v>5</v>
       </c>
-      <c r="L315" t="n">
+      <c r="M315" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12457,6 +13404,9 @@
         <v>0</v>
       </c>
       <c r="L316" t="n">
+        <v>0</v>
+      </c>
+      <c r="M316" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12495,6 +13445,9 @@
         <v>0</v>
       </c>
       <c r="L317" t="n">
+        <v>0</v>
+      </c>
+      <c r="M317" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12515,24 +13468,27 @@
         <v>16</v>
       </c>
       <c r="F318" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G318" t="n">
         <v>0</v>
       </c>
       <c r="H318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J318" t="n">
         <v>0</v>
       </c>
       <c r="K318" t="n">
+        <v>0</v>
+      </c>
+      <c r="L318" t="n">
         <v>5</v>
       </c>
-      <c r="L318" t="n">
+      <c r="M318" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12556,7 +13512,7 @@
         <v>1</v>
       </c>
       <c r="G319" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -12568,9 +13524,12 @@
         <v>0</v>
       </c>
       <c r="K319" t="n">
+        <v>0</v>
+      </c>
+      <c r="L319" t="n">
         <v>4</v>
       </c>
-      <c r="L319" t="n">
+      <c r="M319" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12591,10 +13550,10 @@
         <v>5</v>
       </c>
       <c r="F320" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G320" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -12606,9 +13565,12 @@
         <v>0</v>
       </c>
       <c r="K320" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L320" t="n">
+        <v>1</v>
+      </c>
+      <c r="M320" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12647,6 +13609,9 @@
         <v>0</v>
       </c>
       <c r="L321" t="n">
+        <v>0</v>
+      </c>
+      <c r="M321" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12667,13 +13632,13 @@
         <v>4</v>
       </c>
       <c r="F322" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G322" t="n">
         <v>1</v>
       </c>
       <c r="H322" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I322" t="n">
         <v>0</v>
@@ -12682,9 +13647,12 @@
         <v>0</v>
       </c>
       <c r="K322" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L322" t="n">
+        <v>2</v>
+      </c>
+      <c r="M322" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12705,10 +13673,10 @@
         <v>6</v>
       </c>
       <c r="F323" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -12720,9 +13688,12 @@
         <v>0</v>
       </c>
       <c r="K323" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L323" t="n">
+        <v>3</v>
+      </c>
+      <c r="M323" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12743,7 +13714,7 @@
         <v>3</v>
       </c>
       <c r="F324" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G324" t="n">
         <v>0</v>
@@ -12755,12 +13726,15 @@
         <v>0</v>
       </c>
       <c r="J324" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K324" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L324" t="n">
+        <v>0</v>
+      </c>
+      <c r="M324" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12784,21 +13758,24 @@
         <v>1</v>
       </c>
       <c r="G325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H325" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I325" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J325" t="n">
         <v>0</v>
       </c>
       <c r="K325" t="n">
+        <v>0</v>
+      </c>
+      <c r="L325" t="n">
         <v>6</v>
       </c>
-      <c r="L325" t="n">
+      <c r="M325" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12819,24 +13796,27 @@
         <v>24</v>
       </c>
       <c r="F326" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G326" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H326" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I326" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J326" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K326" t="n">
+        <v>2</v>
+      </c>
+      <c r="L326" t="n">
         <v>23</v>
       </c>
-      <c r="L326" t="n">
+      <c r="M326" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12857,24 +13837,27 @@
         <v>19</v>
       </c>
       <c r="F327" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G327" t="n">
         <v>0</v>
       </c>
       <c r="H327" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I327" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J327" t="n">
         <v>0</v>
       </c>
       <c r="K327" t="n">
+        <v>0</v>
+      </c>
+      <c r="L327" t="n">
         <v>19</v>
       </c>
-      <c r="L327" t="n">
+      <c r="M327" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12895,7 +13878,7 @@
         <v>7</v>
       </c>
       <c r="F328" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G328" t="n">
         <v>0</v>
@@ -12910,9 +13893,12 @@
         <v>0</v>
       </c>
       <c r="K328" t="n">
+        <v>0</v>
+      </c>
+      <c r="L328" t="n">
         <v>5</v>
       </c>
-      <c r="L328" t="n">
+      <c r="M328" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12933,7 +13919,7 @@
         <v>7</v>
       </c>
       <c r="F329" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G329" t="n">
         <v>0</v>
@@ -12948,9 +13934,12 @@
         <v>0</v>
       </c>
       <c r="K329" t="n">
+        <v>0</v>
+      </c>
+      <c r="L329" t="n">
         <v>6</v>
       </c>
-      <c r="L329" t="n">
+      <c r="M329" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12974,7 +13963,7 @@
         <v>1</v>
       </c>
       <c r="G330" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -12986,9 +13975,12 @@
         <v>0</v>
       </c>
       <c r="K330" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L330" t="n">
+        <v>1</v>
+      </c>
+      <c r="M330" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13009,7 +14001,7 @@
         <v>5</v>
       </c>
       <c r="F331" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G331" t="n">
         <v>0</v>
@@ -13024,9 +14016,12 @@
         <v>0</v>
       </c>
       <c r="K331" t="n">
+        <v>0</v>
+      </c>
+      <c r="L331" t="n">
         <v>4</v>
       </c>
-      <c r="L331" t="n">
+      <c r="M331" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13047,24 +14042,27 @@
         <v>8</v>
       </c>
       <c r="F332" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G332" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H332" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I332" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J332" t="n">
         <v>0</v>
       </c>
       <c r="K332" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L332" t="n">
+        <v>2</v>
+      </c>
+      <c r="M332" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13085,10 +14083,10 @@
         <v>12</v>
       </c>
       <c r="F333" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G333" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -13100,9 +14098,12 @@
         <v>0</v>
       </c>
       <c r="K333" t="n">
+        <v>0</v>
+      </c>
+      <c r="L333" t="n">
         <v>4</v>
       </c>
-      <c r="L333" t="n">
+      <c r="M333" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13123,10 +14124,10 @@
         <v>3</v>
       </c>
       <c r="F334" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G334" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -13138,9 +14139,12 @@
         <v>0</v>
       </c>
       <c r="K334" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L334" t="n">
+        <v>1</v>
+      </c>
+      <c r="M334" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13176,9 +14180,12 @@
         <v>0</v>
       </c>
       <c r="K335" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L335" t="n">
+        <v>2</v>
+      </c>
+      <c r="M335" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13199,7 +14206,7 @@
         <v>3</v>
       </c>
       <c r="F336" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G336" t="n">
         <v>0</v>
@@ -13211,12 +14218,15 @@
         <v>0</v>
       </c>
       <c r="J336" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K336" t="n">
+        <v>1</v>
+      </c>
+      <c r="L336" t="n">
         <v>4</v>
       </c>
-      <c r="L336" t="n">
+      <c r="M336" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13237,10 +14247,10 @@
         <v>9</v>
       </c>
       <c r="F337" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G337" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H337" t="n">
         <v>0</v>
@@ -13252,9 +14262,12 @@
         <v>0</v>
       </c>
       <c r="K337" t="n">
+        <v>0</v>
+      </c>
+      <c r="L337" t="n">
         <v>8</v>
       </c>
-      <c r="L337" t="n">
+      <c r="M337" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13290,9 +14303,12 @@
         <v>0</v>
       </c>
       <c r="K338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L338" t="n">
+        <v>1</v>
+      </c>
+      <c r="M338" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13331,6 +14347,9 @@
         <v>0</v>
       </c>
       <c r="L339" t="n">
+        <v>0</v>
+      </c>
+      <c r="M339" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13366,9 +14385,12 @@
         <v>0</v>
       </c>
       <c r="K340" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L340" t="n">
+        <v>3</v>
+      </c>
+      <c r="M340" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13407,6 +14429,9 @@
         <v>0</v>
       </c>
       <c r="L341" t="n">
+        <v>0</v>
+      </c>
+      <c r="M341" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13427,7 +14452,7 @@
         <v>4</v>
       </c>
       <c r="F342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G342" t="n">
         <v>0</v>
@@ -13442,9 +14467,12 @@
         <v>0</v>
       </c>
       <c r="K342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L342" t="n">
+        <v>1</v>
+      </c>
+      <c r="M342" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13465,10 +14493,10 @@
         <v>3</v>
       </c>
       <c r="F343" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G343" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H343" t="n">
         <v>0</v>
@@ -13483,6 +14511,9 @@
         <v>0</v>
       </c>
       <c r="L343" t="n">
+        <v>0</v>
+      </c>
+      <c r="M343" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13503,7 +14534,7 @@
         <v>3</v>
       </c>
       <c r="F344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G344" t="n">
         <v>0</v>
@@ -13518,9 +14549,12 @@
         <v>0</v>
       </c>
       <c r="K344" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L344" t="n">
+        <v>2</v>
+      </c>
+      <c r="M344" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13544,7 +14578,7 @@
         <v>1</v>
       </c>
       <c r="G345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -13556,9 +14590,12 @@
         <v>0</v>
       </c>
       <c r="K345" t="n">
+        <v>0</v>
+      </c>
+      <c r="L345" t="n">
         <v>6</v>
       </c>
-      <c r="L345" t="n">
+      <c r="M345" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13579,7 +14616,7 @@
         <v>13</v>
       </c>
       <c r="F346" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G346" t="n">
         <v>0</v>
@@ -13594,9 +14631,12 @@
         <v>0</v>
       </c>
       <c r="K346" t="n">
+        <v>0</v>
+      </c>
+      <c r="L346" t="n">
         <v>6</v>
       </c>
-      <c r="L346" t="n">
+      <c r="M346" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13617,10 +14657,10 @@
         <v>4</v>
       </c>
       <c r="F347" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G347" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -13632,9 +14672,12 @@
         <v>0</v>
       </c>
       <c r="K347" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L347" t="n">
+        <v>2</v>
+      </c>
+      <c r="M347" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13655,24 +14698,27 @@
         <v>8</v>
       </c>
       <c r="F348" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G348" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H348" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J348" t="n">
         <v>0</v>
       </c>
       <c r="K348" t="n">
+        <v>0</v>
+      </c>
+      <c r="L348" t="n">
         <v>4</v>
       </c>
-      <c r="L348" t="n">
+      <c r="M348" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13708,9 +14754,12 @@
         <v>0</v>
       </c>
       <c r="K349" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L349" t="n">
+        <v>2</v>
+      </c>
+      <c r="M349" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13731,7 +14780,7 @@
         <v>2</v>
       </c>
       <c r="F350" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G350" t="n">
         <v>0</v>
@@ -13746,9 +14795,12 @@
         <v>0</v>
       </c>
       <c r="K350" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L350" t="n">
+        <v>1</v>
+      </c>
+      <c r="M350" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13769,7 +14821,7 @@
         <v>1</v>
       </c>
       <c r="F351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G351" t="n">
         <v>0</v>
@@ -13784,9 +14836,12 @@
         <v>0</v>
       </c>
       <c r="K351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L351" t="n">
+        <v>1</v>
+      </c>
+      <c r="M351" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13822,9 +14877,12 @@
         <v>0</v>
       </c>
       <c r="K352" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L352" t="n">
+        <v>1</v>
+      </c>
+      <c r="M352" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13845,7 +14903,7 @@
         <v>4</v>
       </c>
       <c r="F353" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G353" t="n">
         <v>0</v>
@@ -13860,9 +14918,12 @@
         <v>0</v>
       </c>
       <c r="K353" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L353" t="n">
+        <v>1</v>
+      </c>
+      <c r="M353" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13883,24 +14944,27 @@
         <v>10</v>
       </c>
       <c r="F354" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G354" t="n">
         <v>0</v>
       </c>
       <c r="H354" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I354" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J354" t="n">
         <v>0</v>
       </c>
       <c r="K354" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L354" t="n">
+        <v>1</v>
+      </c>
+      <c r="M354" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13933,12 +14997,15 @@
         <v>0</v>
       </c>
       <c r="J355" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K355" t="n">
         <v>1</v>
       </c>
       <c r="L355" t="n">
+        <v>1</v>
+      </c>
+      <c r="M355" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13959,24 +15026,27 @@
         <v>7</v>
       </c>
       <c r="F356" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G356" t="n">
         <v>0</v>
       </c>
       <c r="H356" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J356" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L356" t="n">
+        <v>0</v>
+      </c>
+      <c r="M356" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13997,7 +15067,7 @@
         <v>5</v>
       </c>
       <c r="F357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G357" t="n">
         <v>0</v>
@@ -14009,12 +15079,15 @@
         <v>0</v>
       </c>
       <c r="J357" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L357" t="n">
+        <v>0</v>
+      </c>
+      <c r="M357" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14035,24 +15108,27 @@
         <v>20</v>
       </c>
       <c r="F358" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G358" t="n">
         <v>0</v>
       </c>
       <c r="H358" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I358" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J358" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K358" t="n">
+        <v>1</v>
+      </c>
+      <c r="L358" t="n">
         <v>8</v>
       </c>
-      <c r="L358" t="n">
+      <c r="M358" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14073,24 +15149,27 @@
         <v>16</v>
       </c>
       <c r="F359" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G359" t="n">
         <v>0</v>
       </c>
       <c r="H359" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I359" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J359" t="n">
         <v>0</v>
       </c>
       <c r="K359" t="n">
+        <v>0</v>
+      </c>
+      <c r="L359" t="n">
         <v>8</v>
       </c>
-      <c r="L359" t="n">
+      <c r="M359" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14126,9 +15205,12 @@
         <v>0</v>
       </c>
       <c r="K360" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L360" t="n">
+        <v>3</v>
+      </c>
+      <c r="M360" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14167,6 +15249,9 @@
         <v>0</v>
       </c>
       <c r="L361" t="n">
+        <v>0</v>
+      </c>
+      <c r="M361" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14205,6 +15290,9 @@
         <v>0</v>
       </c>
       <c r="L362" t="n">
+        <v>0</v>
+      </c>
+      <c r="M362" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14225,10 +15313,10 @@
         <v>5</v>
       </c>
       <c r="F363" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G363" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -14240,9 +15328,12 @@
         <v>0</v>
       </c>
       <c r="K363" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L363" t="n">
+        <v>3</v>
+      </c>
+      <c r="M363" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14263,7 +15354,7 @@
         <v>13</v>
       </c>
       <c r="F364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G364" t="n">
         <v>0</v>
@@ -14275,12 +15366,15 @@
         <v>0</v>
       </c>
       <c r="J364" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K364" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L364" t="n">
+        <v>7</v>
+      </c>
+      <c r="M364" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14301,24 +15395,27 @@
         <v>20</v>
       </c>
       <c r="F365" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G365" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H365" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I365" t="n">
         <v>0</v>
       </c>
       <c r="J365" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K365" t="n">
+        <v>2</v>
+      </c>
+      <c r="L365" t="n">
         <v>6</v>
       </c>
-      <c r="L365" t="n">
+      <c r="M365" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14339,7 +15436,7 @@
         <v>5</v>
       </c>
       <c r="F366" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G366" t="n">
         <v>0</v>
@@ -14354,9 +15451,12 @@
         <v>0</v>
       </c>
       <c r="K366" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L366" t="n">
+        <v>1</v>
+      </c>
+      <c r="M366" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14377,24 +15477,27 @@
         <v>6</v>
       </c>
       <c r="F367" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G367" t="n">
         <v>0</v>
       </c>
       <c r="H367" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I367" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J367" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K367" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L367" t="n">
+        <v>0</v>
+      </c>
+      <c r="M367" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14415,7 +15518,7 @@
         <v>3</v>
       </c>
       <c r="F368" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G368" t="n">
         <v>0</v>
@@ -14430,9 +15533,12 @@
         <v>0</v>
       </c>
       <c r="K368" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L368" t="n">
+        <v>2</v>
+      </c>
+      <c r="M368" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14453,7 +15559,7 @@
         <v>30</v>
       </c>
       <c r="F369" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G369" t="n">
         <v>0</v>
@@ -14465,12 +15571,15 @@
         <v>0</v>
       </c>
       <c r="J369" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K369" t="n">
+        <v>3</v>
+      </c>
+      <c r="L369" t="n">
         <v>14</v>
       </c>
-      <c r="L369" t="n">
+      <c r="M369" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14491,7 +15600,7 @@
         <v>13</v>
       </c>
       <c r="F370" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G370" t="n">
         <v>0</v>
@@ -14503,12 +15612,15 @@
         <v>0</v>
       </c>
       <c r="J370" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K370" t="n">
+        <v>1</v>
+      </c>
+      <c r="L370" t="n">
         <v>6</v>
       </c>
-      <c r="L370" t="n">
+      <c r="M370" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14532,7 +15644,7 @@
         <v>1</v>
       </c>
       <c r="G371" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -14544,9 +15656,12 @@
         <v>0</v>
       </c>
       <c r="K371" t="n">
+        <v>0</v>
+      </c>
+      <c r="L371" t="n">
         <v>5</v>
       </c>
-      <c r="L371" t="n">
+      <c r="M371" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14567,24 +15682,27 @@
         <v>7</v>
       </c>
       <c r="F372" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G372" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H372" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I372" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J372" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K372" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L372" t="n">
+        <v>1</v>
+      </c>
+      <c r="M372" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14605,7 +15723,7 @@
         <v>2</v>
       </c>
       <c r="F373" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G373" t="n">
         <v>0</v>
@@ -14617,12 +15735,15 @@
         <v>0</v>
       </c>
       <c r="J373" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K373" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L373" t="n">
+        <v>0</v>
+      </c>
+      <c r="M373" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14643,7 +15764,7 @@
         <v>1</v>
       </c>
       <c r="F374" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G374" t="n">
         <v>0</v>
@@ -14658,9 +15779,12 @@
         <v>0</v>
       </c>
       <c r="K374" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L374" t="n">
+        <v>1</v>
+      </c>
+      <c r="M374" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14681,7 +15805,7 @@
         <v>2</v>
       </c>
       <c r="F375" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G375" t="n">
         <v>0</v>
@@ -14693,12 +15817,15 @@
         <v>0</v>
       </c>
       <c r="J375" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K375" t="n">
         <v>1</v>
       </c>
       <c r="L375" t="n">
+        <v>1</v>
+      </c>
+      <c r="M375" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14719,24 +15846,27 @@
         <v>15</v>
       </c>
       <c r="F376" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G376" t="n">
         <v>0</v>
       </c>
       <c r="H376" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I376" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J376" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K376" t="n">
+        <v>1</v>
+      </c>
+      <c r="L376" t="n">
         <v>6</v>
       </c>
-      <c r="L376" t="n">
+      <c r="M376" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14757,7 +15887,7 @@
         <v>6</v>
       </c>
       <c r="F377" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G377" t="n">
         <v>0</v>
@@ -14772,9 +15902,12 @@
         <v>0</v>
       </c>
       <c r="K377" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L377" t="n">
+        <v>3</v>
+      </c>
+      <c r="M377" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14795,7 +15928,7 @@
         <v>4</v>
       </c>
       <c r="F378" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G378" t="n">
         <v>0</v>
@@ -14807,12 +15940,15 @@
         <v>0</v>
       </c>
       <c r="J378" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K378" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L378" t="n">
+        <v>0</v>
+      </c>
+      <c r="M378" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14833,7 +15969,7 @@
         <v>4</v>
       </c>
       <c r="F379" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G379" t="n">
         <v>0</v>
@@ -14848,9 +15984,12 @@
         <v>0</v>
       </c>
       <c r="K379" t="n">
+        <v>0</v>
+      </c>
+      <c r="L379" t="n">
         <v>6</v>
       </c>
-      <c r="L379" t="n">
+      <c r="M379" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14871,7 +16010,7 @@
         <v>1</v>
       </c>
       <c r="F380" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G380" t="n">
         <v>0</v>
@@ -14886,9 +16025,12 @@
         <v>0</v>
       </c>
       <c r="K380" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L380" t="n">
+        <v>2</v>
+      </c>
+      <c r="M380" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14909,7 +16051,7 @@
         <v>0</v>
       </c>
       <c r="F381" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G381" t="n">
         <v>0</v>
@@ -14924,9 +16066,12 @@
         <v>0</v>
       </c>
       <c r="K381" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L381" t="n">
+        <v>1</v>
+      </c>
+      <c r="M381" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14947,10 +16092,10 @@
         <v>2</v>
       </c>
       <c r="F382" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G382" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -14962,9 +16107,12 @@
         <v>0</v>
       </c>
       <c r="K382" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L382" t="n">
+        <v>1</v>
+      </c>
+      <c r="M382" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14985,10 +16133,10 @@
         <v>10</v>
       </c>
       <c r="F383" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G383" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H383" t="n">
         <v>0</v>
@@ -15000,9 +16148,12 @@
         <v>0</v>
       </c>
       <c r="K383" t="n">
+        <v>0</v>
+      </c>
+      <c r="L383" t="n">
         <v>10</v>
       </c>
-      <c r="L383" t="n">
+      <c r="M383" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15023,24 +16174,27 @@
         <v>10</v>
       </c>
       <c r="F384" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G384" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H384" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I384" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J384" t="n">
         <v>0</v>
       </c>
       <c r="K384" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L384" t="n">
+        <v>3</v>
+      </c>
+      <c r="M384" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15076,9 +16230,12 @@
         <v>0</v>
       </c>
       <c r="K385" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L385" t="n">
+        <v>1</v>
+      </c>
+      <c r="M385" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15099,7 +16256,7 @@
         <v>4</v>
       </c>
       <c r="F386" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G386" t="n">
         <v>0</v>
@@ -15111,12 +16268,15 @@
         <v>0</v>
       </c>
       <c r="J386" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K386" t="n">
+        <v>1</v>
+      </c>
+      <c r="L386" t="n">
         <v>4</v>
       </c>
-      <c r="L386" t="n">
+      <c r="M386" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15137,7 +16297,7 @@
         <v>5</v>
       </c>
       <c r="F387" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G387" t="n">
         <v>0</v>
@@ -15152,9 +16312,12 @@
         <v>0</v>
       </c>
       <c r="K387" t="n">
+        <v>0</v>
+      </c>
+      <c r="L387" t="n">
         <v>6</v>
       </c>
-      <c r="L387" t="n">
+      <c r="M387" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15178,10 +16341,10 @@
         <v>2</v>
       </c>
       <c r="G388" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H388" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I388" t="n">
         <v>0</v>
@@ -15190,9 +16353,12 @@
         <v>0</v>
       </c>
       <c r="K388" t="n">
+        <v>0</v>
+      </c>
+      <c r="L388" t="n">
         <v>4</v>
       </c>
-      <c r="L388" t="n">
+      <c r="M388" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15213,7 +16379,7 @@
         <v>3</v>
       </c>
       <c r="F389" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G389" t="n">
         <v>0</v>
@@ -15228,9 +16394,12 @@
         <v>0</v>
       </c>
       <c r="K389" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L389" t="n">
+        <v>3</v>
+      </c>
+      <c r="M389" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15251,13 +16420,13 @@
         <v>1</v>
       </c>
       <c r="F390" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G390" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H390" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I390" t="n">
         <v>0</v>
@@ -15269,6 +16438,9 @@
         <v>0</v>
       </c>
       <c r="L390" t="n">
+        <v>0</v>
+      </c>
+      <c r="M390" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15289,24 +16461,27 @@
         <v>3</v>
       </c>
       <c r="F391" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G391" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H391" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I391" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J391" t="n">
         <v>0</v>
       </c>
       <c r="K391" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L391" t="n">
+        <v>1</v>
+      </c>
+      <c r="M391" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15327,7 +16502,7 @@
         <v>4</v>
       </c>
       <c r="F392" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G392" t="n">
         <v>0</v>
@@ -15342,9 +16517,12 @@
         <v>0</v>
       </c>
       <c r="K392" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L392" t="n">
+        <v>3</v>
+      </c>
+      <c r="M392" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15365,7 +16543,7 @@
         <v>5</v>
       </c>
       <c r="F393" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G393" t="n">
         <v>0</v>
@@ -15380,9 +16558,12 @@
         <v>0</v>
       </c>
       <c r="K393" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L393" t="n">
+        <v>3</v>
+      </c>
+      <c r="M393" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15403,7 +16584,7 @@
         <v>5</v>
       </c>
       <c r="F394" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G394" t="n">
         <v>0</v>
@@ -15418,9 +16599,12 @@
         <v>0</v>
       </c>
       <c r="K394" t="n">
+        <v>0</v>
+      </c>
+      <c r="L394" t="n">
         <v>4</v>
       </c>
-      <c r="L394" t="n">
+      <c r="M394" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15441,7 +16625,7 @@
         <v>10</v>
       </c>
       <c r="F395" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G395" t="n">
         <v>0</v>
@@ -15456,9 +16640,12 @@
         <v>0</v>
       </c>
       <c r="K395" t="n">
+        <v>0</v>
+      </c>
+      <c r="L395" t="n">
         <v>4</v>
       </c>
-      <c r="L395" t="n">
+      <c r="M395" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15479,24 +16666,27 @@
         <v>1</v>
       </c>
       <c r="F396" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G396" t="n">
         <v>0</v>
       </c>
       <c r="H396" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I396" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J396" t="n">
         <v>0</v>
       </c>
       <c r="K396" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L396" t="n">
+        <v>1</v>
+      </c>
+      <c r="M396" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15532,9 +16722,12 @@
         <v>0</v>
       </c>
       <c r="K397" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L397" t="n">
+        <v>3</v>
+      </c>
+      <c r="M397" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15555,24 +16748,27 @@
         <v>7</v>
       </c>
       <c r="F398" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G398" t="n">
         <v>0</v>
       </c>
       <c r="H398" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I398" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J398" t="n">
         <v>0</v>
       </c>
       <c r="K398" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L398" t="n">
+        <v>1</v>
+      </c>
+      <c r="M398" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15611,6 +16807,9 @@
         <v>0</v>
       </c>
       <c r="L399" t="n">
+        <v>0</v>
+      </c>
+      <c r="M399" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15631,7 +16830,7 @@
         <v>5</v>
       </c>
       <c r="F400" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G400" t="n">
         <v>0</v>
@@ -15646,9 +16845,12 @@
         <v>0</v>
       </c>
       <c r="K400" t="n">
+        <v>0</v>
+      </c>
+      <c r="L400" t="n">
         <v>4</v>
       </c>
-      <c r="L400" t="n">
+      <c r="M400" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15669,10 +16871,10 @@
         <v>9</v>
       </c>
       <c r="F401" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G401" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H401" t="n">
         <v>0</v>
@@ -15684,9 +16886,12 @@
         <v>0</v>
       </c>
       <c r="K401" t="n">
+        <v>0</v>
+      </c>
+      <c r="L401" t="n">
         <v>4</v>
       </c>
-      <c r="L401" t="n">
+      <c r="M401" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15707,7 +16912,7 @@
         <v>20</v>
       </c>
       <c r="F402" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G402" t="n">
         <v>1</v>
@@ -15716,15 +16921,18 @@
         <v>1</v>
       </c>
       <c r="I402" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J402" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K402" t="n">
+        <v>1</v>
+      </c>
+      <c r="L402" t="n">
         <v>16</v>
       </c>
-      <c r="L402" t="n">
+      <c r="M402" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15751,18 +16959,21 @@
         <v>1</v>
       </c>
       <c r="H403" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I403" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J403" t="n">
         <v>0</v>
       </c>
       <c r="K403" t="n">
+        <v>0</v>
+      </c>
+      <c r="L403" t="n">
         <v>14</v>
       </c>
-      <c r="L403" t="n">
+      <c r="M403" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15801,6 +17012,9 @@
         <v>0</v>
       </c>
       <c r="L404" t="n">
+        <v>0</v>
+      </c>
+      <c r="M404" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15839,6 +17053,9 @@
         <v>0</v>
       </c>
       <c r="L405" t="n">
+        <v>0</v>
+      </c>
+      <c r="M405" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15859,7 +17076,7 @@
         <v>8</v>
       </c>
       <c r="F406" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G406" t="n">
         <v>0</v>
@@ -15871,12 +17088,15 @@
         <v>0</v>
       </c>
       <c r="J406" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K406" t="n">
+        <v>1</v>
+      </c>
+      <c r="L406" t="n">
         <v>8</v>
       </c>
-      <c r="L406" t="n">
+      <c r="M406" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15897,7 +17117,7 @@
         <v>8</v>
       </c>
       <c r="F407" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G407" t="n">
         <v>0</v>
@@ -15909,12 +17129,15 @@
         <v>0</v>
       </c>
       <c r="J407" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K407" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L407" t="n">
+        <v>7</v>
+      </c>
+      <c r="M407" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15953,6 +17176,9 @@
         <v>0</v>
       </c>
       <c r="L408" t="n">
+        <v>0</v>
+      </c>
+      <c r="M408" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15973,10 +17199,10 @@
         <v>8</v>
       </c>
       <c r="F409" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G409" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H409" t="n">
         <v>0</v>
@@ -15988,9 +17214,12 @@
         <v>0</v>
       </c>
       <c r="K409" t="n">
+        <v>0</v>
+      </c>
+      <c r="L409" t="n">
         <v>6</v>
       </c>
-      <c r="L409" t="n">
+      <c r="M409" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -16011,11 +17240,11 @@
         <v>27</v>
       </c>
       <c r="F410" t="n">
+        <v>8</v>
+      </c>
+      <c r="G410" t="n">
         <v>4</v>
       </c>
-      <c r="G410" t="n">
-        <v>0</v>
-      </c>
       <c r="H410" t="n">
         <v>0</v>
       </c>
@@ -16026,9 +17255,12 @@
         <v>0</v>
       </c>
       <c r="K410" t="n">
+        <v>0</v>
+      </c>
+      <c r="L410" t="n">
         <v>21</v>
       </c>
-      <c r="L410" t="n">
+      <c r="M410" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -16049,24 +17281,27 @@
         <v>3</v>
       </c>
       <c r="F411" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G411" t="n">
         <v>0</v>
       </c>
       <c r="H411" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I411" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J411" t="n">
         <v>0</v>
       </c>
       <c r="K411" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L411" t="n">
+        <v>3</v>
+      </c>
+      <c r="M411" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -16087,7 +17322,7 @@
         <v>3</v>
       </c>
       <c r="F412" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G412" t="n">
         <v>0</v>
@@ -16102,9 +17337,12 @@
         <v>0</v>
       </c>
       <c r="K412" t="n">
+        <v>0</v>
+      </c>
+      <c r="L412" t="n">
         <v>5</v>
       </c>
-      <c r="L412" t="n">
+      <c r="M412" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -16125,7 +17363,7 @@
         <v>7</v>
       </c>
       <c r="F413" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G413" t="n">
         <v>0</v>
@@ -16137,12 +17375,15 @@
         <v>0</v>
       </c>
       <c r="J413" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K413" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L413" t="n">
+        <v>7</v>
+      </c>
+      <c r="M413" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -16178,9 +17419,12 @@
         <v>0</v>
       </c>
       <c r="K414" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L414" t="n">
+        <v>2</v>
+      </c>
+      <c r="M414" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -16201,7 +17445,7 @@
         <v>4</v>
       </c>
       <c r="F415" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G415" t="n">
         <v>0</v>
@@ -16213,12 +17457,15 @@
         <v>0</v>
       </c>
       <c r="J415" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K415" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L415" t="n">
+        <v>0</v>
+      </c>
+      <c r="M415" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -16239,10 +17486,10 @@
         <v>2</v>
       </c>
       <c r="F416" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G416" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H416" t="n">
         <v>0</v>
@@ -16251,12 +17498,15 @@
         <v>0</v>
       </c>
       <c r="J416" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K416" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L416" t="n">
+        <v>0</v>
+      </c>
+      <c r="M416" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -16277,24 +17527,27 @@
         <v>4</v>
       </c>
       <c r="F417" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G417" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H417" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I417" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J417" t="n">
         <v>0</v>
       </c>
       <c r="K417" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L417" t="n">
+        <v>1</v>
+      </c>
+      <c r="M417" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -16315,24 +17568,27 @@
         <v>14</v>
       </c>
       <c r="F418" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G418" t="n">
         <v>0</v>
       </c>
       <c r="H418" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I418" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J418" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K418" t="n">
+        <v>1</v>
+      </c>
+      <c r="L418" t="n">
         <v>14</v>
       </c>
-      <c r="L418" t="n">
+      <c r="M418" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -16353,7 +17609,7 @@
         <v>7</v>
       </c>
       <c r="F419" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G419" t="n">
         <v>0</v>
@@ -16368,9 +17624,12 @@
         <v>0</v>
       </c>
       <c r="K419" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L419" t="n">
+        <v>1</v>
+      </c>
+      <c r="M419" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -16391,10 +17650,10 @@
         <v>17</v>
       </c>
       <c r="F420" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G420" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -16406,9 +17665,12 @@
         <v>0</v>
       </c>
       <c r="K420" t="n">
+        <v>0</v>
+      </c>
+      <c r="L420" t="n">
         <v>10</v>
       </c>
-      <c r="L420" t="n">
+      <c r="M420" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -16447,6 +17709,9 @@
         <v>0</v>
       </c>
       <c r="L421" t="n">
+        <v>0</v>
+      </c>
+      <c r="M421" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -16467,7 +17732,7 @@
         <v>4</v>
       </c>
       <c r="F422" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G422" t="n">
         <v>0</v>
@@ -16479,12 +17744,15 @@
         <v>0</v>
       </c>
       <c r="J422" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K422" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L422" t="n">
+        <v>1</v>
+      </c>
+      <c r="M422" t="n">
         <v>2015</v>
       </c>
     </row>

--- a/Excel Files IPEDS/Trimmed/c2015_trimmed_file.xlsx
+++ b/Excel Files IPEDS/Trimmed/c2015_trimmed_file.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M422"/>
+  <dimension ref="A1:O422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,6 +491,16 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>C2MORT</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>CNRALT</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Year</t>
         </is>
       </c>
@@ -533,6 +543,12 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O2" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -574,6 +590,12 @@
         <v>1</v>
       </c>
       <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O3" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -615,6 +637,12 @@
         <v>1</v>
       </c>
       <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -656,6 +684,12 @@
         <v>4</v>
       </c>
       <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O5" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -697,6 +731,12 @@
         <v>2</v>
       </c>
       <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2</v>
+      </c>
+      <c r="O6" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -738,6 +778,12 @@
         <v>3</v>
       </c>
       <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -779,6 +825,12 @@
         <v>1</v>
       </c>
       <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3</v>
+      </c>
+      <c r="O8" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -820,6 +872,12 @@
         <v>9</v>
       </c>
       <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5</v>
+      </c>
+      <c r="O9" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -861,6 +919,12 @@
         <v>1</v>
       </c>
       <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -902,6 +966,12 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -943,6 +1013,12 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -984,6 +1060,12 @@
         <v>4</v>
       </c>
       <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1025,6 +1107,12 @@
         <v>8</v>
       </c>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>8</v>
+      </c>
+      <c r="O14" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1066,6 +1154,12 @@
         <v>3</v>
       </c>
       <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1107,6 +1201,12 @@
         <v>6</v>
       </c>
       <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2</v>
+      </c>
+      <c r="O16" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1148,6 +1248,12 @@
         <v>5</v>
       </c>
       <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1189,6 +1295,12 @@
         <v>6</v>
       </c>
       <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>5</v>
+      </c>
+      <c r="O18" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1230,6 +1342,12 @@
         <v>2</v>
       </c>
       <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1271,6 +1389,12 @@
         <v>6</v>
       </c>
       <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>5</v>
+      </c>
+      <c r="O20" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1312,6 +1436,12 @@
         <v>7</v>
       </c>
       <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>9</v>
+      </c>
+      <c r="O21" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1353,6 +1483,12 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1394,6 +1530,12 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1435,6 +1577,12 @@
         <v>2</v>
       </c>
       <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1476,6 +1624,12 @@
         <v>2</v>
       </c>
       <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1517,6 +1671,12 @@
         <v>3</v>
       </c>
       <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1558,6 +1718,12 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1599,6 +1765,12 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1640,6 +1812,12 @@
         <v>19</v>
       </c>
       <c r="M29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>5</v>
+      </c>
+      <c r="O29" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1681,6 +1859,12 @@
         <v>11</v>
       </c>
       <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>12</v>
+      </c>
+      <c r="O30" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1722,6 +1906,12 @@
         <v>6</v>
       </c>
       <c r="M31" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2</v>
+      </c>
+      <c r="O31" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1763,6 +1953,12 @@
         <v>16</v>
       </c>
       <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>4</v>
+      </c>
+      <c r="O32" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1804,6 +2000,12 @@
         <v>7</v>
       </c>
       <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1845,6 +2047,12 @@
         <v>3</v>
       </c>
       <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2</v>
+      </c>
+      <c r="O34" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1886,6 +2094,12 @@
         <v>21</v>
       </c>
       <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2</v>
+      </c>
+      <c r="O35" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1927,6 +2141,12 @@
         <v>9</v>
       </c>
       <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>5</v>
+      </c>
+      <c r="O36" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -1968,6 +2188,12 @@
         <v>4</v>
       </c>
       <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>9</v>
+      </c>
+      <c r="O37" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2009,6 +2235,12 @@
         <v>3</v>
       </c>
       <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>9</v>
+      </c>
+      <c r="O38" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2050,6 +2282,12 @@
         <v>8</v>
       </c>
       <c r="M39" t="n">
+        <v>1</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2091,6 +2329,12 @@
         <v>14</v>
       </c>
       <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>7</v>
+      </c>
+      <c r="O40" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2132,6 +2376,12 @@
         <v>16</v>
       </c>
       <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>5</v>
+      </c>
+      <c r="O41" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2173,6 +2423,12 @@
         <v>6</v>
       </c>
       <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>3</v>
+      </c>
+      <c r="O42" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2214,6 +2470,12 @@
         <v>9</v>
       </c>
       <c r="M43" t="n">
+        <v>1</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2</v>
+      </c>
+      <c r="O43" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2255,6 +2517,12 @@
         <v>4</v>
       </c>
       <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2296,6 +2564,12 @@
         <v>2</v>
       </c>
       <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2337,6 +2611,12 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2378,6 +2658,12 @@
         <v>4</v>
       </c>
       <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2419,6 +2705,12 @@
         <v>3</v>
       </c>
       <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2460,6 +2752,12 @@
         <v>3</v>
       </c>
       <c r="M49" t="n">
+        <v>2</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2501,6 +2799,12 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>5</v>
+      </c>
+      <c r="O50" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2542,6 +2846,12 @@
         <v>3</v>
       </c>
       <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>5</v>
+      </c>
+      <c r="O51" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2583,6 +2893,12 @@
         <v>15</v>
       </c>
       <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>6</v>
+      </c>
+      <c r="O52" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2624,6 +2940,12 @@
         <v>13</v>
       </c>
       <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>10</v>
+      </c>
+      <c r="O53" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2665,6 +2987,12 @@
         <v>6</v>
       </c>
       <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2706,6 +3034,12 @@
         <v>7</v>
       </c>
       <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>2</v>
+      </c>
+      <c r="O55" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2747,6 +3081,12 @@
         <v>3</v>
       </c>
       <c r="M56" t="n">
+        <v>1</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2788,6 +3128,12 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2829,6 +3175,12 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2870,6 +3222,12 @@
         <v>7</v>
       </c>
       <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>5</v>
+      </c>
+      <c r="O59" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2911,6 +3269,12 @@
         <v>4</v>
       </c>
       <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>2</v>
+      </c>
+      <c r="O60" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2952,6 +3316,12 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -2993,6 +3363,12 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3034,6 +3410,12 @@
         <v>9</v>
       </c>
       <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>12</v>
+      </c>
+      <c r="O63" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3075,6 +3457,12 @@
         <v>4</v>
       </c>
       <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>4</v>
+      </c>
+      <c r="O64" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3116,6 +3504,12 @@
         <v>1</v>
       </c>
       <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3157,6 +3551,12 @@
         <v>1</v>
       </c>
       <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>2</v>
+      </c>
+      <c r="O66" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3198,6 +3598,12 @@
         <v>1</v>
       </c>
       <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
+        <v>5</v>
+      </c>
+      <c r="O67" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3239,6 +3645,12 @@
         <v>3</v>
       </c>
       <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="n">
+        <v>2</v>
+      </c>
+      <c r="O68" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3280,6 +3692,12 @@
         <v>1</v>
       </c>
       <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>2</v>
+      </c>
+      <c r="O69" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3321,6 +3739,12 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="n">
+        <v>1</v>
+      </c>
+      <c r="O70" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3362,6 +3786,12 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
+        <v>1</v>
+      </c>
+      <c r="O71" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3403,6 +3833,12 @@
         <v>1</v>
       </c>
       <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3444,6 +3880,12 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="n">
+        <v>4</v>
+      </c>
+      <c r="O73" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3485,6 +3927,12 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3526,6 +3974,12 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="n">
+        <v>1</v>
+      </c>
+      <c r="O75" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3567,6 +4021,12 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="n">
+        <v>4</v>
+      </c>
+      <c r="O76" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3608,6 +4068,12 @@
         <v>6</v>
       </c>
       <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="n">
+        <v>14</v>
+      </c>
+      <c r="O77" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3649,6 +4115,12 @@
         <v>0</v>
       </c>
       <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3690,6 +4162,12 @@
         <v>0</v>
       </c>
       <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3731,6 +4209,12 @@
         <v>0</v>
       </c>
       <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>3</v>
+      </c>
+      <c r="O80" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3772,6 +4256,12 @@
         <v>1</v>
       </c>
       <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3813,6 +4303,12 @@
         <v>2</v>
       </c>
       <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="n">
+        <v>1</v>
+      </c>
+      <c r="O82" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3854,6 +4350,12 @@
         <v>0</v>
       </c>
       <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="n">
+        <v>2</v>
+      </c>
+      <c r="O83" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3895,6 +4397,12 @@
         <v>0</v>
       </c>
       <c r="M84" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3936,6 +4444,12 @@
         <v>2</v>
       </c>
       <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="n">
+        <v>2</v>
+      </c>
+      <c r="O85" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -3977,6 +4491,12 @@
         <v>12</v>
       </c>
       <c r="M86" t="n">
+        <v>1</v>
+      </c>
+      <c r="N86" t="n">
+        <v>20</v>
+      </c>
+      <c r="O86" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4018,6 +4538,12 @@
         <v>9</v>
       </c>
       <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>6</v>
+      </c>
+      <c r="O87" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4059,6 +4585,12 @@
         <v>6</v>
       </c>
       <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>2</v>
+      </c>
+      <c r="O88" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4100,6 +4632,12 @@
         <v>7</v>
       </c>
       <c r="M89" t="n">
+        <v>1</v>
+      </c>
+      <c r="N89" t="n">
+        <v>9</v>
+      </c>
+      <c r="O89" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4141,6 +4679,12 @@
         <v>0</v>
       </c>
       <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>3</v>
+      </c>
+      <c r="O90" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4182,6 +4726,12 @@
         <v>7</v>
       </c>
       <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>3</v>
+      </c>
+      <c r="O91" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4223,6 +4773,12 @@
         <v>5</v>
       </c>
       <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="n">
+        <v>3</v>
+      </c>
+      <c r="O92" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4264,6 +4820,12 @@
         <v>0</v>
       </c>
       <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4305,6 +4867,12 @@
         <v>0</v>
       </c>
       <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="n">
+        <v>1</v>
+      </c>
+      <c r="O94" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4346,6 +4914,12 @@
         <v>1</v>
       </c>
       <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="n">
+        <v>3</v>
+      </c>
+      <c r="O95" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4387,6 +4961,12 @@
         <v>3</v>
       </c>
       <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="n">
+        <v>2</v>
+      </c>
+      <c r="O96" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4428,6 +5008,12 @@
         <v>4</v>
       </c>
       <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="n">
+        <v>9</v>
+      </c>
+      <c r="O97" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4469,6 +5055,12 @@
         <v>2</v>
       </c>
       <c r="M98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" t="n">
+        <v>4</v>
+      </c>
+      <c r="O98" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4510,6 +5102,12 @@
         <v>0</v>
       </c>
       <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="n">
+        <v>5</v>
+      </c>
+      <c r="O99" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4551,6 +5149,12 @@
         <v>2</v>
       </c>
       <c r="M100" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" t="n">
+        <v>2</v>
+      </c>
+      <c r="O100" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4592,6 +5196,12 @@
         <v>2</v>
       </c>
       <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="n">
+        <v>3</v>
+      </c>
+      <c r="O101" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4633,6 +5243,12 @@
         <v>1</v>
       </c>
       <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="n">
+        <v>1</v>
+      </c>
+      <c r="O102" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4674,6 +5290,12 @@
         <v>2</v>
       </c>
       <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4715,6 +5337,12 @@
         <v>3</v>
       </c>
       <c r="M104" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" t="n">
+        <v>2</v>
+      </c>
+      <c r="O104" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4756,6 +5384,12 @@
         <v>2</v>
       </c>
       <c r="M105" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" t="n">
+        <v>1</v>
+      </c>
+      <c r="O105" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4797,6 +5431,12 @@
         <v>0</v>
       </c>
       <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="n">
+        <v>2</v>
+      </c>
+      <c r="O106" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4838,6 +5478,12 @@
         <v>0</v>
       </c>
       <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="n">
+        <v>1</v>
+      </c>
+      <c r="O107" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4879,6 +5525,12 @@
         <v>0</v>
       </c>
       <c r="M108" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4920,6 +5572,12 @@
         <v>0</v>
       </c>
       <c r="M109" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -4961,6 +5619,12 @@
         <v>5</v>
       </c>
       <c r="M110" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" t="n">
+        <v>5</v>
+      </c>
+      <c r="O110" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5002,6 +5666,12 @@
         <v>10</v>
       </c>
       <c r="M111" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" t="n">
+        <v>8</v>
+      </c>
+      <c r="O111" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5043,6 +5713,12 @@
         <v>0</v>
       </c>
       <c r="M112" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5084,6 +5760,12 @@
         <v>1</v>
       </c>
       <c r="M113" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" t="n">
+        <v>6</v>
+      </c>
+      <c r="O113" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5125,6 +5807,12 @@
         <v>4</v>
       </c>
       <c r="M114" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" t="n">
+        <v>2</v>
+      </c>
+      <c r="O114" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5166,6 +5854,12 @@
         <v>6</v>
       </c>
       <c r="M115" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" t="n">
+        <v>8</v>
+      </c>
+      <c r="O115" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5207,6 +5901,12 @@
         <v>12</v>
       </c>
       <c r="M116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N116" t="n">
+        <v>13</v>
+      </c>
+      <c r="O116" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5248,6 +5948,12 @@
         <v>0</v>
       </c>
       <c r="M117" t="n">
+        <v>0</v>
+      </c>
+      <c r="N117" t="n">
+        <v>4</v>
+      </c>
+      <c r="O117" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5289,6 +5995,12 @@
         <v>3</v>
       </c>
       <c r="M118" t="n">
+        <v>2</v>
+      </c>
+      <c r="N118" t="n">
+        <v>2</v>
+      </c>
+      <c r="O118" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5330,6 +6042,12 @@
         <v>2</v>
       </c>
       <c r="M119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" t="n">
+        <v>2</v>
+      </c>
+      <c r="O119" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5371,6 +6089,12 @@
         <v>3</v>
       </c>
       <c r="M120" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" t="n">
+        <v>2</v>
+      </c>
+      <c r="O120" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5412,6 +6136,12 @@
         <v>3</v>
       </c>
       <c r="M121" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" t="n">
+        <v>4</v>
+      </c>
+      <c r="O121" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5453,6 +6183,12 @@
         <v>0</v>
       </c>
       <c r="M122" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" t="n">
+        <v>1</v>
+      </c>
+      <c r="O122" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5494,6 +6230,12 @@
         <v>2</v>
       </c>
       <c r="M123" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" t="n">
+        <v>15</v>
+      </c>
+      <c r="O123" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5535,6 +6277,12 @@
         <v>3</v>
       </c>
       <c r="M124" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" t="n">
+        <v>1</v>
+      </c>
+      <c r="O124" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5576,6 +6324,12 @@
         <v>0</v>
       </c>
       <c r="M125" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" t="n">
+        <v>3</v>
+      </c>
+      <c r="O125" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5617,6 +6371,12 @@
         <v>5</v>
       </c>
       <c r="M126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" t="n">
+        <v>7</v>
+      </c>
+      <c r="O126" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5658,6 +6418,12 @@
         <v>6</v>
       </c>
       <c r="M127" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" t="n">
+        <v>8</v>
+      </c>
+      <c r="O127" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5699,6 +6465,12 @@
         <v>10</v>
       </c>
       <c r="M128" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" t="n">
+        <v>5</v>
+      </c>
+      <c r="O128" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5740,6 +6512,12 @@
         <v>5</v>
       </c>
       <c r="M129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" t="n">
+        <v>4</v>
+      </c>
+      <c r="O129" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5781,6 +6559,12 @@
         <v>0</v>
       </c>
       <c r="M130" t="n">
+        <v>0</v>
+      </c>
+      <c r="N130" t="n">
+        <v>1</v>
+      </c>
+      <c r="O130" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5822,6 +6606,12 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" t="n">
+        <v>2</v>
+      </c>
+      <c r="O131" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5863,6 +6653,12 @@
         <v>5</v>
       </c>
       <c r="M132" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" t="n">
+        <v>6</v>
+      </c>
+      <c r="O132" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5904,6 +6700,12 @@
         <v>3</v>
       </c>
       <c r="M133" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" t="n">
+        <v>1</v>
+      </c>
+      <c r="O133" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5945,6 +6747,12 @@
         <v>3</v>
       </c>
       <c r="M134" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" t="n">
+        <v>2</v>
+      </c>
+      <c r="O134" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -5986,6 +6794,12 @@
         <v>2</v>
       </c>
       <c r="M135" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" t="n">
+        <v>5</v>
+      </c>
+      <c r="O135" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6027,6 +6841,12 @@
         <v>1</v>
       </c>
       <c r="M136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N136" t="n">
+        <v>6</v>
+      </c>
+      <c r="O136" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6068,6 +6888,12 @@
         <v>0</v>
       </c>
       <c r="M137" t="n">
+        <v>1</v>
+      </c>
+      <c r="N137" t="n">
+        <v>2</v>
+      </c>
+      <c r="O137" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6109,6 +6935,12 @@
         <v>4</v>
       </c>
       <c r="M138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" t="n">
+        <v>3</v>
+      </c>
+      <c r="O138" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6150,6 +6982,12 @@
         <v>4</v>
       </c>
       <c r="M139" t="n">
+        <v>0</v>
+      </c>
+      <c r="N139" t="n">
+        <v>6</v>
+      </c>
+      <c r="O139" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6191,6 +7029,12 @@
         <v>6</v>
       </c>
       <c r="M140" t="n">
+        <v>1</v>
+      </c>
+      <c r="N140" t="n">
+        <v>3</v>
+      </c>
+      <c r="O140" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6232,6 +7076,12 @@
         <v>1</v>
       </c>
       <c r="M141" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" t="n">
+        <v>2</v>
+      </c>
+      <c r="O141" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6273,6 +7123,12 @@
         <v>0</v>
       </c>
       <c r="M142" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" t="n">
+        <v>2</v>
+      </c>
+      <c r="O142" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6314,6 +7170,12 @@
         <v>3</v>
       </c>
       <c r="M143" t="n">
+        <v>0</v>
+      </c>
+      <c r="N143" t="n">
+        <v>5</v>
+      </c>
+      <c r="O143" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6355,6 +7217,12 @@
         <v>2</v>
       </c>
       <c r="M144" t="n">
+        <v>0</v>
+      </c>
+      <c r="N144" t="n">
+        <v>1</v>
+      </c>
+      <c r="O144" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6396,6 +7264,12 @@
         <v>3</v>
       </c>
       <c r="M145" t="n">
+        <v>0</v>
+      </c>
+      <c r="N145" t="n">
+        <v>1</v>
+      </c>
+      <c r="O145" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6437,6 +7311,12 @@
         <v>0</v>
       </c>
       <c r="M146" t="n">
+        <v>0</v>
+      </c>
+      <c r="N146" t="n">
+        <v>0</v>
+      </c>
+      <c r="O146" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6478,6 +7358,12 @@
         <v>1</v>
       </c>
       <c r="M147" t="n">
+        <v>0</v>
+      </c>
+      <c r="N147" t="n">
+        <v>0</v>
+      </c>
+      <c r="O147" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6519,6 +7405,12 @@
         <v>0</v>
       </c>
       <c r="M148" t="n">
+        <v>0</v>
+      </c>
+      <c r="N148" t="n">
+        <v>3</v>
+      </c>
+      <c r="O148" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6560,6 +7452,12 @@
         <v>1</v>
       </c>
       <c r="M149" t="n">
+        <v>0</v>
+      </c>
+      <c r="N149" t="n">
+        <v>0</v>
+      </c>
+      <c r="O149" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6601,6 +7499,12 @@
         <v>0</v>
       </c>
       <c r="M150" t="n">
+        <v>0</v>
+      </c>
+      <c r="N150" t="n">
+        <v>0</v>
+      </c>
+      <c r="O150" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6642,6 +7546,12 @@
         <v>2</v>
       </c>
       <c r="M151" t="n">
+        <v>0</v>
+      </c>
+      <c r="N151" t="n">
+        <v>1</v>
+      </c>
+      <c r="O151" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6683,6 +7593,12 @@
         <v>0</v>
       </c>
       <c r="M152" t="n">
+        <v>0</v>
+      </c>
+      <c r="N152" t="n">
+        <v>0</v>
+      </c>
+      <c r="O152" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6724,6 +7640,12 @@
         <v>11</v>
       </c>
       <c r="M153" t="n">
+        <v>0</v>
+      </c>
+      <c r="N153" t="n">
+        <v>4</v>
+      </c>
+      <c r="O153" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6765,6 +7687,12 @@
         <v>7</v>
       </c>
       <c r="M154" t="n">
+        <v>0</v>
+      </c>
+      <c r="N154" t="n">
+        <v>8</v>
+      </c>
+      <c r="O154" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6806,6 +7734,12 @@
         <v>5</v>
       </c>
       <c r="M155" t="n">
+        <v>0</v>
+      </c>
+      <c r="N155" t="n">
+        <v>2</v>
+      </c>
+      <c r="O155" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6847,6 +7781,12 @@
         <v>1</v>
       </c>
       <c r="M156" t="n">
+        <v>0</v>
+      </c>
+      <c r="N156" t="n">
+        <v>1</v>
+      </c>
+      <c r="O156" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6888,6 +7828,12 @@
         <v>5</v>
       </c>
       <c r="M157" t="n">
+        <v>0</v>
+      </c>
+      <c r="N157" t="n">
+        <v>2</v>
+      </c>
+      <c r="O157" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6929,6 +7875,12 @@
         <v>19</v>
       </c>
       <c r="M158" t="n">
+        <v>0</v>
+      </c>
+      <c r="N158" t="n">
+        <v>12</v>
+      </c>
+      <c r="O158" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -6970,6 +7922,12 @@
         <v>5</v>
       </c>
       <c r="M159" t="n">
+        <v>0</v>
+      </c>
+      <c r="N159" t="n">
+        <v>3</v>
+      </c>
+      <c r="O159" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7011,6 +7969,12 @@
         <v>1</v>
       </c>
       <c r="M160" t="n">
+        <v>0</v>
+      </c>
+      <c r="N160" t="n">
+        <v>7</v>
+      </c>
+      <c r="O160" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7052,6 +8016,12 @@
         <v>2</v>
       </c>
       <c r="M161" t="n">
+        <v>0</v>
+      </c>
+      <c r="N161" t="n">
+        <v>4</v>
+      </c>
+      <c r="O161" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7093,6 +8063,12 @@
         <v>8</v>
       </c>
       <c r="M162" t="n">
+        <v>0</v>
+      </c>
+      <c r="N162" t="n">
+        <v>8</v>
+      </c>
+      <c r="O162" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7134,6 +8110,12 @@
         <v>2</v>
       </c>
       <c r="M163" t="n">
+        <v>0</v>
+      </c>
+      <c r="N163" t="n">
+        <v>1</v>
+      </c>
+      <c r="O163" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7175,6 +8157,12 @@
         <v>3</v>
       </c>
       <c r="M164" t="n">
+        <v>0</v>
+      </c>
+      <c r="N164" t="n">
+        <v>3</v>
+      </c>
+      <c r="O164" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7216,6 +8204,12 @@
         <v>0</v>
       </c>
       <c r="M165" t="n">
+        <v>0</v>
+      </c>
+      <c r="N165" t="n">
+        <v>0</v>
+      </c>
+      <c r="O165" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7257,6 +8251,12 @@
         <v>0</v>
       </c>
       <c r="M166" t="n">
+        <v>0</v>
+      </c>
+      <c r="N166" t="n">
+        <v>0</v>
+      </c>
+      <c r="O166" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7298,6 +8298,12 @@
         <v>10</v>
       </c>
       <c r="M167" t="n">
+        <v>1</v>
+      </c>
+      <c r="N167" t="n">
+        <v>12</v>
+      </c>
+      <c r="O167" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7339,6 +8345,12 @@
         <v>16</v>
       </c>
       <c r="M168" t="n">
+        <v>0</v>
+      </c>
+      <c r="N168" t="n">
+        <v>9</v>
+      </c>
+      <c r="O168" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7380,6 +8392,12 @@
         <v>7</v>
       </c>
       <c r="M169" t="n">
+        <v>0</v>
+      </c>
+      <c r="N169" t="n">
+        <v>12</v>
+      </c>
+      <c r="O169" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7421,6 +8439,12 @@
         <v>4</v>
       </c>
       <c r="M170" t="n">
+        <v>0</v>
+      </c>
+      <c r="N170" t="n">
+        <v>5</v>
+      </c>
+      <c r="O170" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7462,6 +8486,12 @@
         <v>3</v>
       </c>
       <c r="M171" t="n">
+        <v>0</v>
+      </c>
+      <c r="N171" t="n">
+        <v>0</v>
+      </c>
+      <c r="O171" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7503,6 +8533,12 @@
         <v>2</v>
       </c>
       <c r="M172" t="n">
+        <v>0</v>
+      </c>
+      <c r="N172" t="n">
+        <v>4</v>
+      </c>
+      <c r="O172" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7544,6 +8580,12 @@
         <v>3</v>
       </c>
       <c r="M173" t="n">
+        <v>0</v>
+      </c>
+      <c r="N173" t="n">
+        <v>2</v>
+      </c>
+      <c r="O173" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7585,6 +8627,12 @@
         <v>3</v>
       </c>
       <c r="M174" t="n">
+        <v>0</v>
+      </c>
+      <c r="N174" t="n">
+        <v>2</v>
+      </c>
+      <c r="O174" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7626,6 +8674,12 @@
         <v>13</v>
       </c>
       <c r="M175" t="n">
+        <v>0</v>
+      </c>
+      <c r="N175" t="n">
+        <v>18</v>
+      </c>
+      <c r="O175" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7667,6 +8721,12 @@
         <v>4</v>
       </c>
       <c r="M176" t="n">
+        <v>0</v>
+      </c>
+      <c r="N176" t="n">
+        <v>5</v>
+      </c>
+      <c r="O176" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7708,6 +8768,12 @@
         <v>2</v>
       </c>
       <c r="M177" t="n">
+        <v>0</v>
+      </c>
+      <c r="N177" t="n">
+        <v>7</v>
+      </c>
+      <c r="O177" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7749,6 +8815,12 @@
         <v>2</v>
       </c>
       <c r="M178" t="n">
+        <v>0</v>
+      </c>
+      <c r="N178" t="n">
+        <v>2</v>
+      </c>
+      <c r="O178" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7790,6 +8862,12 @@
         <v>2</v>
       </c>
       <c r="M179" t="n">
+        <v>0</v>
+      </c>
+      <c r="N179" t="n">
+        <v>2</v>
+      </c>
+      <c r="O179" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7831,6 +8909,12 @@
         <v>2</v>
       </c>
       <c r="M180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N180" t="n">
+        <v>2</v>
+      </c>
+      <c r="O180" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7872,6 +8956,12 @@
         <v>2</v>
       </c>
       <c r="M181" t="n">
+        <v>0</v>
+      </c>
+      <c r="N181" t="n">
+        <v>1</v>
+      </c>
+      <c r="O181" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7913,6 +9003,12 @@
         <v>0</v>
       </c>
       <c r="M182" t="n">
+        <v>0</v>
+      </c>
+      <c r="N182" t="n">
+        <v>1</v>
+      </c>
+      <c r="O182" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7954,6 +9050,12 @@
         <v>0</v>
       </c>
       <c r="M183" t="n">
+        <v>0</v>
+      </c>
+      <c r="N183" t="n">
+        <v>2</v>
+      </c>
+      <c r="O183" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -7995,6 +9097,12 @@
         <v>1</v>
       </c>
       <c r="M184" t="n">
+        <v>1</v>
+      </c>
+      <c r="N184" t="n">
+        <v>0</v>
+      </c>
+      <c r="O184" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8036,6 +9144,12 @@
         <v>4</v>
       </c>
       <c r="M185" t="n">
+        <v>1</v>
+      </c>
+      <c r="N185" t="n">
+        <v>2</v>
+      </c>
+      <c r="O185" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8077,6 +9191,12 @@
         <v>16</v>
       </c>
       <c r="M186" t="n">
+        <v>1</v>
+      </c>
+      <c r="N186" t="n">
+        <v>13</v>
+      </c>
+      <c r="O186" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8118,6 +9238,12 @@
         <v>12</v>
       </c>
       <c r="M187" t="n">
+        <v>0</v>
+      </c>
+      <c r="N187" t="n">
+        <v>3</v>
+      </c>
+      <c r="O187" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8159,6 +9285,12 @@
         <v>8</v>
       </c>
       <c r="M188" t="n">
+        <v>0</v>
+      </c>
+      <c r="N188" t="n">
+        <v>14</v>
+      </c>
+      <c r="O188" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8200,6 +9332,12 @@
         <v>1</v>
       </c>
       <c r="M189" t="n">
+        <v>0</v>
+      </c>
+      <c r="N189" t="n">
+        <v>0</v>
+      </c>
+      <c r="O189" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8241,6 +9379,12 @@
         <v>1</v>
       </c>
       <c r="M190" t="n">
+        <v>0</v>
+      </c>
+      <c r="N190" t="n">
+        <v>0</v>
+      </c>
+      <c r="O190" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8282,6 +9426,12 @@
         <v>0</v>
       </c>
       <c r="M191" t="n">
+        <v>0</v>
+      </c>
+      <c r="N191" t="n">
+        <v>0</v>
+      </c>
+      <c r="O191" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8323,6 +9473,12 @@
         <v>7</v>
       </c>
       <c r="M192" t="n">
+        <v>0</v>
+      </c>
+      <c r="N192" t="n">
+        <v>6</v>
+      </c>
+      <c r="O192" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8364,6 +9520,12 @@
         <v>1</v>
       </c>
       <c r="M193" t="n">
+        <v>0</v>
+      </c>
+      <c r="N193" t="n">
+        <v>5</v>
+      </c>
+      <c r="O193" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8405,6 +9567,12 @@
         <v>0</v>
       </c>
       <c r="M194" t="n">
+        <v>0</v>
+      </c>
+      <c r="N194" t="n">
+        <v>3</v>
+      </c>
+      <c r="O194" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8446,6 +9614,12 @@
         <v>0</v>
       </c>
       <c r="M195" t="n">
+        <v>0</v>
+      </c>
+      <c r="N195" t="n">
+        <v>3</v>
+      </c>
+      <c r="O195" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8487,6 +9661,12 @@
         <v>1</v>
       </c>
       <c r="M196" t="n">
+        <v>0</v>
+      </c>
+      <c r="N196" t="n">
+        <v>0</v>
+      </c>
+      <c r="O196" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8528,6 +9708,12 @@
         <v>10</v>
       </c>
       <c r="M197" t="n">
+        <v>0</v>
+      </c>
+      <c r="N197" t="n">
+        <v>2</v>
+      </c>
+      <c r="O197" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8569,6 +9755,12 @@
         <v>13</v>
       </c>
       <c r="M198" t="n">
+        <v>0</v>
+      </c>
+      <c r="N198" t="n">
+        <v>6</v>
+      </c>
+      <c r="O198" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8610,6 +9802,12 @@
         <v>2</v>
       </c>
       <c r="M199" t="n">
+        <v>0</v>
+      </c>
+      <c r="N199" t="n">
+        <v>1</v>
+      </c>
+      <c r="O199" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8651,6 +9849,12 @@
         <v>0</v>
       </c>
       <c r="M200" t="n">
+        <v>0</v>
+      </c>
+      <c r="N200" t="n">
+        <v>10</v>
+      </c>
+      <c r="O200" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8692,6 +9896,12 @@
         <v>0</v>
       </c>
       <c r="M201" t="n">
+        <v>0</v>
+      </c>
+      <c r="N201" t="n">
+        <v>3</v>
+      </c>
+      <c r="O201" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8733,6 +9943,12 @@
         <v>1</v>
       </c>
       <c r="M202" t="n">
+        <v>0</v>
+      </c>
+      <c r="N202" t="n">
+        <v>7</v>
+      </c>
+      <c r="O202" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8774,6 +9990,12 @@
         <v>2</v>
       </c>
       <c r="M203" t="n">
+        <v>0</v>
+      </c>
+      <c r="N203" t="n">
+        <v>0</v>
+      </c>
+      <c r="O203" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8815,6 +10037,12 @@
         <v>5</v>
       </c>
       <c r="M204" t="n">
+        <v>0</v>
+      </c>
+      <c r="N204" t="n">
+        <v>5</v>
+      </c>
+      <c r="O204" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8856,6 +10084,12 @@
         <v>3</v>
       </c>
       <c r="M205" t="n">
+        <v>0</v>
+      </c>
+      <c r="N205" t="n">
+        <v>8</v>
+      </c>
+      <c r="O205" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8897,6 +10131,12 @@
         <v>8</v>
       </c>
       <c r="M206" t="n">
+        <v>0</v>
+      </c>
+      <c r="N206" t="n">
+        <v>4</v>
+      </c>
+      <c r="O206" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8938,6 +10178,12 @@
         <v>3</v>
       </c>
       <c r="M207" t="n">
+        <v>0</v>
+      </c>
+      <c r="N207" t="n">
+        <v>5</v>
+      </c>
+      <c r="O207" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -8979,6 +10225,12 @@
         <v>0</v>
       </c>
       <c r="M208" t="n">
+        <v>0</v>
+      </c>
+      <c r="N208" t="n">
+        <v>1</v>
+      </c>
+      <c r="O208" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9020,6 +10272,12 @@
         <v>2</v>
       </c>
       <c r="M209" t="n">
+        <v>0</v>
+      </c>
+      <c r="N209" t="n">
+        <v>1</v>
+      </c>
+      <c r="O209" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9061,6 +10319,12 @@
         <v>0</v>
       </c>
       <c r="M210" t="n">
+        <v>0</v>
+      </c>
+      <c r="N210" t="n">
+        <v>0</v>
+      </c>
+      <c r="O210" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9102,6 +10366,12 @@
         <v>3</v>
       </c>
       <c r="M211" t="n">
+        <v>0</v>
+      </c>
+      <c r="N211" t="n">
+        <v>3</v>
+      </c>
+      <c r="O211" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9143,6 +10413,12 @@
         <v>8</v>
       </c>
       <c r="M212" t="n">
+        <v>0</v>
+      </c>
+      <c r="N212" t="n">
+        <v>5</v>
+      </c>
+      <c r="O212" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9184,6 +10460,12 @@
         <v>5</v>
       </c>
       <c r="M213" t="n">
+        <v>0</v>
+      </c>
+      <c r="N213" t="n">
+        <v>2</v>
+      </c>
+      <c r="O213" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9225,6 +10507,12 @@
         <v>1</v>
       </c>
       <c r="M214" t="n">
+        <v>0</v>
+      </c>
+      <c r="N214" t="n">
+        <v>0</v>
+      </c>
+      <c r="O214" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9266,6 +10554,12 @@
         <v>3</v>
       </c>
       <c r="M215" t="n">
+        <v>0</v>
+      </c>
+      <c r="N215" t="n">
+        <v>0</v>
+      </c>
+      <c r="O215" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9307,6 +10601,12 @@
         <v>3</v>
       </c>
       <c r="M216" t="n">
+        <v>0</v>
+      </c>
+      <c r="N216" t="n">
+        <v>4</v>
+      </c>
+      <c r="O216" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9348,6 +10648,12 @@
         <v>1</v>
       </c>
       <c r="M217" t="n">
+        <v>0</v>
+      </c>
+      <c r="N217" t="n">
+        <v>3</v>
+      </c>
+      <c r="O217" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9389,6 +10695,12 @@
         <v>0</v>
       </c>
       <c r="M218" t="n">
+        <v>0</v>
+      </c>
+      <c r="N218" t="n">
+        <v>0</v>
+      </c>
+      <c r="O218" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9430,6 +10742,12 @@
         <v>1</v>
       </c>
       <c r="M219" t="n">
+        <v>0</v>
+      </c>
+      <c r="N219" t="n">
+        <v>1</v>
+      </c>
+      <c r="O219" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9471,6 +10789,12 @@
         <v>4</v>
       </c>
       <c r="M220" t="n">
+        <v>0</v>
+      </c>
+      <c r="N220" t="n">
+        <v>1</v>
+      </c>
+      <c r="O220" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9512,6 +10836,12 @@
         <v>3</v>
       </c>
       <c r="M221" t="n">
+        <v>0</v>
+      </c>
+      <c r="N221" t="n">
+        <v>4</v>
+      </c>
+      <c r="O221" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9553,6 +10883,12 @@
         <v>1</v>
       </c>
       <c r="M222" t="n">
+        <v>0</v>
+      </c>
+      <c r="N222" t="n">
+        <v>1</v>
+      </c>
+      <c r="O222" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9594,6 +10930,12 @@
         <v>2</v>
       </c>
       <c r="M223" t="n">
+        <v>0</v>
+      </c>
+      <c r="N223" t="n">
+        <v>4</v>
+      </c>
+      <c r="O223" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9635,6 +10977,12 @@
         <v>2</v>
       </c>
       <c r="M224" t="n">
+        <v>0</v>
+      </c>
+      <c r="N224" t="n">
+        <v>0</v>
+      </c>
+      <c r="O224" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9676,6 +11024,12 @@
         <v>3</v>
       </c>
       <c r="M225" t="n">
+        <v>0</v>
+      </c>
+      <c r="N225" t="n">
+        <v>3</v>
+      </c>
+      <c r="O225" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9717,6 +11071,12 @@
         <v>0</v>
       </c>
       <c r="M226" t="n">
+        <v>0</v>
+      </c>
+      <c r="N226" t="n">
+        <v>2</v>
+      </c>
+      <c r="O226" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9758,6 +11118,12 @@
         <v>0</v>
       </c>
       <c r="M227" t="n">
+        <v>0</v>
+      </c>
+      <c r="N227" t="n">
+        <v>3</v>
+      </c>
+      <c r="O227" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9799,6 +11165,12 @@
         <v>6</v>
       </c>
       <c r="M228" t="n">
+        <v>0</v>
+      </c>
+      <c r="N228" t="n">
+        <v>12</v>
+      </c>
+      <c r="O228" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9840,6 +11212,12 @@
         <v>10</v>
       </c>
       <c r="M229" t="n">
+        <v>1</v>
+      </c>
+      <c r="N229" t="n">
+        <v>16</v>
+      </c>
+      <c r="O229" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9881,6 +11259,12 @@
         <v>0</v>
       </c>
       <c r="M230" t="n">
+        <v>0</v>
+      </c>
+      <c r="N230" t="n">
+        <v>0</v>
+      </c>
+      <c r="O230" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9922,6 +11306,12 @@
         <v>0</v>
       </c>
       <c r="M231" t="n">
+        <v>0</v>
+      </c>
+      <c r="N231" t="n">
+        <v>1</v>
+      </c>
+      <c r="O231" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -9963,6 +11353,12 @@
         <v>0</v>
       </c>
       <c r="M232" t="n">
+        <v>0</v>
+      </c>
+      <c r="N232" t="n">
+        <v>0</v>
+      </c>
+      <c r="O232" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10004,6 +11400,12 @@
         <v>0</v>
       </c>
       <c r="M233" t="n">
+        <v>0</v>
+      </c>
+      <c r="N233" t="n">
+        <v>6</v>
+      </c>
+      <c r="O233" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10045,6 +11447,12 @@
         <v>1</v>
       </c>
       <c r="M234" t="n">
+        <v>0</v>
+      </c>
+      <c r="N234" t="n">
+        <v>1</v>
+      </c>
+      <c r="O234" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10086,6 +11494,12 @@
         <v>4</v>
       </c>
       <c r="M235" t="n">
+        <v>0</v>
+      </c>
+      <c r="N235" t="n">
+        <v>0</v>
+      </c>
+      <c r="O235" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10127,6 +11541,12 @@
         <v>8</v>
       </c>
       <c r="M236" t="n">
+        <v>0</v>
+      </c>
+      <c r="N236" t="n">
+        <v>1</v>
+      </c>
+      <c r="O236" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10168,6 +11588,12 @@
         <v>5</v>
       </c>
       <c r="M237" t="n">
+        <v>0</v>
+      </c>
+      <c r="N237" t="n">
+        <v>1</v>
+      </c>
+      <c r="O237" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10209,6 +11635,12 @@
         <v>2</v>
       </c>
       <c r="M238" t="n">
+        <v>0</v>
+      </c>
+      <c r="N238" t="n">
+        <v>1</v>
+      </c>
+      <c r="O238" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10250,6 +11682,12 @@
         <v>0</v>
       </c>
       <c r="M239" t="n">
+        <v>0</v>
+      </c>
+      <c r="N239" t="n">
+        <v>3</v>
+      </c>
+      <c r="O239" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10291,6 +11729,12 @@
         <v>1</v>
       </c>
       <c r="M240" t="n">
+        <v>1</v>
+      </c>
+      <c r="N240" t="n">
+        <v>2</v>
+      </c>
+      <c r="O240" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10332,6 +11776,12 @@
         <v>1</v>
       </c>
       <c r="M241" t="n">
+        <v>0</v>
+      </c>
+      <c r="N241" t="n">
+        <v>0</v>
+      </c>
+      <c r="O241" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10373,6 +11823,12 @@
         <v>1</v>
       </c>
       <c r="M242" t="n">
+        <v>0</v>
+      </c>
+      <c r="N242" t="n">
+        <v>9</v>
+      </c>
+      <c r="O242" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10414,6 +11870,12 @@
         <v>3</v>
       </c>
       <c r="M243" t="n">
+        <v>0</v>
+      </c>
+      <c r="N243" t="n">
+        <v>10</v>
+      </c>
+      <c r="O243" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10455,6 +11917,12 @@
         <v>10</v>
       </c>
       <c r="M244" t="n">
+        <v>0</v>
+      </c>
+      <c r="N244" t="n">
+        <v>12</v>
+      </c>
+      <c r="O244" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10496,6 +11964,12 @@
         <v>12</v>
       </c>
       <c r="M245" t="n">
+        <v>0</v>
+      </c>
+      <c r="N245" t="n">
+        <v>6</v>
+      </c>
+      <c r="O245" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10537,6 +12011,12 @@
         <v>1</v>
       </c>
       <c r="M246" t="n">
+        <v>0</v>
+      </c>
+      <c r="N246" t="n">
+        <v>1</v>
+      </c>
+      <c r="O246" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10578,6 +12058,12 @@
         <v>5</v>
       </c>
       <c r="M247" t="n">
+        <v>0</v>
+      </c>
+      <c r="N247" t="n">
+        <v>3</v>
+      </c>
+      <c r="O247" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10619,6 +12105,12 @@
         <v>1</v>
       </c>
       <c r="M248" t="n">
+        <v>0</v>
+      </c>
+      <c r="N248" t="n">
+        <v>6</v>
+      </c>
+      <c r="O248" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10660,6 +12152,12 @@
         <v>4</v>
       </c>
       <c r="M249" t="n">
+        <v>0</v>
+      </c>
+      <c r="N249" t="n">
+        <v>14</v>
+      </c>
+      <c r="O249" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10701,6 +12199,12 @@
         <v>1</v>
       </c>
       <c r="M250" t="n">
+        <v>0</v>
+      </c>
+      <c r="N250" t="n">
+        <v>2</v>
+      </c>
+      <c r="O250" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10742,6 +12246,12 @@
         <v>0</v>
       </c>
       <c r="M251" t="n">
+        <v>0</v>
+      </c>
+      <c r="N251" t="n">
+        <v>0</v>
+      </c>
+      <c r="O251" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10783,6 +12293,12 @@
         <v>0</v>
       </c>
       <c r="M252" t="n">
+        <v>0</v>
+      </c>
+      <c r="N252" t="n">
+        <v>4</v>
+      </c>
+      <c r="O252" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10824,6 +12340,12 @@
         <v>4</v>
       </c>
       <c r="M253" t="n">
+        <v>1</v>
+      </c>
+      <c r="N253" t="n">
+        <v>27</v>
+      </c>
+      <c r="O253" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10865,6 +12387,12 @@
         <v>4</v>
       </c>
       <c r="M254" t="n">
+        <v>0</v>
+      </c>
+      <c r="N254" t="n">
+        <v>9</v>
+      </c>
+      <c r="O254" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10906,6 +12434,12 @@
         <v>7</v>
       </c>
       <c r="M255" t="n">
+        <v>0</v>
+      </c>
+      <c r="N255" t="n">
+        <v>1</v>
+      </c>
+      <c r="O255" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10947,6 +12481,12 @@
         <v>4</v>
       </c>
       <c r="M256" t="n">
+        <v>0</v>
+      </c>
+      <c r="N256" t="n">
+        <v>4</v>
+      </c>
+      <c r="O256" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -10988,6 +12528,12 @@
         <v>3</v>
       </c>
       <c r="M257" t="n">
+        <v>0</v>
+      </c>
+      <c r="N257" t="n">
+        <v>1</v>
+      </c>
+      <c r="O257" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11029,6 +12575,12 @@
         <v>5</v>
       </c>
       <c r="M258" t="n">
+        <v>0</v>
+      </c>
+      <c r="N258" t="n">
+        <v>1</v>
+      </c>
+      <c r="O258" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11070,6 +12622,12 @@
         <v>0</v>
       </c>
       <c r="M259" t="n">
+        <v>0</v>
+      </c>
+      <c r="N259" t="n">
+        <v>0</v>
+      </c>
+      <c r="O259" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11111,6 +12669,12 @@
         <v>3</v>
       </c>
       <c r="M260" t="n">
+        <v>0</v>
+      </c>
+      <c r="N260" t="n">
+        <v>0</v>
+      </c>
+      <c r="O260" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11152,6 +12716,12 @@
         <v>2</v>
       </c>
       <c r="M261" t="n">
+        <v>0</v>
+      </c>
+      <c r="N261" t="n">
+        <v>5</v>
+      </c>
+      <c r="O261" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11193,6 +12763,12 @@
         <v>3</v>
       </c>
       <c r="M262" t="n">
+        <v>0</v>
+      </c>
+      <c r="N262" t="n">
+        <v>0</v>
+      </c>
+      <c r="O262" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11234,6 +12810,12 @@
         <v>1</v>
       </c>
       <c r="M263" t="n">
+        <v>0</v>
+      </c>
+      <c r="N263" t="n">
+        <v>1</v>
+      </c>
+      <c r="O263" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11275,6 +12857,12 @@
         <v>2</v>
       </c>
       <c r="M264" t="n">
+        <v>0</v>
+      </c>
+      <c r="N264" t="n">
+        <v>7</v>
+      </c>
+      <c r="O264" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11316,6 +12904,12 @@
         <v>6</v>
       </c>
       <c r="M265" t="n">
+        <v>0</v>
+      </c>
+      <c r="N265" t="n">
+        <v>5</v>
+      </c>
+      <c r="O265" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11357,6 +12951,12 @@
         <v>1</v>
       </c>
       <c r="M266" t="n">
+        <v>1</v>
+      </c>
+      <c r="N266" t="n">
+        <v>6</v>
+      </c>
+      <c r="O266" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11398,6 +12998,12 @@
         <v>5</v>
       </c>
       <c r="M267" t="n">
+        <v>0</v>
+      </c>
+      <c r="N267" t="n">
+        <v>12</v>
+      </c>
+      <c r="O267" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11439,6 +13045,12 @@
         <v>3</v>
       </c>
       <c r="M268" t="n">
+        <v>0</v>
+      </c>
+      <c r="N268" t="n">
+        <v>1</v>
+      </c>
+      <c r="O268" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11480,6 +13092,12 @@
         <v>2</v>
       </c>
       <c r="M269" t="n">
+        <v>0</v>
+      </c>
+      <c r="N269" t="n">
+        <v>9</v>
+      </c>
+      <c r="O269" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11521,6 +13139,12 @@
         <v>10</v>
       </c>
       <c r="M270" t="n">
+        <v>0</v>
+      </c>
+      <c r="N270" t="n">
+        <v>0</v>
+      </c>
+      <c r="O270" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11562,6 +13186,12 @@
         <v>0</v>
       </c>
       <c r="M271" t="n">
+        <v>0</v>
+      </c>
+      <c r="N271" t="n">
+        <v>1</v>
+      </c>
+      <c r="O271" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11603,6 +13233,12 @@
         <v>3</v>
       </c>
       <c r="M272" t="n">
+        <v>0</v>
+      </c>
+      <c r="N272" t="n">
+        <v>4</v>
+      </c>
+      <c r="O272" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11644,6 +13280,12 @@
         <v>6</v>
       </c>
       <c r="M273" t="n">
+        <v>0</v>
+      </c>
+      <c r="N273" t="n">
+        <v>0</v>
+      </c>
+      <c r="O273" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11685,6 +13327,12 @@
         <v>2</v>
       </c>
       <c r="M274" t="n">
+        <v>0</v>
+      </c>
+      <c r="N274" t="n">
+        <v>0</v>
+      </c>
+      <c r="O274" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11726,6 +13374,12 @@
         <v>4</v>
       </c>
       <c r="M275" t="n">
+        <v>0</v>
+      </c>
+      <c r="N275" t="n">
+        <v>0</v>
+      </c>
+      <c r="O275" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11767,6 +13421,12 @@
         <v>5</v>
       </c>
       <c r="M276" t="n">
+        <v>0</v>
+      </c>
+      <c r="N276" t="n">
+        <v>1</v>
+      </c>
+      <c r="O276" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11808,6 +13468,12 @@
         <v>3</v>
       </c>
       <c r="M277" t="n">
+        <v>0</v>
+      </c>
+      <c r="N277" t="n">
+        <v>0</v>
+      </c>
+      <c r="O277" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11849,6 +13515,12 @@
         <v>0</v>
       </c>
       <c r="M278" t="n">
+        <v>0</v>
+      </c>
+      <c r="N278" t="n">
+        <v>5</v>
+      </c>
+      <c r="O278" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11890,6 +13562,12 @@
         <v>6</v>
       </c>
       <c r="M279" t="n">
+        <v>0</v>
+      </c>
+      <c r="N279" t="n">
+        <v>7</v>
+      </c>
+      <c r="O279" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11931,6 +13609,12 @@
         <v>10</v>
       </c>
       <c r="M280" t="n">
+        <v>0</v>
+      </c>
+      <c r="N280" t="n">
+        <v>2</v>
+      </c>
+      <c r="O280" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -11972,6 +13656,12 @@
         <v>0</v>
       </c>
       <c r="M281" t="n">
+        <v>0</v>
+      </c>
+      <c r="N281" t="n">
+        <v>0</v>
+      </c>
+      <c r="O281" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12013,6 +13703,12 @@
         <v>2</v>
       </c>
       <c r="M282" t="n">
+        <v>0</v>
+      </c>
+      <c r="N282" t="n">
+        <v>2</v>
+      </c>
+      <c r="O282" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12054,6 +13750,12 @@
         <v>0</v>
       </c>
       <c r="M283" t="n">
+        <v>0</v>
+      </c>
+      <c r="N283" t="n">
+        <v>0</v>
+      </c>
+      <c r="O283" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12095,6 +13797,12 @@
         <v>2</v>
       </c>
       <c r="M284" t="n">
+        <v>0</v>
+      </c>
+      <c r="N284" t="n">
+        <v>0</v>
+      </c>
+      <c r="O284" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12136,6 +13844,12 @@
         <v>0</v>
       </c>
       <c r="M285" t="n">
+        <v>0</v>
+      </c>
+      <c r="N285" t="n">
+        <v>0</v>
+      </c>
+      <c r="O285" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12177,6 +13891,12 @@
         <v>1</v>
       </c>
       <c r="M286" t="n">
+        <v>0</v>
+      </c>
+      <c r="N286" t="n">
+        <v>1</v>
+      </c>
+      <c r="O286" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12218,6 +13938,12 @@
         <v>0</v>
       </c>
       <c r="M287" t="n">
+        <v>0</v>
+      </c>
+      <c r="N287" t="n">
+        <v>3</v>
+      </c>
+      <c r="O287" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12259,6 +13985,12 @@
         <v>3</v>
       </c>
       <c r="M288" t="n">
+        <v>0</v>
+      </c>
+      <c r="N288" t="n">
+        <v>5</v>
+      </c>
+      <c r="O288" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12300,6 +14032,12 @@
         <v>2</v>
       </c>
       <c r="M289" t="n">
+        <v>0</v>
+      </c>
+      <c r="N289" t="n">
+        <v>1</v>
+      </c>
+      <c r="O289" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12341,6 +14079,12 @@
         <v>2</v>
       </c>
       <c r="M290" t="n">
+        <v>0</v>
+      </c>
+      <c r="N290" t="n">
+        <v>2</v>
+      </c>
+      <c r="O290" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12382,6 +14126,12 @@
         <v>3</v>
       </c>
       <c r="M291" t="n">
+        <v>0</v>
+      </c>
+      <c r="N291" t="n">
+        <v>7</v>
+      </c>
+      <c r="O291" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12423,6 +14173,12 @@
         <v>0</v>
       </c>
       <c r="M292" t="n">
+        <v>0</v>
+      </c>
+      <c r="N292" t="n">
+        <v>0</v>
+      </c>
+      <c r="O292" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12464,6 +14220,12 @@
         <v>2</v>
       </c>
       <c r="M293" t="n">
+        <v>0</v>
+      </c>
+      <c r="N293" t="n">
+        <v>1</v>
+      </c>
+      <c r="O293" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12505,6 +14267,12 @@
         <v>0</v>
       </c>
       <c r="M294" t="n">
+        <v>0</v>
+      </c>
+      <c r="N294" t="n">
+        <v>6</v>
+      </c>
+      <c r="O294" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12546,6 +14314,12 @@
         <v>2</v>
       </c>
       <c r="M295" t="n">
+        <v>0</v>
+      </c>
+      <c r="N295" t="n">
+        <v>1</v>
+      </c>
+      <c r="O295" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12587,6 +14361,12 @@
         <v>8</v>
       </c>
       <c r="M296" t="n">
+        <v>0</v>
+      </c>
+      <c r="N296" t="n">
+        <v>1</v>
+      </c>
+      <c r="O296" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12628,6 +14408,12 @@
         <v>15</v>
       </c>
       <c r="M297" t="n">
+        <v>0</v>
+      </c>
+      <c r="N297" t="n">
+        <v>1</v>
+      </c>
+      <c r="O297" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12669,6 +14455,12 @@
         <v>19</v>
       </c>
       <c r="M298" t="n">
+        <v>0</v>
+      </c>
+      <c r="N298" t="n">
+        <v>9</v>
+      </c>
+      <c r="O298" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12710,6 +14502,12 @@
         <v>4</v>
       </c>
       <c r="M299" t="n">
+        <v>0</v>
+      </c>
+      <c r="N299" t="n">
+        <v>6</v>
+      </c>
+      <c r="O299" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12751,6 +14549,12 @@
         <v>0</v>
       </c>
       <c r="M300" t="n">
+        <v>0</v>
+      </c>
+      <c r="N300" t="n">
+        <v>9</v>
+      </c>
+      <c r="O300" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12792,6 +14596,12 @@
         <v>5</v>
       </c>
       <c r="M301" t="n">
+        <v>0</v>
+      </c>
+      <c r="N301" t="n">
+        <v>3</v>
+      </c>
+      <c r="O301" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12833,6 +14643,12 @@
         <v>2</v>
       </c>
       <c r="M302" t="n">
+        <v>0</v>
+      </c>
+      <c r="N302" t="n">
+        <v>7</v>
+      </c>
+      <c r="O302" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12874,6 +14690,12 @@
         <v>0</v>
       </c>
       <c r="M303" t="n">
+        <v>0</v>
+      </c>
+      <c r="N303" t="n">
+        <v>0</v>
+      </c>
+      <c r="O303" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12915,6 +14737,12 @@
         <v>0</v>
       </c>
       <c r="M304" t="n">
+        <v>0</v>
+      </c>
+      <c r="N304" t="n">
+        <v>4</v>
+      </c>
+      <c r="O304" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12956,6 +14784,12 @@
         <v>0</v>
       </c>
       <c r="M305" t="n">
+        <v>0</v>
+      </c>
+      <c r="N305" t="n">
+        <v>0</v>
+      </c>
+      <c r="O305" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -12997,6 +14831,12 @@
         <v>1</v>
       </c>
       <c r="M306" t="n">
+        <v>0</v>
+      </c>
+      <c r="N306" t="n">
+        <v>0</v>
+      </c>
+      <c r="O306" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13038,6 +14878,12 @@
         <v>3</v>
       </c>
       <c r="M307" t="n">
+        <v>0</v>
+      </c>
+      <c r="N307" t="n">
+        <v>5</v>
+      </c>
+      <c r="O307" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13079,6 +14925,12 @@
         <v>8</v>
       </c>
       <c r="M308" t="n">
+        <v>0</v>
+      </c>
+      <c r="N308" t="n">
+        <v>2</v>
+      </c>
+      <c r="O308" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13120,6 +14972,12 @@
         <v>0</v>
       </c>
       <c r="M309" t="n">
+        <v>0</v>
+      </c>
+      <c r="N309" t="n">
+        <v>0</v>
+      </c>
+      <c r="O309" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13161,6 +15019,12 @@
         <v>4</v>
       </c>
       <c r="M310" t="n">
+        <v>0</v>
+      </c>
+      <c r="N310" t="n">
+        <v>1</v>
+      </c>
+      <c r="O310" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13202,6 +15066,12 @@
         <v>4</v>
       </c>
       <c r="M311" t="n">
+        <v>0</v>
+      </c>
+      <c r="N311" t="n">
+        <v>1</v>
+      </c>
+      <c r="O311" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13243,6 +15113,12 @@
         <v>3</v>
       </c>
       <c r="M312" t="n">
+        <v>0</v>
+      </c>
+      <c r="N312" t="n">
+        <v>2</v>
+      </c>
+      <c r="O312" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13284,6 +15160,12 @@
         <v>4</v>
       </c>
       <c r="M313" t="n">
+        <v>0</v>
+      </c>
+      <c r="N313" t="n">
+        <v>4</v>
+      </c>
+      <c r="O313" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13325,6 +15207,12 @@
         <v>1</v>
       </c>
       <c r="M314" t="n">
+        <v>0</v>
+      </c>
+      <c r="N314" t="n">
+        <v>1</v>
+      </c>
+      <c r="O314" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13366,6 +15254,12 @@
         <v>5</v>
       </c>
       <c r="M315" t="n">
+        <v>0</v>
+      </c>
+      <c r="N315" t="n">
+        <v>1</v>
+      </c>
+      <c r="O315" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13407,6 +15301,12 @@
         <v>0</v>
       </c>
       <c r="M316" t="n">
+        <v>0</v>
+      </c>
+      <c r="N316" t="n">
+        <v>0</v>
+      </c>
+      <c r="O316" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13448,6 +15348,12 @@
         <v>0</v>
       </c>
       <c r="M317" t="n">
+        <v>0</v>
+      </c>
+      <c r="N317" t="n">
+        <v>0</v>
+      </c>
+      <c r="O317" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13489,6 +15395,12 @@
         <v>5</v>
       </c>
       <c r="M318" t="n">
+        <v>0</v>
+      </c>
+      <c r="N318" t="n">
+        <v>12</v>
+      </c>
+      <c r="O318" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13530,6 +15442,12 @@
         <v>4</v>
       </c>
       <c r="M319" t="n">
+        <v>0</v>
+      </c>
+      <c r="N319" t="n">
+        <v>6</v>
+      </c>
+      <c r="O319" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13571,6 +15489,12 @@
         <v>1</v>
       </c>
       <c r="M320" t="n">
+        <v>0</v>
+      </c>
+      <c r="N320" t="n">
+        <v>3</v>
+      </c>
+      <c r="O320" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13612,6 +15536,12 @@
         <v>0</v>
       </c>
       <c r="M321" t="n">
+        <v>0</v>
+      </c>
+      <c r="N321" t="n">
+        <v>0</v>
+      </c>
+      <c r="O321" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13653,6 +15583,12 @@
         <v>2</v>
       </c>
       <c r="M322" t="n">
+        <v>0</v>
+      </c>
+      <c r="N322" t="n">
+        <v>2</v>
+      </c>
+      <c r="O322" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13694,6 +15630,12 @@
         <v>3</v>
       </c>
       <c r="M323" t="n">
+        <v>0</v>
+      </c>
+      <c r="N323" t="n">
+        <v>2</v>
+      </c>
+      <c r="O323" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13735,6 +15677,12 @@
         <v>0</v>
       </c>
       <c r="M324" t="n">
+        <v>0</v>
+      </c>
+      <c r="N324" t="n">
+        <v>2</v>
+      </c>
+      <c r="O324" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13776,6 +15724,12 @@
         <v>6</v>
       </c>
       <c r="M325" t="n">
+        <v>2</v>
+      </c>
+      <c r="N325" t="n">
+        <v>11</v>
+      </c>
+      <c r="O325" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13817,6 +15771,12 @@
         <v>23</v>
       </c>
       <c r="M326" t="n">
+        <v>1</v>
+      </c>
+      <c r="N326" t="n">
+        <v>5</v>
+      </c>
+      <c r="O326" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13858,6 +15818,12 @@
         <v>19</v>
       </c>
       <c r="M327" t="n">
+        <v>0</v>
+      </c>
+      <c r="N327" t="n">
+        <v>3</v>
+      </c>
+      <c r="O327" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13899,6 +15865,12 @@
         <v>5</v>
       </c>
       <c r="M328" t="n">
+        <v>0</v>
+      </c>
+      <c r="N328" t="n">
+        <v>3</v>
+      </c>
+      <c r="O328" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13940,6 +15912,12 @@
         <v>6</v>
       </c>
       <c r="M329" t="n">
+        <v>0</v>
+      </c>
+      <c r="N329" t="n">
+        <v>4</v>
+      </c>
+      <c r="O329" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -13981,6 +15959,12 @@
         <v>1</v>
       </c>
       <c r="M330" t="n">
+        <v>0</v>
+      </c>
+      <c r="N330" t="n">
+        <v>1</v>
+      </c>
+      <c r="O330" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14022,6 +16006,12 @@
         <v>4</v>
       </c>
       <c r="M331" t="n">
+        <v>0</v>
+      </c>
+      <c r="N331" t="n">
+        <v>3</v>
+      </c>
+      <c r="O331" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14063,6 +16053,12 @@
         <v>2</v>
       </c>
       <c r="M332" t="n">
+        <v>0</v>
+      </c>
+      <c r="N332" t="n">
+        <v>3</v>
+      </c>
+      <c r="O332" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14104,6 +16100,12 @@
         <v>4</v>
       </c>
       <c r="M333" t="n">
+        <v>0</v>
+      </c>
+      <c r="N333" t="n">
+        <v>10</v>
+      </c>
+      <c r="O333" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14145,6 +16147,12 @@
         <v>1</v>
       </c>
       <c r="M334" t="n">
+        <v>0</v>
+      </c>
+      <c r="N334" t="n">
+        <v>0</v>
+      </c>
+      <c r="O334" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14186,6 +16194,12 @@
         <v>2</v>
       </c>
       <c r="M335" t="n">
+        <v>0</v>
+      </c>
+      <c r="N335" t="n">
+        <v>0</v>
+      </c>
+      <c r="O335" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14227,6 +16241,12 @@
         <v>4</v>
       </c>
       <c r="M336" t="n">
+        <v>0</v>
+      </c>
+      <c r="N336" t="n">
+        <v>0</v>
+      </c>
+      <c r="O336" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14268,6 +16288,12 @@
         <v>8</v>
       </c>
       <c r="M337" t="n">
+        <v>0</v>
+      </c>
+      <c r="N337" t="n">
+        <v>3</v>
+      </c>
+      <c r="O337" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14309,6 +16335,12 @@
         <v>1</v>
       </c>
       <c r="M338" t="n">
+        <v>0</v>
+      </c>
+      <c r="N338" t="n">
+        <v>2</v>
+      </c>
+      <c r="O338" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14350,6 +16382,12 @@
         <v>0</v>
       </c>
       <c r="M339" t="n">
+        <v>0</v>
+      </c>
+      <c r="N339" t="n">
+        <v>3</v>
+      </c>
+      <c r="O339" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14391,6 +16429,12 @@
         <v>3</v>
       </c>
       <c r="M340" t="n">
+        <v>0</v>
+      </c>
+      <c r="N340" t="n">
+        <v>0</v>
+      </c>
+      <c r="O340" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14432,6 +16476,12 @@
         <v>0</v>
       </c>
       <c r="M341" t="n">
+        <v>0</v>
+      </c>
+      <c r="N341" t="n">
+        <v>0</v>
+      </c>
+      <c r="O341" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14473,6 +16523,12 @@
         <v>1</v>
       </c>
       <c r="M342" t="n">
+        <v>0</v>
+      </c>
+      <c r="N342" t="n">
+        <v>4</v>
+      </c>
+      <c r="O342" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14514,6 +16570,12 @@
         <v>0</v>
       </c>
       <c r="M343" t="n">
+        <v>0</v>
+      </c>
+      <c r="N343" t="n">
+        <v>0</v>
+      </c>
+      <c r="O343" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14555,6 +16617,12 @@
         <v>2</v>
       </c>
       <c r="M344" t="n">
+        <v>0</v>
+      </c>
+      <c r="N344" t="n">
+        <v>1</v>
+      </c>
+      <c r="O344" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14596,6 +16664,12 @@
         <v>6</v>
       </c>
       <c r="M345" t="n">
+        <v>0</v>
+      </c>
+      <c r="N345" t="n">
+        <v>6</v>
+      </c>
+      <c r="O345" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14637,6 +16711,12 @@
         <v>6</v>
       </c>
       <c r="M346" t="n">
+        <v>0</v>
+      </c>
+      <c r="N346" t="n">
+        <v>9</v>
+      </c>
+      <c r="O346" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14678,6 +16758,12 @@
         <v>2</v>
       </c>
       <c r="M347" t="n">
+        <v>0</v>
+      </c>
+      <c r="N347" t="n">
+        <v>0</v>
+      </c>
+      <c r="O347" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14719,6 +16805,12 @@
         <v>4</v>
       </c>
       <c r="M348" t="n">
+        <v>0</v>
+      </c>
+      <c r="N348" t="n">
+        <v>4</v>
+      </c>
+      <c r="O348" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14760,6 +16852,12 @@
         <v>2</v>
       </c>
       <c r="M349" t="n">
+        <v>0</v>
+      </c>
+      <c r="N349" t="n">
+        <v>2</v>
+      </c>
+      <c r="O349" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14801,6 +16899,12 @@
         <v>1</v>
       </c>
       <c r="M350" t="n">
+        <v>0</v>
+      </c>
+      <c r="N350" t="n">
+        <v>2</v>
+      </c>
+      <c r="O350" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14842,6 +16946,12 @@
         <v>1</v>
       </c>
       <c r="M351" t="n">
+        <v>0</v>
+      </c>
+      <c r="N351" t="n">
+        <v>1</v>
+      </c>
+      <c r="O351" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14883,6 +16993,12 @@
         <v>1</v>
       </c>
       <c r="M352" t="n">
+        <v>0</v>
+      </c>
+      <c r="N352" t="n">
+        <v>2</v>
+      </c>
+      <c r="O352" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14924,6 +17040,12 @@
         <v>1</v>
       </c>
       <c r="M353" t="n">
+        <v>0</v>
+      </c>
+      <c r="N353" t="n">
+        <v>5</v>
+      </c>
+      <c r="O353" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -14965,6 +17087,12 @@
         <v>1</v>
       </c>
       <c r="M354" t="n">
+        <v>0</v>
+      </c>
+      <c r="N354" t="n">
+        <v>13</v>
+      </c>
+      <c r="O354" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15006,6 +17134,12 @@
         <v>1</v>
       </c>
       <c r="M355" t="n">
+        <v>0</v>
+      </c>
+      <c r="N355" t="n">
+        <v>1</v>
+      </c>
+      <c r="O355" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15047,6 +17181,12 @@
         <v>0</v>
       </c>
       <c r="M356" t="n">
+        <v>0</v>
+      </c>
+      <c r="N356" t="n">
+        <v>7</v>
+      </c>
+      <c r="O356" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15088,6 +17228,12 @@
         <v>0</v>
       </c>
       <c r="M357" t="n">
+        <v>0</v>
+      </c>
+      <c r="N357" t="n">
+        <v>5</v>
+      </c>
+      <c r="O357" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15129,6 +17275,12 @@
         <v>8</v>
       </c>
       <c r="M358" t="n">
+        <v>0</v>
+      </c>
+      <c r="N358" t="n">
+        <v>10</v>
+      </c>
+      <c r="O358" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15170,6 +17322,12 @@
         <v>8</v>
       </c>
       <c r="M359" t="n">
+        <v>0</v>
+      </c>
+      <c r="N359" t="n">
+        <v>10</v>
+      </c>
+      <c r="O359" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15211,6 +17369,12 @@
         <v>3</v>
       </c>
       <c r="M360" t="n">
+        <v>0</v>
+      </c>
+      <c r="N360" t="n">
+        <v>1</v>
+      </c>
+      <c r="O360" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15252,6 +17416,12 @@
         <v>0</v>
       </c>
       <c r="M361" t="n">
+        <v>0</v>
+      </c>
+      <c r="N361" t="n">
+        <v>1</v>
+      </c>
+      <c r="O361" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15293,6 +17463,12 @@
         <v>0</v>
       </c>
       <c r="M362" t="n">
+        <v>0</v>
+      </c>
+      <c r="N362" t="n">
+        <v>0</v>
+      </c>
+      <c r="O362" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15334,6 +17510,12 @@
         <v>3</v>
       </c>
       <c r="M363" t="n">
+        <v>0</v>
+      </c>
+      <c r="N363" t="n">
+        <v>1</v>
+      </c>
+      <c r="O363" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15375,6 +17557,12 @@
         <v>7</v>
       </c>
       <c r="M364" t="n">
+        <v>0</v>
+      </c>
+      <c r="N364" t="n">
+        <v>5</v>
+      </c>
+      <c r="O364" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15416,6 +17604,12 @@
         <v>6</v>
       </c>
       <c r="M365" t="n">
+        <v>0</v>
+      </c>
+      <c r="N365" t="n">
+        <v>13</v>
+      </c>
+      <c r="O365" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15457,6 +17651,12 @@
         <v>1</v>
       </c>
       <c r="M366" t="n">
+        <v>0</v>
+      </c>
+      <c r="N366" t="n">
+        <v>4</v>
+      </c>
+      <c r="O366" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15498,6 +17698,12 @@
         <v>0</v>
       </c>
       <c r="M367" t="n">
+        <v>0</v>
+      </c>
+      <c r="N367" t="n">
+        <v>6</v>
+      </c>
+      <c r="O367" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15539,6 +17745,12 @@
         <v>2</v>
       </c>
       <c r="M368" t="n">
+        <v>0</v>
+      </c>
+      <c r="N368" t="n">
+        <v>2</v>
+      </c>
+      <c r="O368" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15580,6 +17792,12 @@
         <v>14</v>
       </c>
       <c r="M369" t="n">
+        <v>0</v>
+      </c>
+      <c r="N369" t="n">
+        <v>18</v>
+      </c>
+      <c r="O369" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15621,6 +17839,12 @@
         <v>6</v>
       </c>
       <c r="M370" t="n">
+        <v>0</v>
+      </c>
+      <c r="N370" t="n">
+        <v>7</v>
+      </c>
+      <c r="O370" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15662,6 +17886,12 @@
         <v>5</v>
       </c>
       <c r="M371" t="n">
+        <v>0</v>
+      </c>
+      <c r="N371" t="n">
+        <v>2</v>
+      </c>
+      <c r="O371" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15703,6 +17933,12 @@
         <v>1</v>
       </c>
       <c r="M372" t="n">
+        <v>0</v>
+      </c>
+      <c r="N372" t="n">
+        <v>5</v>
+      </c>
+      <c r="O372" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15744,6 +17980,12 @@
         <v>0</v>
       </c>
       <c r="M373" t="n">
+        <v>0</v>
+      </c>
+      <c r="N373" t="n">
+        <v>2</v>
+      </c>
+      <c r="O373" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15785,6 +18027,12 @@
         <v>1</v>
       </c>
       <c r="M374" t="n">
+        <v>0</v>
+      </c>
+      <c r="N374" t="n">
+        <v>1</v>
+      </c>
+      <c r="O374" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15826,6 +18074,12 @@
         <v>1</v>
       </c>
       <c r="M375" t="n">
+        <v>0</v>
+      </c>
+      <c r="N375" t="n">
+        <v>5</v>
+      </c>
+      <c r="O375" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15867,6 +18121,12 @@
         <v>6</v>
       </c>
       <c r="M376" t="n">
+        <v>0</v>
+      </c>
+      <c r="N376" t="n">
+        <v>8</v>
+      </c>
+      <c r="O376" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15908,6 +18168,12 @@
         <v>3</v>
       </c>
       <c r="M377" t="n">
+        <v>0</v>
+      </c>
+      <c r="N377" t="n">
+        <v>6</v>
+      </c>
+      <c r="O377" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15949,6 +18215,12 @@
         <v>0</v>
       </c>
       <c r="M378" t="n">
+        <v>0</v>
+      </c>
+      <c r="N378" t="n">
+        <v>4</v>
+      </c>
+      <c r="O378" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -15990,6 +18262,12 @@
         <v>6</v>
       </c>
       <c r="M379" t="n">
+        <v>0</v>
+      </c>
+      <c r="N379" t="n">
+        <v>1</v>
+      </c>
+      <c r="O379" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -16031,6 +18309,12 @@
         <v>2</v>
       </c>
       <c r="M380" t="n">
+        <v>0</v>
+      </c>
+      <c r="N380" t="n">
+        <v>0</v>
+      </c>
+      <c r="O380" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -16072,6 +18356,12 @@
         <v>1</v>
       </c>
       <c r="M381" t="n">
+        <v>0</v>
+      </c>
+      <c r="N381" t="n">
+        <v>0</v>
+      </c>
+      <c r="O381" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -16113,6 +18403,12 @@
         <v>1</v>
       </c>
       <c r="M382" t="n">
+        <v>0</v>
+      </c>
+      <c r="N382" t="n">
+        <v>0</v>
+      </c>
+      <c r="O382" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -16154,6 +18450,12 @@
         <v>10</v>
       </c>
       <c r="M383" t="n">
+        <v>0</v>
+      </c>
+      <c r="N383" t="n">
+        <v>2</v>
+      </c>
+      <c r="O383" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -16195,6 +18497,12 @@
         <v>3</v>
       </c>
       <c r="M384" t="n">
+        <v>0</v>
+      </c>
+      <c r="N384" t="n">
+        <v>5</v>
+      </c>
+      <c r="O384" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -16236,6 +18544,12 @@
         <v>1</v>
       </c>
       <c r="M385" t="n">
+        <v>1</v>
+      </c>
+      <c r="N385" t="n">
+        <v>0</v>
+      </c>
+      <c r="O385" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -16277,6 +18591,12 @@
         <v>4</v>
       </c>
       <c r="M386" t="n">
+        <v>0</v>
+      </c>
+      <c r="N386" t="n">
+        <v>0</v>
+      </c>
+      <c r="O386" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -16318,6 +18638,12 @@
         <v>6</v>
       </c>
       <c r="M387" t="n">
+        <v>0</v>
+      </c>
+      <c r="N387" t="n">
+        <v>1</v>
+      </c>
+      <c r="O387" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -16359,6 +18685,12 @@
         <v>4</v>
       </c>
       <c r="M388" t="n">
+        <v>1</v>
+      </c>
+      <c r="N388" t="n">
+        <v>0</v>
+      </c>
+      <c r="O388" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -16400,6 +18732,12 @@
         <v>3</v>
       </c>
       <c r="M389" t="n">
+        <v>0</v>
+      </c>
+      <c r="N389" t="n">
+        <v>1</v>
+      </c>
+      <c r="O389" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -16441,6 +18779,12 @@
         <v>0</v>
       </c>
       <c r="M390" t="n">
+        <v>0</v>
+      </c>
+      <c r="N390" t="n">
+        <v>0</v>
+      </c>
+      <c r="O390" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -16482,6 +18826,12 @@
         <v>1</v>
       </c>
       <c r="M391" t="n">
+        <v>0</v>
+      </c>
+      <c r="N391" t="n">
+        <v>0</v>
+      </c>
+      <c r="O391" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -16523,6 +18873,12 @@
         <v>3</v>
       </c>
       <c r="M392" t="n">
+        <v>0</v>
+      </c>
+      <c r="N392" t="n">
+        <v>3</v>
+      </c>
+      <c r="O392" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -16564,6 +18920,12 @@
         <v>3</v>
       </c>
       <c r="M393" t="n">
+        <v>0</v>
+      </c>
+      <c r="N393" t="n">
+        <v>5</v>
+      </c>
+      <c r="O393" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -16605,6 +18967,12 @@
         <v>4</v>
       </c>
       <c r="M394" t="n">
+        <v>1</v>
+      </c>
+      <c r="N394" t="n">
+        <v>2</v>
+      </c>
+      <c r="O394" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -16646,6 +19014,12 @@
         <v>4</v>
       </c>
       <c r="M395" t="n">
+        <v>1</v>
+      </c>
+      <c r="N395" t="n">
+        <v>7</v>
+      </c>
+      <c r="O395" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -16687,6 +19061,12 @@
         <v>1</v>
       </c>
       <c r="M396" t="n">
+        <v>0</v>
+      </c>
+      <c r="N396" t="n">
+        <v>1</v>
+      </c>
+      <c r="O396" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -16728,6 +19108,12 @@
         <v>3</v>
       </c>
       <c r="M397" t="n">
+        <v>0</v>
+      </c>
+      <c r="N397" t="n">
+        <v>1</v>
+      </c>
+      <c r="O397" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -16769,6 +19155,12 @@
         <v>1</v>
       </c>
       <c r="M398" t="n">
+        <v>0</v>
+      </c>
+      <c r="N398" t="n">
+        <v>11</v>
+      </c>
+      <c r="O398" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -16810,6 +19202,12 @@
         <v>0</v>
       </c>
       <c r="M399" t="n">
+        <v>0</v>
+      </c>
+      <c r="N399" t="n">
+        <v>0</v>
+      </c>
+      <c r="O399" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -16851,6 +19249,12 @@
         <v>4</v>
       </c>
       <c r="M400" t="n">
+        <v>0</v>
+      </c>
+      <c r="N400" t="n">
+        <v>2</v>
+      </c>
+      <c r="O400" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -16892,6 +19296,12 @@
         <v>4</v>
       </c>
       <c r="M401" t="n">
+        <v>0</v>
+      </c>
+      <c r="N401" t="n">
+        <v>4</v>
+      </c>
+      <c r="O401" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -16933,6 +19343,12 @@
         <v>16</v>
       </c>
       <c r="M402" t="n">
+        <v>0</v>
+      </c>
+      <c r="N402" t="n">
+        <v>4</v>
+      </c>
+      <c r="O402" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -16974,6 +19390,12 @@
         <v>14</v>
       </c>
       <c r="M403" t="n">
+        <v>0</v>
+      </c>
+      <c r="N403" t="n">
+        <v>2</v>
+      </c>
+      <c r="O403" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -17015,6 +19437,12 @@
         <v>0</v>
       </c>
       <c r="M404" t="n">
+        <v>0</v>
+      </c>
+      <c r="N404" t="n">
+        <v>0</v>
+      </c>
+      <c r="O404" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -17056,6 +19484,12 @@
         <v>0</v>
       </c>
       <c r="M405" t="n">
+        <v>0</v>
+      </c>
+      <c r="N405" t="n">
+        <v>0</v>
+      </c>
+      <c r="O405" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -17097,6 +19531,12 @@
         <v>8</v>
       </c>
       <c r="M406" t="n">
+        <v>0</v>
+      </c>
+      <c r="N406" t="n">
+        <v>1</v>
+      </c>
+      <c r="O406" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -17138,6 +19578,12 @@
         <v>7</v>
       </c>
       <c r="M407" t="n">
+        <v>0</v>
+      </c>
+      <c r="N407" t="n">
+        <v>0</v>
+      </c>
+      <c r="O407" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -17179,6 +19625,12 @@
         <v>0</v>
       </c>
       <c r="M408" t="n">
+        <v>0</v>
+      </c>
+      <c r="N408" t="n">
+        <v>0</v>
+      </c>
+      <c r="O408" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -17220,6 +19672,12 @@
         <v>6</v>
       </c>
       <c r="M409" t="n">
+        <v>0</v>
+      </c>
+      <c r="N409" t="n">
+        <v>1</v>
+      </c>
+      <c r="O409" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -17261,6 +19719,12 @@
         <v>21</v>
       </c>
       <c r="M410" t="n">
+        <v>0</v>
+      </c>
+      <c r="N410" t="n">
+        <v>10</v>
+      </c>
+      <c r="O410" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -17302,6 +19766,12 @@
         <v>3</v>
       </c>
       <c r="M411" t="n">
+        <v>0</v>
+      </c>
+      <c r="N411" t="n">
+        <v>0</v>
+      </c>
+      <c r="O411" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -17343,6 +19813,12 @@
         <v>5</v>
       </c>
       <c r="M412" t="n">
+        <v>0</v>
+      </c>
+      <c r="N412" t="n">
+        <v>0</v>
+      </c>
+      <c r="O412" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -17384,6 +19860,12 @@
         <v>7</v>
       </c>
       <c r="M413" t="n">
+        <v>0</v>
+      </c>
+      <c r="N413" t="n">
+        <v>3</v>
+      </c>
+      <c r="O413" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -17425,6 +19907,12 @@
         <v>2</v>
       </c>
       <c r="M414" t="n">
+        <v>0</v>
+      </c>
+      <c r="N414" t="n">
+        <v>0</v>
+      </c>
+      <c r="O414" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -17466,6 +19954,12 @@
         <v>0</v>
       </c>
       <c r="M415" t="n">
+        <v>0</v>
+      </c>
+      <c r="N415" t="n">
+        <v>4</v>
+      </c>
+      <c r="O415" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -17507,6 +20001,12 @@
         <v>0</v>
       </c>
       <c r="M416" t="n">
+        <v>0</v>
+      </c>
+      <c r="N416" t="n">
+        <v>0</v>
+      </c>
+      <c r="O416" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -17548,6 +20048,12 @@
         <v>1</v>
       </c>
       <c r="M417" t="n">
+        <v>1</v>
+      </c>
+      <c r="N417" t="n">
+        <v>0</v>
+      </c>
+      <c r="O417" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -17589,6 +20095,12 @@
         <v>14</v>
       </c>
       <c r="M418" t="n">
+        <v>1</v>
+      </c>
+      <c r="N418" t="n">
+        <v>4</v>
+      </c>
+      <c r="O418" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -17630,6 +20142,12 @@
         <v>1</v>
       </c>
       <c r="M419" t="n">
+        <v>1</v>
+      </c>
+      <c r="N419" t="n">
+        <v>6</v>
+      </c>
+      <c r="O419" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -17671,6 +20189,12 @@
         <v>10</v>
       </c>
       <c r="M420" t="n">
+        <v>0</v>
+      </c>
+      <c r="N420" t="n">
+        <v>10</v>
+      </c>
+      <c r="O420" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -17712,6 +20236,12 @@
         <v>0</v>
       </c>
       <c r="M421" t="n">
+        <v>0</v>
+      </c>
+      <c r="N421" t="n">
+        <v>0</v>
+      </c>
+      <c r="O421" t="n">
         <v>2015</v>
       </c>
     </row>
@@ -17753,6 +20283,12 @@
         <v>1</v>
       </c>
       <c r="M422" t="n">
+        <v>0</v>
+      </c>
+      <c r="N422" t="n">
+        <v>1</v>
+      </c>
+      <c r="O422" t="n">
         <v>2015</v>
       </c>
     </row>

--- a/Excel Files IPEDS/Trimmed/c2015_trimmed_file.xlsx
+++ b/Excel Files IPEDS/Trimmed/c2015_trimmed_file.xlsx
@@ -14,99 +14,102 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
-    <t>UNITID</t>
+    <t>unitid</t>
   </si>
   <si>
-    <t>CIPCODE</t>
+    <t>cipcode</t>
   </si>
   <si>
-    <t>CTOTALT</t>
+    <t>ctotalt</t>
   </si>
   <si>
-    <t>AWLEVEL</t>
+    <t>awlevel</t>
   </si>
   <si>
-    <t>CTOTALM</t>
+    <t>ctotalm</t>
   </si>
   <si>
-    <t>CTOTALW</t>
+    <t>ctotalw</t>
   </si>
   <si>
-    <t>CUNKNT</t>
+    <t>cunknt</t>
   </si>
   <si>
-    <t>CBKAAT</t>
+    <t>cbkaat</t>
   </si>
   <si>
-    <t>CASIAT</t>
+    <t>casiat</t>
   </si>
   <si>
-    <t>CNHPIT</t>
+    <t>cnhpit</t>
   </si>
   <si>
-    <t>CHISPT</t>
+    <t>chispt</t>
   </si>
   <si>
-    <t>CWHITT</t>
+    <t>cwhitt</t>
   </si>
   <si>
-    <t>C2MORT</t>
+    <t>c2mort</t>
   </si>
   <si>
-    <t>CNRALT</t>
+    <t>cnralt</t>
   </si>
   <si>
-    <t>CBKAAM</t>
+    <t>cbkaam</t>
   </si>
   <si>
-    <t>CASIAM</t>
+    <t>casiam</t>
   </si>
   <si>
-    <t>CNHPIM</t>
+    <t>cnhpim</t>
   </si>
   <si>
-    <t>CHISPM</t>
+    <t>chispm</t>
   </si>
   <si>
-    <t>CWHITM</t>
+    <t>cwhitm</t>
   </si>
   <si>
-    <t>CUNKNM</t>
+    <t>cunknm</t>
   </si>
   <si>
-    <t>C2MORM</t>
+    <t>c2morm</t>
   </si>
   <si>
-    <t>CNRALM</t>
+    <t>cnralm</t>
   </si>
   <si>
-    <t>CBKAAW</t>
+    <t>cbkaaw</t>
   </si>
   <si>
-    <t>CASIAW</t>
+    <t>casiaw</t>
   </si>
   <si>
-    <t>CNHPIW</t>
+    <t>cnhpiw</t>
   </si>
   <si>
-    <t>CHISPW</t>
+    <t>chispw</t>
   </si>
   <si>
-    <t>CWHITW</t>
+    <t>cwhitw</t>
   </si>
   <si>
-    <t>CUNKNW</t>
+    <t>cunknw</t>
   </si>
   <si>
-    <t>C2MORW</t>
+    <t>c2morw</t>
   </si>
   <si>
-    <t>CNRALW</t>
+    <t>cnralw</t>
   </si>
   <si>
-    <t>Year</t>
+    <t>majornum</t>
+  </si>
+  <si>
+    <t>year</t>
   </si>
 </sst>
 </file>
@@ -464,10 +467,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE422"/>
+  <dimension ref="A1:AF422"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:32">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -561,8 +564,11 @@
       <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:31">
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32">
       <c r="A2">
         <v>100654</v>
       </c>
@@ -654,10 +660,13 @@
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF2">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32">
       <c r="A3">
         <v>100663</v>
       </c>
@@ -749,10 +758,13 @@
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF3">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32">
       <c r="A4">
         <v>100663</v>
       </c>
@@ -844,10 +856,13 @@
         <v>0</v>
       </c>
       <c r="AE4">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF4">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32">
       <c r="A5">
         <v>100706</v>
       </c>
@@ -939,10 +954,13 @@
         <v>1</v>
       </c>
       <c r="AE5">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="6" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF5">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32">
       <c r="A6">
         <v>100706</v>
       </c>
@@ -1034,10 +1052,13 @@
         <v>1</v>
       </c>
       <c r="AE6">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="7" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF6">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32">
       <c r="A7">
         <v>100751</v>
       </c>
@@ -1129,10 +1150,13 @@
         <v>0</v>
       </c>
       <c r="AE7">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF7">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32">
       <c r="A8">
         <v>100751</v>
       </c>
@@ -1224,10 +1248,13 @@
         <v>1</v>
       </c>
       <c r="AE8">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF8">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32">
       <c r="A9">
         <v>100858</v>
       </c>
@@ -1319,10 +1346,13 @@
         <v>0</v>
       </c>
       <c r="AE9">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF9">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32">
       <c r="A10">
         <v>100858</v>
       </c>
@@ -1414,10 +1444,13 @@
         <v>0</v>
       </c>
       <c r="AE10">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF10">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32">
       <c r="A11">
         <v>102614</v>
       </c>
@@ -1509,10 +1542,13 @@
         <v>0</v>
       </c>
       <c r="AE11">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="12" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF11">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32">
       <c r="A12">
         <v>102614</v>
       </c>
@@ -1604,10 +1640,13 @@
         <v>0</v>
       </c>
       <c r="AE12">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="13" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF12">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32">
       <c r="A13">
         <v>104151</v>
       </c>
@@ -1699,10 +1738,13 @@
         <v>0</v>
       </c>
       <c r="AE13">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="14" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF13">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32">
       <c r="A14">
         <v>104151</v>
       </c>
@@ -1794,10 +1836,13 @@
         <v>1</v>
       </c>
       <c r="AE14">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF14">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32">
       <c r="A15">
         <v>104179</v>
       </c>
@@ -1889,10 +1934,13 @@
         <v>0</v>
       </c>
       <c r="AE15">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="16" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF15">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32">
       <c r="A16">
         <v>104179</v>
       </c>
@@ -1984,10 +2032,13 @@
         <v>0</v>
       </c>
       <c r="AE16">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="17" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF16">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32">
       <c r="A17">
         <v>105330</v>
       </c>
@@ -2079,10 +2130,13 @@
         <v>0</v>
       </c>
       <c r="AE17">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="18" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF17">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32">
       <c r="A18">
         <v>106397</v>
       </c>
@@ -2174,10 +2228,13 @@
         <v>3</v>
       </c>
       <c r="AE18">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="19" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF18">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="19" spans="1:32">
       <c r="A19">
         <v>106397</v>
       </c>
@@ -2269,10 +2326,13 @@
         <v>0</v>
       </c>
       <c r="AE19">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="20" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF19">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32">
       <c r="A20">
         <v>110404</v>
       </c>
@@ -2364,10 +2424,13 @@
         <v>0</v>
       </c>
       <c r="AE20">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="21" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF20">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32">
       <c r="A21">
         <v>110404</v>
       </c>
@@ -2459,10 +2522,13 @@
         <v>2</v>
       </c>
       <c r="AE21">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="22" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF21">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32">
       <c r="A22">
         <v>110422</v>
       </c>
@@ -2554,10 +2620,13 @@
         <v>0</v>
       </c>
       <c r="AE22">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="23" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF22">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32">
       <c r="A23">
         <v>110422</v>
       </c>
@@ -2649,10 +2718,13 @@
         <v>0</v>
       </c>
       <c r="AE23">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="24" spans="1:31">
+        <v>2</v>
+      </c>
+      <c r="AF23">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32">
       <c r="A24">
         <v>110556</v>
       </c>
@@ -2744,10 +2816,13 @@
         <v>0</v>
       </c>
       <c r="AE24">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="25" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF24">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="25" spans="1:32">
       <c r="A25">
         <v>110565</v>
       </c>
@@ -2839,10 +2914,13 @@
         <v>0</v>
       </c>
       <c r="AE25">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="26" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF25">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="26" spans="1:32">
       <c r="A26">
         <v>110583</v>
       </c>
@@ -2934,10 +3012,13 @@
         <v>0</v>
       </c>
       <c r="AE26">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="27" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF26">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="27" spans="1:32">
       <c r="A27">
         <v>110592</v>
       </c>
@@ -3029,10 +3110,13 @@
         <v>0</v>
       </c>
       <c r="AE27">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="28" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF27">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="28" spans="1:32">
       <c r="A28">
         <v>110608</v>
       </c>
@@ -3124,10 +3208,13 @@
         <v>1</v>
       </c>
       <c r="AE28">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="29" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF28">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="29" spans="1:32">
       <c r="A29">
         <v>110635</v>
       </c>
@@ -3219,10 +3306,13 @@
         <v>0</v>
       </c>
       <c r="AE29">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="30" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF29">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="30" spans="1:32">
       <c r="A30">
         <v>110635</v>
       </c>
@@ -3314,10 +3404,13 @@
         <v>1</v>
       </c>
       <c r="AE30">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="31" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF30">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="31" spans="1:32">
       <c r="A31">
         <v>110644</v>
       </c>
@@ -3409,10 +3502,13 @@
         <v>0</v>
       </c>
       <c r="AE31">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="32" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF31">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="32" spans="1:32">
       <c r="A32">
         <v>110644</v>
       </c>
@@ -3504,10 +3600,13 @@
         <v>1</v>
       </c>
       <c r="AE32">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="33" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF32">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="33" spans="1:32">
       <c r="A33">
         <v>110653</v>
       </c>
@@ -3599,10 +3698,13 @@
         <v>0</v>
       </c>
       <c r="AE33">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="34" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF33">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="34" spans="1:32">
       <c r="A34">
         <v>110653</v>
       </c>
@@ -3694,10 +3796,13 @@
         <v>0</v>
       </c>
       <c r="AE34">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="35" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF34">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="35" spans="1:32">
       <c r="A35">
         <v>110662</v>
       </c>
@@ -3789,10 +3894,13 @@
         <v>1</v>
       </c>
       <c r="AE35">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="36" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF35">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="36" spans="1:32">
       <c r="A36">
         <v>110662</v>
       </c>
@@ -3884,10 +3992,13 @@
         <v>1</v>
       </c>
       <c r="AE36">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="37" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF36">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="37" spans="1:32">
       <c r="A37">
         <v>110671</v>
       </c>
@@ -3979,10 +4090,13 @@
         <v>1</v>
       </c>
       <c r="AE37">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="38" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF37">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="38" spans="1:32">
       <c r="A38">
         <v>110671</v>
       </c>
@@ -4074,10 +4188,13 @@
         <v>0</v>
       </c>
       <c r="AE38">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="39" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF38">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="39" spans="1:32">
       <c r="A39">
         <v>110680</v>
       </c>
@@ -4169,10 +4286,13 @@
         <v>0</v>
       </c>
       <c r="AE39">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="40" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF39">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="40" spans="1:32">
       <c r="A40">
         <v>110680</v>
       </c>
@@ -4264,10 +4384,13 @@
         <v>3</v>
       </c>
       <c r="AE40">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="41" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF40">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="41" spans="1:32">
       <c r="A41">
         <v>110705</v>
       </c>
@@ -4359,10 +4482,13 @@
         <v>0</v>
       </c>
       <c r="AE41">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="42" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF41">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="42" spans="1:32">
       <c r="A42">
         <v>110705</v>
       </c>
@@ -4454,10 +4580,13 @@
         <v>1</v>
       </c>
       <c r="AE42">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="43" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF42">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="43" spans="1:32">
       <c r="A43">
         <v>110714</v>
       </c>
@@ -4549,10 +4678,13 @@
         <v>1</v>
       </c>
       <c r="AE43">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="44" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF43">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="44" spans="1:32">
       <c r="A44">
         <v>110714</v>
       </c>
@@ -4644,10 +4776,13 @@
         <v>0</v>
       </c>
       <c r="AE44">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="45" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF44">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="45" spans="1:32">
       <c r="A45">
         <v>119678</v>
       </c>
@@ -4739,10 +4874,13 @@
         <v>0</v>
       </c>
       <c r="AE45">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="46" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF45">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="46" spans="1:32">
       <c r="A46">
         <v>119678</v>
       </c>
@@ -4834,10 +4972,13 @@
         <v>0</v>
       </c>
       <c r="AE46">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="47" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF46">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="47" spans="1:32">
       <c r="A47">
         <v>122409</v>
       </c>
@@ -4929,10 +5070,13 @@
         <v>0</v>
       </c>
       <c r="AE47">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="48" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF47">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="48" spans="1:32">
       <c r="A48">
         <v>122597</v>
       </c>
@@ -5024,10 +5168,13 @@
         <v>1</v>
       </c>
       <c r="AE48">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="49" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF48">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="49" spans="1:32">
       <c r="A49">
         <v>122755</v>
       </c>
@@ -5119,10 +5266,13 @@
         <v>0</v>
       </c>
       <c r="AE49">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="50" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF49">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="50" spans="1:32">
       <c r="A50">
         <v>123961</v>
       </c>
@@ -5214,10 +5364,13 @@
         <v>1</v>
       </c>
       <c r="AE50">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="51" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF50">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="51" spans="1:32">
       <c r="A51">
         <v>123961</v>
       </c>
@@ -5309,10 +5462,13 @@
         <v>1</v>
       </c>
       <c r="AE51">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="52" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF51">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="52" spans="1:32">
       <c r="A52">
         <v>126614</v>
       </c>
@@ -5404,10 +5560,13 @@
         <v>0</v>
       </c>
       <c r="AE52">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="53" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF52">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="53" spans="1:32">
       <c r="A53">
         <v>126614</v>
       </c>
@@ -5499,10 +5658,13 @@
         <v>2</v>
       </c>
       <c r="AE53">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="54" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF53">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="54" spans="1:32">
       <c r="A54">
         <v>126775</v>
       </c>
@@ -5594,10 +5756,13 @@
         <v>0</v>
       </c>
       <c r="AE54">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="55" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF54">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="55" spans="1:32">
       <c r="A55">
         <v>126818</v>
       </c>
@@ -5689,10 +5854,13 @@
         <v>0</v>
       </c>
       <c r="AE55">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="56" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF55">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="56" spans="1:32">
       <c r="A56">
         <v>126818</v>
       </c>
@@ -5784,10 +5952,13 @@
         <v>0</v>
       </c>
       <c r="AE56">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="57" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF56">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="57" spans="1:32">
       <c r="A57">
         <v>127060</v>
       </c>
@@ -5879,10 +6050,13 @@
         <v>0</v>
       </c>
       <c r="AE57">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="58" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF57">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="58" spans="1:32">
       <c r="A58">
         <v>127060</v>
       </c>
@@ -5974,10 +6148,13 @@
         <v>0</v>
       </c>
       <c r="AE58">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="59" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF58">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="59" spans="1:32">
       <c r="A59">
         <v>129020</v>
       </c>
@@ -6069,10 +6246,13 @@
         <v>0</v>
       </c>
       <c r="AE59">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="60" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF59">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="60" spans="1:32">
       <c r="A60">
         <v>129020</v>
       </c>
@@ -6164,10 +6344,13 @@
         <v>1</v>
       </c>
       <c r="AE60">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="61" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF60">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="61" spans="1:32">
       <c r="A61">
         <v>130697</v>
       </c>
@@ -6259,10 +6442,13 @@
         <v>0</v>
       </c>
       <c r="AE61">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="62" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF61">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="62" spans="1:32">
       <c r="A62">
         <v>130697</v>
       </c>
@@ -6354,10 +6540,13 @@
         <v>0</v>
       </c>
       <c r="AE62">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="63" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF62">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="63" spans="1:32">
       <c r="A63">
         <v>130794</v>
       </c>
@@ -6449,10 +6638,13 @@
         <v>5</v>
       </c>
       <c r="AE63">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="64" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF63">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="64" spans="1:32">
       <c r="A64">
         <v>130794</v>
       </c>
@@ -6544,10 +6736,13 @@
         <v>0</v>
       </c>
       <c r="AE64">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="65" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF64">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="65" spans="1:32">
       <c r="A65">
         <v>130934</v>
       </c>
@@ -6639,10 +6834,13 @@
         <v>0</v>
       </c>
       <c r="AE65">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="66" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF65">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="66" spans="1:32">
       <c r="A66">
         <v>130943</v>
       </c>
@@ -6734,10 +6932,13 @@
         <v>0</v>
       </c>
       <c r="AE66">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="67" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF66">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="67" spans="1:32">
       <c r="A67">
         <v>130943</v>
       </c>
@@ -6829,10 +7030,13 @@
         <v>2</v>
       </c>
       <c r="AE67">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="68" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF67">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="68" spans="1:32">
       <c r="A68">
         <v>131283</v>
       </c>
@@ -6924,10 +7128,13 @@
         <v>1</v>
       </c>
       <c r="AE68">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="69" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF68">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="69" spans="1:32">
       <c r="A69">
         <v>131283</v>
       </c>
@@ -7019,10 +7226,13 @@
         <v>0</v>
       </c>
       <c r="AE69">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="70" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF69">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="70" spans="1:32">
       <c r="A70">
         <v>131469</v>
       </c>
@@ -7114,10 +7324,13 @@
         <v>0</v>
       </c>
       <c r="AE70">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="71" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF70">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="71" spans="1:32">
       <c r="A71">
         <v>131469</v>
       </c>
@@ -7209,10 +7422,13 @@
         <v>0</v>
       </c>
       <c r="AE71">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="72" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF71">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="72" spans="1:32">
       <c r="A72">
         <v>131496</v>
       </c>
@@ -7304,10 +7520,13 @@
         <v>0</v>
       </c>
       <c r="AE72">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="73" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF72">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="73" spans="1:32">
       <c r="A73">
         <v>131496</v>
       </c>
@@ -7399,10 +7618,13 @@
         <v>1</v>
       </c>
       <c r="AE73">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="74" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF73">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="74" spans="1:32">
       <c r="A74">
         <v>131520</v>
       </c>
@@ -7494,10 +7716,13 @@
         <v>0</v>
       </c>
       <c r="AE74">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="75" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF74">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="75" spans="1:32">
       <c r="A75">
         <v>131520</v>
       </c>
@@ -7589,10 +7814,13 @@
         <v>0</v>
       </c>
       <c r="AE75">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="76" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF75">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="76" spans="1:32">
       <c r="A76">
         <v>132903</v>
       </c>
@@ -7684,10 +7912,13 @@
         <v>2</v>
       </c>
       <c r="AE76">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="77" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF76">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="77" spans="1:32">
       <c r="A77">
         <v>132903</v>
       </c>
@@ -7779,10 +8010,13 @@
         <v>1</v>
       </c>
       <c r="AE77">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="78" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF77">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="78" spans="1:32">
       <c r="A78">
         <v>133650</v>
       </c>
@@ -7874,10 +8108,13 @@
         <v>0</v>
       </c>
       <c r="AE78">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="79" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF78">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="79" spans="1:32">
       <c r="A79">
         <v>133650</v>
       </c>
@@ -7969,10 +8206,13 @@
         <v>0</v>
       </c>
       <c r="AE79">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="80" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF79">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="80" spans="1:32">
       <c r="A80">
         <v>133669</v>
       </c>
@@ -8064,10 +8304,13 @@
         <v>1</v>
       </c>
       <c r="AE80">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="81" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF80">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="81" spans="1:32">
       <c r="A81">
         <v>133669</v>
       </c>
@@ -8159,10 +8402,13 @@
         <v>0</v>
       </c>
       <c r="AE81">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="82" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF81">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="82" spans="1:32">
       <c r="A82">
         <v>133881</v>
       </c>
@@ -8254,10 +8500,13 @@
         <v>0</v>
       </c>
       <c r="AE82">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="83" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF82">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="83" spans="1:32">
       <c r="A83">
         <v>133881</v>
       </c>
@@ -8349,10 +8598,13 @@
         <v>1</v>
       </c>
       <c r="AE83">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="84" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF83">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="84" spans="1:32">
       <c r="A84">
         <v>133951</v>
       </c>
@@ -8444,10 +8696,13 @@
         <v>0</v>
       </c>
       <c r="AE84">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="85" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF84">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="85" spans="1:32">
       <c r="A85">
         <v>133951</v>
       </c>
@@ -8539,10 +8794,13 @@
         <v>0</v>
       </c>
       <c r="AE85">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="86" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF85">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="86" spans="1:32">
       <c r="A86">
         <v>134097</v>
       </c>
@@ -8634,10 +8892,13 @@
         <v>9</v>
       </c>
       <c r="AE86">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="87" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF86">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="87" spans="1:32">
       <c r="A87">
         <v>134097</v>
       </c>
@@ -8729,10 +8990,13 @@
         <v>0</v>
       </c>
       <c r="AE87">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="88" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF87">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="88" spans="1:32">
       <c r="A88">
         <v>134130</v>
       </c>
@@ -8824,10 +9088,13 @@
         <v>1</v>
       </c>
       <c r="AE88">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="89" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF88">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="89" spans="1:32">
       <c r="A89">
         <v>134130</v>
       </c>
@@ -8919,10 +9186,13 @@
         <v>2</v>
       </c>
       <c r="AE89">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="90" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF89">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="90" spans="1:32">
       <c r="A90">
         <v>135726</v>
       </c>
@@ -9014,10 +9284,13 @@
         <v>0</v>
       </c>
       <c r="AE90">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="91" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF90">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="91" spans="1:32">
       <c r="A91">
         <v>137351</v>
       </c>
@@ -9109,10 +9382,13 @@
         <v>1</v>
       </c>
       <c r="AE91">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="92" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF91">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="92" spans="1:32">
       <c r="A92">
         <v>137351</v>
       </c>
@@ -9204,10 +9480,13 @@
         <v>0</v>
       </c>
       <c r="AE92">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="93" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF92">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="93" spans="1:32">
       <c r="A93">
         <v>138947</v>
       </c>
@@ -9299,10 +9578,13 @@
         <v>0</v>
       </c>
       <c r="AE93">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="94" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF93">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="94" spans="1:32">
       <c r="A94">
         <v>139658</v>
       </c>
@@ -9394,10 +9676,13 @@
         <v>0</v>
       </c>
       <c r="AE94">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="95" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF94">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="95" spans="1:32">
       <c r="A95">
         <v>139658</v>
       </c>
@@ -9489,10 +9774,13 @@
         <v>1</v>
       </c>
       <c r="AE95">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="96" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF95">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="96" spans="1:32">
       <c r="A96">
         <v>139755</v>
       </c>
@@ -9584,10 +9872,13 @@
         <v>1</v>
       </c>
       <c r="AE96">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="97" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF96">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="97" spans="1:32">
       <c r="A97">
         <v>139755</v>
       </c>
@@ -9679,10 +9970,13 @@
         <v>1</v>
       </c>
       <c r="AE97">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="98" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF97">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="98" spans="1:32">
       <c r="A98">
         <v>139940</v>
       </c>
@@ -9774,10 +10068,13 @@
         <v>1</v>
       </c>
       <c r="AE98">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="99" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF98">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="99" spans="1:32">
       <c r="A99">
         <v>139940</v>
       </c>
@@ -9869,10 +10166,13 @@
         <v>2</v>
       </c>
       <c r="AE99">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="100" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF99">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="100" spans="1:32">
       <c r="A100">
         <v>139959</v>
       </c>
@@ -9964,10 +10264,13 @@
         <v>1</v>
       </c>
       <c r="AE100">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="101" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF100">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="101" spans="1:32">
       <c r="A101">
         <v>139959</v>
       </c>
@@ -10059,10 +10362,13 @@
         <v>0</v>
       </c>
       <c r="AE101">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="102" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF101">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="102" spans="1:32">
       <c r="A102">
         <v>141574</v>
       </c>
@@ -10154,10 +10460,13 @@
         <v>0</v>
       </c>
       <c r="AE102">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="103" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF102">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="103" spans="1:32">
       <c r="A103">
         <v>141574</v>
       </c>
@@ -10249,10 +10558,13 @@
         <v>0</v>
       </c>
       <c r="AE103">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="104" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF103">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="104" spans="1:32">
       <c r="A104">
         <v>142276</v>
       </c>
@@ -10344,10 +10656,13 @@
         <v>1</v>
       </c>
       <c r="AE104">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="105" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF104">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="105" spans="1:32">
       <c r="A105">
         <v>142276</v>
       </c>
@@ -10439,10 +10754,13 @@
         <v>0</v>
       </c>
       <c r="AE105">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="106" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF105">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="106" spans="1:32">
       <c r="A106">
         <v>142285</v>
       </c>
@@ -10534,10 +10852,13 @@
         <v>0</v>
       </c>
       <c r="AE106">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="107" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF106">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="107" spans="1:32">
       <c r="A107">
         <v>142285</v>
       </c>
@@ -10629,10 +10950,13 @@
         <v>0</v>
       </c>
       <c r="AE107">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="108" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF107">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="108" spans="1:32">
       <c r="A108">
         <v>142285</v>
       </c>
@@ -10724,10 +11048,13 @@
         <v>0</v>
       </c>
       <c r="AE108">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="109" spans="1:31">
+        <v>2</v>
+      </c>
+      <c r="AF108">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="109" spans="1:32">
       <c r="A109">
         <v>142285</v>
       </c>
@@ -10819,10 +11146,13 @@
         <v>0</v>
       </c>
       <c r="AE109">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="110" spans="1:31">
+        <v>2</v>
+      </c>
+      <c r="AF109">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="110" spans="1:32">
       <c r="A110">
         <v>144050</v>
       </c>
@@ -10914,10 +11244,13 @@
         <v>1</v>
       </c>
       <c r="AE110">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="111" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF110">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="111" spans="1:32">
       <c r="A111">
         <v>144050</v>
       </c>
@@ -11009,10 +11342,13 @@
         <v>2</v>
       </c>
       <c r="AE111">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="112" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF111">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="112" spans="1:32">
       <c r="A112">
         <v>144740</v>
       </c>
@@ -11104,10 +11440,13 @@
         <v>0</v>
       </c>
       <c r="AE112">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="113" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF112">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="113" spans="1:32">
       <c r="A113">
         <v>145600</v>
       </c>
@@ -11199,10 +11538,13 @@
         <v>1</v>
       </c>
       <c r="AE113">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="114" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF113">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="114" spans="1:32">
       <c r="A114">
         <v>145600</v>
       </c>
@@ -11294,10 +11636,13 @@
         <v>0</v>
       </c>
       <c r="AE114">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="115" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF114">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="115" spans="1:32">
       <c r="A115">
         <v>145637</v>
       </c>
@@ -11389,10 +11734,13 @@
         <v>4</v>
       </c>
       <c r="AE115">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="116" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF115">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="116" spans="1:32">
       <c r="A116">
         <v>145637</v>
       </c>
@@ -11484,10 +11832,13 @@
         <v>2</v>
       </c>
       <c r="AE116">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="117" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF116">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="117" spans="1:32">
       <c r="A117">
         <v>145725</v>
       </c>
@@ -11579,10 +11930,13 @@
         <v>2</v>
       </c>
       <c r="AE117">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="118" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF117">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="118" spans="1:32">
       <c r="A118">
         <v>145725</v>
       </c>
@@ -11674,10 +12028,13 @@
         <v>1</v>
       </c>
       <c r="AE118">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="119" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF118">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="119" spans="1:32">
       <c r="A119">
         <v>147703</v>
       </c>
@@ -11769,10 +12126,13 @@
         <v>1</v>
       </c>
       <c r="AE119">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="120" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF119">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="120" spans="1:32">
       <c r="A120">
         <v>147703</v>
       </c>
@@ -11864,10 +12224,13 @@
         <v>0</v>
       </c>
       <c r="AE120">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="121" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF120">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="121" spans="1:32">
       <c r="A121">
         <v>149222</v>
       </c>
@@ -11959,10 +12322,13 @@
         <v>1</v>
       </c>
       <c r="AE121">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="122" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF121">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="122" spans="1:32">
       <c r="A122">
         <v>149222</v>
       </c>
@@ -12054,10 +12420,13 @@
         <v>0</v>
       </c>
       <c r="AE122">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="123" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF122">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="123" spans="1:32">
       <c r="A123">
         <v>149772</v>
       </c>
@@ -12149,10 +12518,13 @@
         <v>6</v>
       </c>
       <c r="AE123">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="124" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF123">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="124" spans="1:32">
       <c r="A124">
         <v>150136</v>
       </c>
@@ -12244,10 +12616,13 @@
         <v>1</v>
       </c>
       <c r="AE124">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="125" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF124">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="125" spans="1:32">
       <c r="A125">
         <v>151111</v>
       </c>
@@ -12339,10 +12714,13 @@
         <v>0</v>
       </c>
       <c r="AE125">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="126" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF125">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="126" spans="1:32">
       <c r="A126">
         <v>151351</v>
       </c>
@@ -12434,10 +12812,13 @@
         <v>1</v>
       </c>
       <c r="AE126">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="127" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF126">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="127" spans="1:32">
       <c r="A127">
         <v>151351</v>
       </c>
@@ -12529,10 +12910,13 @@
         <v>3</v>
       </c>
       <c r="AE127">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="128" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF127">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="128" spans="1:32">
       <c r="A128">
         <v>152080</v>
       </c>
@@ -12624,10 +13008,13 @@
         <v>4</v>
       </c>
       <c r="AE128">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="129" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF128">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="129" spans="1:32">
       <c r="A129">
         <v>152080</v>
       </c>
@@ -12719,10 +13106,13 @@
         <v>1</v>
       </c>
       <c r="AE129">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="130" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF129">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="130" spans="1:32">
       <c r="A130">
         <v>153603</v>
       </c>
@@ -12814,10 +13204,13 @@
         <v>1</v>
       </c>
       <c r="AE130">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="131" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF130">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="131" spans="1:32">
       <c r="A131">
         <v>153658</v>
       </c>
@@ -12909,10 +13302,13 @@
         <v>1</v>
       </c>
       <c r="AE131">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="132" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF131">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="132" spans="1:32">
       <c r="A132">
         <v>153658</v>
       </c>
@@ -13004,10 +13400,13 @@
         <v>2</v>
       </c>
       <c r="AE132">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="133" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF132">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="133" spans="1:32">
       <c r="A133">
         <v>155317</v>
       </c>
@@ -13099,10 +13498,13 @@
         <v>1</v>
       </c>
       <c r="AE133">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="134" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF133">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="134" spans="1:32">
       <c r="A134">
         <v>155317</v>
       </c>
@@ -13194,10 +13596,13 @@
         <v>0</v>
       </c>
       <c r="AE134">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="135" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF134">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="135" spans="1:32">
       <c r="A135">
         <v>155399</v>
       </c>
@@ -13289,10 +13694,13 @@
         <v>1</v>
       </c>
       <c r="AE135">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="136" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF135">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="136" spans="1:32">
       <c r="A136">
         <v>155399</v>
       </c>
@@ -13384,10 +13792,13 @@
         <v>2</v>
       </c>
       <c r="AE136">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="137" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF136">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="137" spans="1:32">
       <c r="A137">
         <v>155681</v>
       </c>
@@ -13479,10 +13890,13 @@
         <v>2</v>
       </c>
       <c r="AE137">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="138" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF137">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="138" spans="1:32">
       <c r="A138">
         <v>157085</v>
       </c>
@@ -13574,10 +13988,13 @@
         <v>0</v>
       </c>
       <c r="AE138">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="139" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF138">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="139" spans="1:32">
       <c r="A139">
         <v>157085</v>
       </c>
@@ -13669,10 +14086,13 @@
         <v>1</v>
       </c>
       <c r="AE139">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="140" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF139">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="140" spans="1:32">
       <c r="A140">
         <v>157289</v>
       </c>
@@ -13764,10 +14184,13 @@
         <v>0</v>
       </c>
       <c r="AE140">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="141" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF140">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="141" spans="1:32">
       <c r="A141">
         <v>157289</v>
       </c>
@@ -13859,10 +14282,13 @@
         <v>1</v>
       </c>
       <c r="AE141">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="142" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF141">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="142" spans="1:32">
       <c r="A142">
         <v>159391</v>
       </c>
@@ -13954,10 +14380,13 @@
         <v>0</v>
       </c>
       <c r="AE142">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="143" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF142">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="143" spans="1:32">
       <c r="A143">
         <v>159391</v>
       </c>
@@ -14049,10 +14478,13 @@
         <v>1</v>
       </c>
       <c r="AE143">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="144" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF143">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="144" spans="1:32">
       <c r="A144">
         <v>159647</v>
       </c>
@@ -14144,10 +14576,13 @@
         <v>1</v>
       </c>
       <c r="AE144">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="145" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF144">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="145" spans="1:32">
       <c r="A145">
         <v>159939</v>
       </c>
@@ -14239,10 +14674,13 @@
         <v>0</v>
       </c>
       <c r="AE145">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="146" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF145">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="146" spans="1:32">
       <c r="A146">
         <v>160621</v>
       </c>
@@ -14334,10 +14772,13 @@
         <v>0</v>
       </c>
       <c r="AE146">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="147" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF146">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="147" spans="1:32">
       <c r="A147">
         <v>160658</v>
       </c>
@@ -14429,10 +14870,13 @@
         <v>0</v>
       </c>
       <c r="AE147">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="148" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF147">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="148" spans="1:32">
       <c r="A148">
         <v>160755</v>
       </c>
@@ -14524,10 +14968,13 @@
         <v>0</v>
       </c>
       <c r="AE148">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="149" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF148">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="149" spans="1:32">
       <c r="A149">
         <v>160755</v>
       </c>
@@ -14619,10 +15066,13 @@
         <v>0</v>
       </c>
       <c r="AE149">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="150" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF149">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="150" spans="1:32">
       <c r="A150">
         <v>161253</v>
       </c>
@@ -14714,10 +15164,13 @@
         <v>0</v>
       </c>
       <c r="AE150">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="151" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF150">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="151" spans="1:32">
       <c r="A151">
         <v>161253</v>
       </c>
@@ -14809,10 +15262,13 @@
         <v>0</v>
       </c>
       <c r="AE151">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="152" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF151">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="152" spans="1:32">
       <c r="A152">
         <v>161253</v>
       </c>
@@ -14904,10 +15360,13 @@
         <v>0</v>
       </c>
       <c r="AE152">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="153" spans="1:31">
+        <v>2</v>
+      </c>
+      <c r="AF152">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="153" spans="1:32">
       <c r="A153">
         <v>162928</v>
       </c>
@@ -14999,10 +15458,13 @@
         <v>0</v>
       </c>
       <c r="AE153">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="154" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF153">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="154" spans="1:32">
       <c r="A154">
         <v>162928</v>
       </c>
@@ -15094,10 +15556,13 @@
         <v>0</v>
       </c>
       <c r="AE154">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="155" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF154">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="155" spans="1:32">
       <c r="A155">
         <v>163268</v>
       </c>
@@ -15189,10 +15654,13 @@
         <v>1</v>
       </c>
       <c r="AE155">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="156" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF155">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="156" spans="1:32">
       <c r="A156">
         <v>163268</v>
       </c>
@@ -15284,10 +15752,13 @@
         <v>1</v>
       </c>
       <c r="AE156">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="157" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF156">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="157" spans="1:32">
       <c r="A157">
         <v>163286</v>
       </c>
@@ -15379,10 +15850,13 @@
         <v>1</v>
       </c>
       <c r="AE157">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="158" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF157">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="158" spans="1:32">
       <c r="A158">
         <v>163286</v>
       </c>
@@ -15474,10 +15948,13 @@
         <v>0</v>
       </c>
       <c r="AE158">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="159" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF158">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="159" spans="1:32">
       <c r="A159">
         <v>164924</v>
       </c>
@@ -15569,10 +16046,13 @@
         <v>1</v>
       </c>
       <c r="AE159">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="160" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF159">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="160" spans="1:32">
       <c r="A160">
         <v>164924</v>
       </c>
@@ -15664,10 +16144,13 @@
         <v>2</v>
       </c>
       <c r="AE160">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="161" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF160">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="161" spans="1:32">
       <c r="A161">
         <v>164988</v>
       </c>
@@ -15759,10 +16242,13 @@
         <v>1</v>
       </c>
       <c r="AE161">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="162" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF161">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="162" spans="1:32">
       <c r="A162">
         <v>164988</v>
       </c>
@@ -15854,10 +16340,13 @@
         <v>1</v>
       </c>
       <c r="AE162">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="163" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF162">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="163" spans="1:32">
       <c r="A163">
         <v>165015</v>
       </c>
@@ -15949,10 +16438,13 @@
         <v>0</v>
       </c>
       <c r="AE163">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="164" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF163">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="164" spans="1:32">
       <c r="A164">
         <v>165015</v>
       </c>
@@ -16044,10 +16536,13 @@
         <v>0</v>
       </c>
       <c r="AE164">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="165" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF164">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="165" spans="1:32">
       <c r="A165">
         <v>165334</v>
       </c>
@@ -16139,10 +16634,13 @@
         <v>0</v>
       </c>
       <c r="AE165">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="166" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF165">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="166" spans="1:32">
       <c r="A166">
         <v>165334</v>
       </c>
@@ -16234,10 +16732,13 @@
         <v>0</v>
       </c>
       <c r="AE166">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="167" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF166">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="167" spans="1:32">
       <c r="A167">
         <v>166027</v>
       </c>
@@ -16329,10 +16830,13 @@
         <v>6</v>
       </c>
       <c r="AE167">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="168" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF167">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="168" spans="1:32">
       <c r="A168">
         <v>166027</v>
       </c>
@@ -16424,10 +16928,13 @@
         <v>2</v>
       </c>
       <c r="AE168">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="169" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF168">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="169" spans="1:32">
       <c r="A169">
         <v>166513</v>
       </c>
@@ -16519,10 +17026,13 @@
         <v>4</v>
       </c>
       <c r="AE169">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="170" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF169">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="170" spans="1:32">
       <c r="A170">
         <v>166513</v>
       </c>
@@ -16614,10 +17124,13 @@
         <v>3</v>
       </c>
       <c r="AE170">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="171" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF170">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="171" spans="1:32">
       <c r="A171">
         <v>166629</v>
       </c>
@@ -16709,10 +17222,13 @@
         <v>0</v>
       </c>
       <c r="AE171">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="172" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF171">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="172" spans="1:32">
       <c r="A172">
         <v>166629</v>
       </c>
@@ -16804,10 +17320,13 @@
         <v>1</v>
       </c>
       <c r="AE172">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="173" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF172">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="173" spans="1:32">
       <c r="A173">
         <v>166638</v>
       </c>
@@ -16899,10 +17418,13 @@
         <v>0</v>
       </c>
       <c r="AE173">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="174" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF173">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="174" spans="1:32">
       <c r="A174">
         <v>166683</v>
       </c>
@@ -16994,10 +17516,13 @@
         <v>1</v>
       </c>
       <c r="AE174">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="175" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF174">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="175" spans="1:32">
       <c r="A175">
         <v>166683</v>
       </c>
@@ -17089,10 +17614,13 @@
         <v>4</v>
       </c>
       <c r="AE175">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="176" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF175">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="176" spans="1:32">
       <c r="A176">
         <v>167358</v>
       </c>
@@ -17184,10 +17712,13 @@
         <v>3</v>
       </c>
       <c r="AE176">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="177" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF176">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="177" spans="1:32">
       <c r="A177">
         <v>167358</v>
       </c>
@@ -17279,10 +17810,13 @@
         <v>3</v>
       </c>
       <c r="AE177">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="178" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF177">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="178" spans="1:32">
       <c r="A178">
         <v>167987</v>
       </c>
@@ -17374,10 +17908,13 @@
         <v>0</v>
       </c>
       <c r="AE178">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="179" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF178">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="179" spans="1:32">
       <c r="A179">
         <v>168148</v>
       </c>
@@ -17469,10 +18006,13 @@
         <v>0</v>
       </c>
       <c r="AE179">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="180" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF179">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="180" spans="1:32">
       <c r="A180">
         <v>168148</v>
       </c>
@@ -17564,10 +18104,13 @@
         <v>1</v>
       </c>
       <c r="AE180">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="181" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF180">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="181" spans="1:32">
       <c r="A181">
         <v>168421</v>
       </c>
@@ -17659,10 +18202,13 @@
         <v>0</v>
       </c>
       <c r="AE181">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="182" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF181">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="182" spans="1:32">
       <c r="A182">
         <v>168421</v>
       </c>
@@ -17754,10 +18300,13 @@
         <v>0</v>
       </c>
       <c r="AE182">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="183" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF182">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="183" spans="1:32">
       <c r="A183">
         <v>169248</v>
       </c>
@@ -17849,10 +18398,13 @@
         <v>0</v>
       </c>
       <c r="AE183">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="184" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF183">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="184" spans="1:32">
       <c r="A184">
         <v>169798</v>
       </c>
@@ -17944,10 +18496,13 @@
         <v>0</v>
       </c>
       <c r="AE184">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="185" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF184">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="185" spans="1:32">
       <c r="A185">
         <v>170976</v>
       </c>
@@ -18039,10 +18594,13 @@
         <v>0</v>
       </c>
       <c r="AE185">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="186" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF185">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="186" spans="1:32">
       <c r="A186">
         <v>170976</v>
       </c>
@@ -18134,10 +18692,13 @@
         <v>3</v>
       </c>
       <c r="AE186">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="187" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF186">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="187" spans="1:32">
       <c r="A187">
         <v>171100</v>
       </c>
@@ -18229,10 +18790,13 @@
         <v>0</v>
       </c>
       <c r="AE187">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="188" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF187">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="188" spans="1:32">
       <c r="A188">
         <v>171100</v>
       </c>
@@ -18324,10 +18888,13 @@
         <v>4</v>
       </c>
       <c r="AE188">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="189" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF188">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="189" spans="1:32">
       <c r="A189">
         <v>171128</v>
       </c>
@@ -18419,10 +18986,13 @@
         <v>0</v>
       </c>
       <c r="AE189">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="190" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF189">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="190" spans="1:32">
       <c r="A190">
         <v>171128</v>
       </c>
@@ -18514,10 +19084,13 @@
         <v>0</v>
       </c>
       <c r="AE190">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="191" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF190">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="191" spans="1:32">
       <c r="A191">
         <v>171571</v>
       </c>
@@ -18609,10 +19182,13 @@
         <v>0</v>
       </c>
       <c r="AE191">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="192" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF191">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="192" spans="1:32">
       <c r="A192">
         <v>172644</v>
       </c>
@@ -18704,10 +19280,13 @@
         <v>2</v>
       </c>
       <c r="AE192">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="193" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF192">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="193" spans="1:32">
       <c r="A193">
         <v>172644</v>
       </c>
@@ -18799,10 +19378,13 @@
         <v>1</v>
       </c>
       <c r="AE193">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="194" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF193">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="194" spans="1:32">
       <c r="A194">
         <v>172699</v>
       </c>
@@ -18894,10 +19476,13 @@
         <v>2</v>
       </c>
       <c r="AE194">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="195" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF194">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="195" spans="1:32">
       <c r="A195">
         <v>172699</v>
       </c>
@@ -18989,10 +19574,13 @@
         <v>2</v>
       </c>
       <c r="AE195">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="196" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF195">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="196" spans="1:32">
       <c r="A196">
         <v>173920</v>
       </c>
@@ -19084,10 +19672,13 @@
         <v>0</v>
       </c>
       <c r="AE196">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="197" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF196">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="197" spans="1:32">
       <c r="A197">
         <v>174066</v>
       </c>
@@ -19179,10 +19770,13 @@
         <v>0</v>
       </c>
       <c r="AE197">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="198" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF197">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="198" spans="1:32">
       <c r="A198">
         <v>174066</v>
       </c>
@@ -19274,10 +19868,13 @@
         <v>4</v>
       </c>
       <c r="AE198">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="199" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF198">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="199" spans="1:32">
       <c r="A199">
         <v>174233</v>
       </c>
@@ -19369,10 +19966,13 @@
         <v>0</v>
       </c>
       <c r="AE199">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="200" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF199">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="200" spans="1:32">
       <c r="A200">
         <v>176017</v>
       </c>
@@ -19464,10 +20064,13 @@
         <v>2</v>
       </c>
       <c r="AE200">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="201" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF200">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="201" spans="1:32">
       <c r="A201">
         <v>176017</v>
       </c>
@@ -19559,10 +20162,13 @@
         <v>2</v>
       </c>
       <c r="AE201">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="202" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF201">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="202" spans="1:32">
       <c r="A202">
         <v>176080</v>
       </c>
@@ -19654,10 +20260,13 @@
         <v>1</v>
       </c>
       <c r="AE202">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="203" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF202">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="203" spans="1:32">
       <c r="A203">
         <v>176372</v>
       </c>
@@ -19749,10 +20358,13 @@
         <v>0</v>
       </c>
       <c r="AE203">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="204" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF203">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="204" spans="1:32">
       <c r="A204">
         <v>178396</v>
       </c>
@@ -19844,10 +20456,13 @@
         <v>3</v>
       </c>
       <c r="AE204">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="205" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF204">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="205" spans="1:32">
       <c r="A205">
         <v>178396</v>
       </c>
@@ -19939,10 +20554,13 @@
         <v>1</v>
       </c>
       <c r="AE205">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="206" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF205">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="206" spans="1:32">
       <c r="A206">
         <v>178402</v>
       </c>
@@ -20034,10 +20652,13 @@
         <v>0</v>
       </c>
       <c r="AE206">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="207" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF206">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="207" spans="1:32">
       <c r="A207">
         <v>178411</v>
       </c>
@@ -20129,10 +20750,13 @@
         <v>0</v>
       </c>
       <c r="AE207">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="208" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF207">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="208" spans="1:32">
       <c r="A208">
         <v>178411</v>
       </c>
@@ -20224,10 +20848,13 @@
         <v>0</v>
       </c>
       <c r="AE208">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="209" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF208">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="209" spans="1:32">
       <c r="A209">
         <v>178420</v>
       </c>
@@ -20319,10 +20946,13 @@
         <v>1</v>
       </c>
       <c r="AE209">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="210" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF209">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="210" spans="1:32">
       <c r="A210">
         <v>178420</v>
       </c>
@@ -20414,10 +21044,13 @@
         <v>0</v>
       </c>
       <c r="AE210">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="211" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF210">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="211" spans="1:32">
       <c r="A211">
         <v>179867</v>
       </c>
@@ -20509,10 +21142,13 @@
         <v>2</v>
       </c>
       <c r="AE211">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="212" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF211">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="212" spans="1:32">
       <c r="A212">
         <v>179867</v>
       </c>
@@ -20604,10 +21240,13 @@
         <v>1</v>
       </c>
       <c r="AE212">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="213" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF212">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="213" spans="1:32">
       <c r="A213">
         <v>180461</v>
       </c>
@@ -20699,10 +21338,13 @@
         <v>0</v>
       </c>
       <c r="AE213">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="214" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF213">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="214" spans="1:32">
       <c r="A214">
         <v>180461</v>
       </c>
@@ -20794,10 +21436,13 @@
         <v>0</v>
       </c>
       <c r="AE214">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="215" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF214">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="215" spans="1:32">
       <c r="A215">
         <v>181002</v>
       </c>
@@ -20889,10 +21534,13 @@
         <v>0</v>
       </c>
       <c r="AE215">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="216" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF215">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="216" spans="1:32">
       <c r="A216">
         <v>181464</v>
       </c>
@@ -20984,10 +21632,13 @@
         <v>1</v>
       </c>
       <c r="AE216">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="217" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF216">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="217" spans="1:32">
       <c r="A217">
         <v>181464</v>
       </c>
@@ -21079,10 +21730,13 @@
         <v>1</v>
       </c>
       <c r="AE217">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="218" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF217">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="218" spans="1:32">
       <c r="A218">
         <v>182281</v>
       </c>
@@ -21174,10 +21828,13 @@
         <v>0</v>
       </c>
       <c r="AE218">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="219" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF218">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="219" spans="1:32">
       <c r="A219">
         <v>182281</v>
       </c>
@@ -21269,10 +21926,13 @@
         <v>1</v>
       </c>
       <c r="AE219">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="220" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF219">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="220" spans="1:32">
       <c r="A220">
         <v>182290</v>
       </c>
@@ -21364,10 +22024,13 @@
         <v>0</v>
       </c>
       <c r="AE220">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="221" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF220">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="221" spans="1:32">
       <c r="A221">
         <v>182290</v>
       </c>
@@ -21459,10 +22122,13 @@
         <v>0</v>
       </c>
       <c r="AE221">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="222" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF221">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="222" spans="1:32">
       <c r="A222">
         <v>182670</v>
       </c>
@@ -21554,10 +22220,13 @@
         <v>0</v>
       </c>
       <c r="AE222">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="223" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF222">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="223" spans="1:32">
       <c r="A223">
         <v>182670</v>
       </c>
@@ -21649,10 +22318,13 @@
         <v>1</v>
       </c>
       <c r="AE223">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="224" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF223">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="224" spans="1:32">
       <c r="A224">
         <v>183044</v>
       </c>
@@ -21744,10 +22416,13 @@
         <v>0</v>
       </c>
       <c r="AE224">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="225" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF224">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="225" spans="1:32">
       <c r="A225">
         <v>183044</v>
       </c>
@@ -21839,10 +22514,13 @@
         <v>0</v>
       </c>
       <c r="AE225">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="226" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF225">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="226" spans="1:32">
       <c r="A226">
         <v>185828</v>
       </c>
@@ -21934,10 +22612,13 @@
         <v>1</v>
       </c>
       <c r="AE226">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="227" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF226">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="227" spans="1:32">
       <c r="A227">
         <v>185828</v>
       </c>
@@ -22029,10 +22710,13 @@
         <v>0</v>
       </c>
       <c r="AE227">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="228" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF227">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="228" spans="1:32">
       <c r="A228">
         <v>186131</v>
       </c>
@@ -22124,10 +22808,13 @@
         <v>1</v>
       </c>
       <c r="AE228">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="229" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF228">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="229" spans="1:32">
       <c r="A229">
         <v>186131</v>
       </c>
@@ -22219,10 +22906,13 @@
         <v>1</v>
       </c>
       <c r="AE229">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="230" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF229">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="230" spans="1:32">
       <c r="A230">
         <v>186399</v>
       </c>
@@ -22314,10 +23004,13 @@
         <v>0</v>
       </c>
       <c r="AE230">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="231" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF230">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="231" spans="1:32">
       <c r="A231">
         <v>186399</v>
       </c>
@@ -22409,10 +23102,13 @@
         <v>0</v>
       </c>
       <c r="AE231">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="232" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF231">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="232" spans="1:32">
       <c r="A232">
         <v>186867</v>
       </c>
@@ -22504,10 +23200,13 @@
         <v>0</v>
       </c>
       <c r="AE232">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="233" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF232">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="233" spans="1:32">
       <c r="A233">
         <v>186867</v>
       </c>
@@ -22599,10 +23298,13 @@
         <v>1</v>
       </c>
       <c r="AE233">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="234" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF233">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="234" spans="1:32">
       <c r="A234">
         <v>187967</v>
       </c>
@@ -22694,10 +23396,13 @@
         <v>1</v>
       </c>
       <c r="AE234">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="235" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF234">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="235" spans="1:32">
       <c r="A235">
         <v>187967</v>
       </c>
@@ -22789,10 +23494,13 @@
         <v>0</v>
       </c>
       <c r="AE235">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="236" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF235">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="236" spans="1:32">
       <c r="A236">
         <v>187985</v>
       </c>
@@ -22884,10 +23592,13 @@
         <v>0</v>
       </c>
       <c r="AE236">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="237" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF236">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="237" spans="1:32">
       <c r="A237">
         <v>187985</v>
       </c>
@@ -22979,10 +23690,13 @@
         <v>0</v>
       </c>
       <c r="AE237">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="238" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF237">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="238" spans="1:32">
       <c r="A238">
         <v>188030</v>
       </c>
@@ -23074,10 +23788,13 @@
         <v>0</v>
       </c>
       <c r="AE238">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="239" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF238">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="239" spans="1:32">
       <c r="A239">
         <v>188030</v>
       </c>
@@ -23169,10 +23886,13 @@
         <v>2</v>
       </c>
       <c r="AE239">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="240" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF239">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="240" spans="1:32">
       <c r="A240">
         <v>190044</v>
       </c>
@@ -23264,10 +23984,13 @@
         <v>1</v>
       </c>
       <c r="AE240">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="241" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF240">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="241" spans="1:32">
       <c r="A241">
         <v>190044</v>
       </c>
@@ -23359,10 +24082,13 @@
         <v>0</v>
       </c>
       <c r="AE241">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="242" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF241">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="242" spans="1:32">
       <c r="A242">
         <v>190150</v>
       </c>
@@ -23454,10 +24180,13 @@
         <v>1</v>
       </c>
       <c r="AE242">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="243" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF242">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="243" spans="1:32">
       <c r="A243">
         <v>190150</v>
       </c>
@@ -23549,10 +24278,13 @@
         <v>2</v>
       </c>
       <c r="AE243">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="244" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF243">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="244" spans="1:32">
       <c r="A244">
         <v>190415</v>
       </c>
@@ -23644,10 +24376,13 @@
         <v>2</v>
       </c>
       <c r="AE244">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="245" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF244">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="245" spans="1:32">
       <c r="A245">
         <v>190415</v>
       </c>
@@ -23739,10 +24474,13 @@
         <v>0</v>
       </c>
       <c r="AE245">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="246" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF245">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="246" spans="1:32">
       <c r="A246">
         <v>190549</v>
       </c>
@@ -23834,10 +24572,13 @@
         <v>1</v>
       </c>
       <c r="AE246">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="247" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF246">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="247" spans="1:32">
       <c r="A247">
         <v>190567</v>
       </c>
@@ -23929,10 +24670,13 @@
         <v>1</v>
       </c>
       <c r="AE247">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="248" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF247">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="248" spans="1:32">
       <c r="A248">
         <v>190576</v>
       </c>
@@ -24024,10 +24768,13 @@
         <v>1</v>
       </c>
       <c r="AE248">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="249" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF248">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="249" spans="1:32">
       <c r="A249">
         <v>190576</v>
       </c>
@@ -24119,10 +24866,13 @@
         <v>2</v>
       </c>
       <c r="AE249">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="250" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF249">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="250" spans="1:32">
       <c r="A250">
         <v>190594</v>
       </c>
@@ -24214,10 +24964,13 @@
         <v>1</v>
       </c>
       <c r="AE250">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="251" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF250">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="251" spans="1:32">
       <c r="A251">
         <v>190594</v>
       </c>
@@ -24309,10 +25062,13 @@
         <v>0</v>
       </c>
       <c r="AE251">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="252" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF251">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="252" spans="1:32">
       <c r="A252">
         <v>190664</v>
       </c>
@@ -24404,10 +25160,13 @@
         <v>1</v>
       </c>
       <c r="AE252">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="253" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF252">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="253" spans="1:32">
       <c r="A253">
         <v>193900</v>
       </c>
@@ -24499,10 +25258,13 @@
         <v>17</v>
       </c>
       <c r="AE253">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="254" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF253">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="254" spans="1:32">
       <c r="A254">
         <v>193900</v>
       </c>
@@ -24594,10 +25356,13 @@
         <v>0</v>
       </c>
       <c r="AE254">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="255" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF254">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="255" spans="1:32">
       <c r="A255">
         <v>194824</v>
       </c>
@@ -24689,10 +25454,13 @@
         <v>0</v>
       </c>
       <c r="AE255">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="256" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF255">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="256" spans="1:32">
       <c r="A256">
         <v>194824</v>
       </c>
@@ -24784,10 +25552,13 @@
         <v>1</v>
       </c>
       <c r="AE256">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="257" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF256">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="257" spans="1:32">
       <c r="A257">
         <v>195030</v>
       </c>
@@ -24879,10 +25650,13 @@
         <v>1</v>
       </c>
       <c r="AE257">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="258" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF257">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="258" spans="1:32">
       <c r="A258">
         <v>195030</v>
       </c>
@@ -24974,10 +25748,13 @@
         <v>0</v>
       </c>
       <c r="AE258">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="259" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF258">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="259" spans="1:32">
       <c r="A259">
         <v>195030</v>
       </c>
@@ -25069,10 +25846,13 @@
         <v>0</v>
       </c>
       <c r="AE259">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="260" spans="1:31">
+        <v>2</v>
+      </c>
+      <c r="AF259">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="260" spans="1:32">
       <c r="A260">
         <v>196060</v>
       </c>
@@ -25164,10 +25944,13 @@
         <v>0</v>
       </c>
       <c r="AE260">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="261" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF260">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="261" spans="1:32">
       <c r="A261">
         <v>196060</v>
       </c>
@@ -25259,10 +26042,13 @@
         <v>2</v>
       </c>
       <c r="AE261">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="262" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF261">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="262" spans="1:32">
       <c r="A262">
         <v>196079</v>
       </c>
@@ -25354,10 +26140,13 @@
         <v>0</v>
       </c>
       <c r="AE262">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="263" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF262">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="263" spans="1:32">
       <c r="A263">
         <v>196079</v>
       </c>
@@ -25449,10 +26238,13 @@
         <v>1</v>
       </c>
       <c r="AE263">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="264" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF263">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="264" spans="1:32">
       <c r="A264">
         <v>196088</v>
       </c>
@@ -25544,10 +26336,13 @@
         <v>2</v>
       </c>
       <c r="AE264">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="265" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF264">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="265" spans="1:32">
       <c r="A265">
         <v>196088</v>
       </c>
@@ -25639,10 +26434,13 @@
         <v>0</v>
       </c>
       <c r="AE265">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="266" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF265">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="266" spans="1:32">
       <c r="A266">
         <v>196097</v>
       </c>
@@ -25734,10 +26532,13 @@
         <v>2</v>
       </c>
       <c r="AE266">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="267" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF266">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="267" spans="1:32">
       <c r="A267">
         <v>196097</v>
       </c>
@@ -25829,10 +26630,13 @@
         <v>3</v>
       </c>
       <c r="AE267">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="268" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF267">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="268" spans="1:32">
       <c r="A268">
         <v>196413</v>
       </c>
@@ -25924,10 +26728,13 @@
         <v>0</v>
       </c>
       <c r="AE268">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="269" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF268">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="269" spans="1:32">
       <c r="A269">
         <v>196413</v>
       </c>
@@ -26019,10 +26826,13 @@
         <v>1</v>
       </c>
       <c r="AE269">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="270" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF269">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="270" spans="1:32">
       <c r="A270">
         <v>197869</v>
       </c>
@@ -26114,10 +26924,13 @@
         <v>0</v>
       </c>
       <c r="AE270">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="271" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF270">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="271" spans="1:32">
       <c r="A271">
         <v>198419</v>
       </c>
@@ -26209,10 +27022,13 @@
         <v>0</v>
       </c>
       <c r="AE271">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="272" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF271">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="272" spans="1:32">
       <c r="A272">
         <v>198419</v>
       </c>
@@ -26304,10 +27120,13 @@
         <v>1</v>
       </c>
       <c r="AE272">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="273" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF272">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="273" spans="1:32">
       <c r="A273">
         <v>198464</v>
       </c>
@@ -26399,10 +27218,13 @@
         <v>0</v>
       </c>
       <c r="AE273">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="274" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF273">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="274" spans="1:32">
       <c r="A274">
         <v>199102</v>
       </c>
@@ -26494,10 +27316,13 @@
         <v>0</v>
       </c>
       <c r="AE274">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="275" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF274">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="275" spans="1:32">
       <c r="A275">
         <v>199120</v>
       </c>
@@ -26589,10 +27414,13 @@
         <v>0</v>
       </c>
       <c r="AE275">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="276" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF275">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="276" spans="1:32">
       <c r="A276">
         <v>199120</v>
       </c>
@@ -26684,10 +27512,13 @@
         <v>0</v>
       </c>
       <c r="AE276">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="277" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF276">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="277" spans="1:32">
       <c r="A277">
         <v>199139</v>
       </c>
@@ -26779,10 +27610,13 @@
         <v>0</v>
       </c>
       <c r="AE277">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="278" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF277">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="278" spans="1:32">
       <c r="A278">
         <v>199157</v>
       </c>
@@ -26874,10 +27708,13 @@
         <v>1</v>
       </c>
       <c r="AE278">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="279" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF278">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="279" spans="1:32">
       <c r="A279">
         <v>199193</v>
       </c>
@@ -26969,10 +27806,13 @@
         <v>1</v>
       </c>
       <c r="AE279">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="280" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF279">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="280" spans="1:32">
       <c r="A280">
         <v>199193</v>
       </c>
@@ -27064,10 +27904,13 @@
         <v>0</v>
       </c>
       <c r="AE280">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="281" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF280">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="281" spans="1:32">
       <c r="A281">
         <v>199847</v>
       </c>
@@ -27159,10 +28002,13 @@
         <v>0</v>
       </c>
       <c r="AE281">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="282" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF281">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="282" spans="1:32">
       <c r="A282">
         <v>199847</v>
       </c>
@@ -27254,10 +28100,13 @@
         <v>1</v>
       </c>
       <c r="AE282">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="283" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF282">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="283" spans="1:32">
       <c r="A283">
         <v>200280</v>
       </c>
@@ -27349,10 +28198,13 @@
         <v>0</v>
       </c>
       <c r="AE283">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="284" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF283">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="284" spans="1:32">
       <c r="A284">
         <v>200280</v>
       </c>
@@ -27444,10 +28296,13 @@
         <v>0</v>
       </c>
       <c r="AE284">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="285" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF284">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="285" spans="1:32">
       <c r="A285">
         <v>200332</v>
       </c>
@@ -27539,10 +28394,13 @@
         <v>0</v>
       </c>
       <c r="AE285">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="286" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF285">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="286" spans="1:32">
       <c r="A286">
         <v>200332</v>
       </c>
@@ -27634,10 +28492,13 @@
         <v>0</v>
       </c>
       <c r="AE286">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="287" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF286">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="287" spans="1:32">
       <c r="A287">
         <v>200800</v>
       </c>
@@ -27729,10 +28590,13 @@
         <v>2</v>
       </c>
       <c r="AE287">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="288" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF287">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="288" spans="1:32">
       <c r="A288">
         <v>201441</v>
       </c>
@@ -27824,10 +28688,13 @@
         <v>0</v>
       </c>
       <c r="AE288">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="289" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF288">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="289" spans="1:32">
       <c r="A289">
         <v>201645</v>
       </c>
@@ -27919,10 +28786,13 @@
         <v>1</v>
       </c>
       <c r="AE289">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="290" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF289">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="290" spans="1:32">
       <c r="A290">
         <v>201645</v>
       </c>
@@ -28014,10 +28884,13 @@
         <v>0</v>
       </c>
       <c r="AE290">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="291" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF290">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="291" spans="1:32">
       <c r="A291">
         <v>201885</v>
       </c>
@@ -28109,10 +28982,13 @@
         <v>2</v>
       </c>
       <c r="AE291">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="292" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF291">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="292" spans="1:32">
       <c r="A292">
         <v>201885</v>
       </c>
@@ -28204,10 +29080,13 @@
         <v>0</v>
       </c>
       <c r="AE292">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="293" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF292">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="293" spans="1:32">
       <c r="A293">
         <v>202134</v>
       </c>
@@ -28299,10 +29178,13 @@
         <v>1</v>
       </c>
       <c r="AE293">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="294" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF293">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="294" spans="1:32">
       <c r="A294">
         <v>203517</v>
       </c>
@@ -28394,10 +29276,13 @@
         <v>4</v>
       </c>
       <c r="AE294">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="295" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF294">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="295" spans="1:32">
       <c r="A295">
         <v>203517</v>
       </c>
@@ -28489,10 +29374,13 @@
         <v>0</v>
       </c>
       <c r="AE295">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="296" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF295">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="296" spans="1:32">
       <c r="A296">
         <v>204024</v>
       </c>
@@ -28584,10 +29472,13 @@
         <v>0</v>
       </c>
       <c r="AE296">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="297" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF296">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="297" spans="1:32">
       <c r="A297">
         <v>204796</v>
       </c>
@@ -28679,10 +29570,13 @@
         <v>0</v>
       </c>
       <c r="AE297">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="298" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF297">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="298" spans="1:32">
       <c r="A298">
         <v>204796</v>
       </c>
@@ -28774,10 +29668,13 @@
         <v>2</v>
       </c>
       <c r="AE298">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="299" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF298">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="299" spans="1:32">
       <c r="A299">
         <v>204857</v>
       </c>
@@ -28869,10 +29766,13 @@
         <v>2</v>
       </c>
       <c r="AE299">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="300" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF299">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="300" spans="1:32">
       <c r="A300">
         <v>204857</v>
       </c>
@@ -28964,10 +29864,13 @@
         <v>5</v>
       </c>
       <c r="AE300">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="301" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF300">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="301" spans="1:32">
       <c r="A301">
         <v>206084</v>
       </c>
@@ -29059,10 +29962,13 @@
         <v>1</v>
       </c>
       <c r="AE301">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="302" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF301">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="302" spans="1:32">
       <c r="A302">
         <v>206084</v>
       </c>
@@ -29154,10 +30060,13 @@
         <v>1</v>
       </c>
       <c r="AE302">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="303" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF302">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="303" spans="1:32">
       <c r="A303">
         <v>206084</v>
       </c>
@@ -29249,10 +30158,13 @@
         <v>0</v>
       </c>
       <c r="AE303">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="304" spans="1:31">
+        <v>2</v>
+      </c>
+      <c r="AF303">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="304" spans="1:32">
       <c r="A304">
         <v>206604</v>
       </c>
@@ -29344,10 +30256,13 @@
         <v>3</v>
       </c>
       <c r="AE304">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="305" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF304">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="305" spans="1:32">
       <c r="A305">
         <v>207388</v>
       </c>
@@ -29439,10 +30354,13 @@
         <v>0</v>
       </c>
       <c r="AE305">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="306" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF305">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="306" spans="1:32">
       <c r="A306">
         <v>207388</v>
       </c>
@@ -29534,10 +30452,13 @@
         <v>0</v>
       </c>
       <c r="AE306">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="307" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF306">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="307" spans="1:32">
       <c r="A307">
         <v>207500</v>
       </c>
@@ -29629,10 +30550,13 @@
         <v>1</v>
       </c>
       <c r="AE307">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="308" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF307">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="308" spans="1:32">
       <c r="A308">
         <v>207500</v>
       </c>
@@ -29724,10 +30648,13 @@
         <v>1</v>
       </c>
       <c r="AE308">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="309" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF308">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="309" spans="1:32">
       <c r="A309">
         <v>207971</v>
       </c>
@@ -29819,10 +30746,13 @@
         <v>0</v>
       </c>
       <c r="AE309">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="310" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF309">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="310" spans="1:32">
       <c r="A310">
         <v>209542</v>
       </c>
@@ -29914,10 +30844,13 @@
         <v>0</v>
       </c>
       <c r="AE310">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="311" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF310">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="311" spans="1:32">
       <c r="A311">
         <v>209542</v>
       </c>
@@ -30009,10 +30942,13 @@
         <v>1</v>
       </c>
       <c r="AE311">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="312" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF311">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="312" spans="1:32">
       <c r="A312">
         <v>209551</v>
       </c>
@@ -30104,10 +31040,13 @@
         <v>0</v>
       </c>
       <c r="AE312">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="313" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF312">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="313" spans="1:32">
       <c r="A313">
         <v>209551</v>
       </c>
@@ -30199,10 +31138,13 @@
         <v>2</v>
       </c>
       <c r="AE313">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="314" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF313">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="314" spans="1:32">
       <c r="A314">
         <v>209807</v>
       </c>
@@ -30294,10 +31236,13 @@
         <v>1</v>
       </c>
       <c r="AE314">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="315" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF314">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="315" spans="1:32">
       <c r="A315">
         <v>209807</v>
       </c>
@@ -30389,10 +31334,13 @@
         <v>0</v>
       </c>
       <c r="AE315">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="316" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF315">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="316" spans="1:32">
       <c r="A316">
         <v>211273</v>
       </c>
@@ -30484,10 +31432,13 @@
         <v>0</v>
       </c>
       <c r="AE316">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="317" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF316">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="317" spans="1:32">
       <c r="A317">
         <v>211273</v>
       </c>
@@ -30579,10 +31530,13 @@
         <v>0</v>
       </c>
       <c r="AE317">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="318" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF317">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="318" spans="1:32">
       <c r="A318">
         <v>211440</v>
       </c>
@@ -30674,10 +31628,13 @@
         <v>0</v>
       </c>
       <c r="AE318">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="319" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF318">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="319" spans="1:32">
       <c r="A319">
         <v>211440</v>
       </c>
@@ -30769,10 +31726,13 @@
         <v>0</v>
       </c>
       <c r="AE319">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="320" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF319">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="320" spans="1:32">
       <c r="A320">
         <v>213020</v>
       </c>
@@ -30864,10 +31824,13 @@
         <v>0</v>
       </c>
       <c r="AE320">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="321" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF320">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="321" spans="1:32">
       <c r="A321">
         <v>213020</v>
       </c>
@@ -30959,10 +31922,13 @@
         <v>0</v>
       </c>
       <c r="AE321">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="322" spans="1:31">
+        <v>2</v>
+      </c>
+      <c r="AF321">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="322" spans="1:32">
       <c r="A322">
         <v>213543</v>
       </c>
@@ -31054,10 +32020,13 @@
         <v>1</v>
       </c>
       <c r="AE322">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="323" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF322">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="323" spans="1:32">
       <c r="A323">
         <v>213543</v>
       </c>
@@ -31149,10 +32118,13 @@
         <v>0</v>
       </c>
       <c r="AE323">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="324" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF323">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="324" spans="1:32">
       <c r="A324">
         <v>214777</v>
       </c>
@@ -31244,10 +32216,13 @@
         <v>1</v>
       </c>
       <c r="AE324">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="325" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF324">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="325" spans="1:32">
       <c r="A325">
         <v>214777</v>
       </c>
@@ -31339,10 +32314,13 @@
         <v>1</v>
       </c>
       <c r="AE325">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="326" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF325">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="326" spans="1:32">
       <c r="A326">
         <v>215062</v>
       </c>
@@ -31434,10 +32412,13 @@
         <v>1</v>
       </c>
       <c r="AE326">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="327" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF326">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="327" spans="1:32">
       <c r="A327">
         <v>215062</v>
       </c>
@@ -31529,10 +32510,13 @@
         <v>1</v>
       </c>
       <c r="AE327">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="328" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF327">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="328" spans="1:32">
       <c r="A328">
         <v>215293</v>
       </c>
@@ -31624,10 +32608,13 @@
         <v>1</v>
       </c>
       <c r="AE328">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="329" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF328">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="329" spans="1:32">
       <c r="A329">
         <v>215293</v>
       </c>
@@ -31719,10 +32706,13 @@
         <v>2</v>
       </c>
       <c r="AE329">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="330" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF329">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="330" spans="1:32">
       <c r="A330">
         <v>216339</v>
       </c>
@@ -31814,10 +32804,13 @@
         <v>1</v>
       </c>
       <c r="AE330">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="331" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF330">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="331" spans="1:32">
       <c r="A331">
         <v>216339</v>
       </c>
@@ -31909,10 +32902,13 @@
         <v>2</v>
       </c>
       <c r="AE331">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="332" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF331">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="332" spans="1:32">
       <c r="A332">
         <v>217156</v>
       </c>
@@ -32004,10 +33000,13 @@
         <v>0</v>
       </c>
       <c r="AE332">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="333" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF332">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="333" spans="1:32">
       <c r="A333">
         <v>217156</v>
       </c>
@@ -32099,10 +33098,13 @@
         <v>3</v>
       </c>
       <c r="AE333">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="334" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF333">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="334" spans="1:32">
       <c r="A334">
         <v>217484</v>
       </c>
@@ -32194,10 +33196,13 @@
         <v>0</v>
       </c>
       <c r="AE334">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="335" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF334">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="335" spans="1:32">
       <c r="A335">
         <v>217484</v>
       </c>
@@ -32289,10 +33294,13 @@
         <v>0</v>
       </c>
       <c r="AE335">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="336" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF335">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="336" spans="1:32">
       <c r="A336">
         <v>217882</v>
       </c>
@@ -32384,10 +33392,13 @@
         <v>0</v>
       </c>
       <c r="AE336">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="337" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF336">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="337" spans="1:32">
       <c r="A337">
         <v>217882</v>
       </c>
@@ -32479,10 +33490,13 @@
         <v>0</v>
       </c>
       <c r="AE337">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="338" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF337">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="338" spans="1:32">
       <c r="A338">
         <v>218663</v>
       </c>
@@ -32574,10 +33588,13 @@
         <v>0</v>
       </c>
       <c r="AE338">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="339" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF338">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="339" spans="1:32">
       <c r="A339">
         <v>218663</v>
       </c>
@@ -32669,10 +33686,13 @@
         <v>0</v>
       </c>
       <c r="AE339">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="340" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF339">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="340" spans="1:32">
       <c r="A340">
         <v>219347</v>
       </c>
@@ -32764,10 +33784,13 @@
         <v>0</v>
       </c>
       <c r="AE340">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="341" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF340">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="341" spans="1:32">
       <c r="A341">
         <v>219347</v>
       </c>
@@ -32859,10 +33882,13 @@
         <v>0</v>
       </c>
       <c r="AE341">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="342" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF341">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="342" spans="1:32">
       <c r="A342">
         <v>219471</v>
       </c>
@@ -32954,10 +33980,13 @@
         <v>1</v>
       </c>
       <c r="AE342">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="343" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF342">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="343" spans="1:32">
       <c r="A343">
         <v>220181</v>
       </c>
@@ -33049,10 +34078,13 @@
         <v>0</v>
       </c>
       <c r="AE343">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="344" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF343">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="344" spans="1:32">
       <c r="A344">
         <v>220862</v>
       </c>
@@ -33144,10 +34176,13 @@
         <v>0</v>
       </c>
       <c r="AE344">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="345" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF344">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="345" spans="1:32">
       <c r="A345">
         <v>221759</v>
       </c>
@@ -33239,10 +34274,13 @@
         <v>1</v>
       </c>
       <c r="AE345">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="346" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF345">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="346" spans="1:32">
       <c r="A346">
         <v>221759</v>
       </c>
@@ -33334,10 +34372,13 @@
         <v>2</v>
       </c>
       <c r="AE346">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="347" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF346">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="347" spans="1:32">
       <c r="A347">
         <v>221999</v>
       </c>
@@ -33429,10 +34470,13 @@
         <v>0</v>
       </c>
       <c r="AE347">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="348" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF347">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="348" spans="1:32">
       <c r="A348">
         <v>221999</v>
       </c>
@@ -33524,10 +34568,13 @@
         <v>1</v>
       </c>
       <c r="AE348">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="349" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF348">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="349" spans="1:32">
       <c r="A349">
         <v>223232</v>
       </c>
@@ -33619,10 +34666,13 @@
         <v>0</v>
       </c>
       <c r="AE349">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="350" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF349">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="350" spans="1:32">
       <c r="A350">
         <v>223232</v>
       </c>
@@ -33714,10 +34764,13 @@
         <v>1</v>
       </c>
       <c r="AE350">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="351" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF350">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="351" spans="1:32">
       <c r="A351">
         <v>224554</v>
       </c>
@@ -33809,10 +34862,13 @@
         <v>0</v>
       </c>
       <c r="AE351">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="352" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF351">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="352" spans="1:32">
       <c r="A352">
         <v>225414</v>
       </c>
@@ -33904,10 +34960,13 @@
         <v>0</v>
       </c>
       <c r="AE352">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="353" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF352">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="353" spans="1:32">
       <c r="A353">
         <v>225511</v>
       </c>
@@ -33999,10 +35058,13 @@
         <v>1</v>
       </c>
       <c r="AE353">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="354" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF353">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="354" spans="1:32">
       <c r="A354">
         <v>225511</v>
       </c>
@@ -34094,10 +35156,13 @@
         <v>3</v>
       </c>
       <c r="AE354">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="355" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF354">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="355" spans="1:32">
       <c r="A355">
         <v>227216</v>
       </c>
@@ -34189,10 +35254,13 @@
         <v>0</v>
       </c>
       <c r="AE355">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="356" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF355">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="356" spans="1:32">
       <c r="A356">
         <v>227216</v>
       </c>
@@ -34284,10 +35352,13 @@
         <v>2</v>
       </c>
       <c r="AE356">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="357" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF356">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="357" spans="1:32">
       <c r="A357">
         <v>227377</v>
       </c>
@@ -34379,10 +35450,13 @@
         <v>1</v>
       </c>
       <c r="AE357">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="358" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF357">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="358" spans="1:32">
       <c r="A358">
         <v>227757</v>
       </c>
@@ -34474,10 +35548,13 @@
         <v>1</v>
       </c>
       <c r="AE358">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="359" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF358">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="359" spans="1:32">
       <c r="A359">
         <v>227757</v>
       </c>
@@ -34569,10 +35646,13 @@
         <v>2</v>
       </c>
       <c r="AE359">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="360" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF359">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="360" spans="1:32">
       <c r="A360">
         <v>228246</v>
       </c>
@@ -34664,10 +35744,13 @@
         <v>0</v>
       </c>
       <c r="AE360">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="361" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF360">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="361" spans="1:32">
       <c r="A361">
         <v>228246</v>
       </c>
@@ -34759,10 +35842,13 @@
         <v>0</v>
       </c>
       <c r="AE361">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="362" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF361">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="362" spans="1:32">
       <c r="A362">
         <v>228431</v>
       </c>
@@ -34854,10 +35940,13 @@
         <v>0</v>
       </c>
       <c r="AE362">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="363" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF362">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="363" spans="1:32">
       <c r="A363">
         <v>228459</v>
       </c>
@@ -34949,10 +36038,13 @@
         <v>0</v>
       </c>
       <c r="AE363">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="364" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF363">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="364" spans="1:32">
       <c r="A364">
         <v>228723</v>
       </c>
@@ -35044,10 +36136,13 @@
         <v>0</v>
       </c>
       <c r="AE364">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="365" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF364">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="365" spans="1:32">
       <c r="A365">
         <v>228723</v>
       </c>
@@ -35139,10 +36234,13 @@
         <v>0</v>
       </c>
       <c r="AE365">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="366" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF365">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="366" spans="1:32">
       <c r="A366">
         <v>228769</v>
       </c>
@@ -35234,10 +36332,13 @@
         <v>0</v>
       </c>
       <c r="AE366">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="367" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF366">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="367" spans="1:32">
       <c r="A367">
         <v>228769</v>
       </c>
@@ -35329,10 +36430,13 @@
         <v>2</v>
       </c>
       <c r="AE367">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="368" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF367">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="368" spans="1:32">
       <c r="A368">
         <v>228778</v>
       </c>
@@ -35424,10 +36528,13 @@
         <v>1</v>
       </c>
       <c r="AE368">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="369" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF368">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="369" spans="1:32">
       <c r="A369">
         <v>228778</v>
       </c>
@@ -35519,10 +36626,13 @@
         <v>2</v>
       </c>
       <c r="AE369">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="370" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF369">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="370" spans="1:32">
       <c r="A370">
         <v>228787</v>
       </c>
@@ -35614,10 +36724,13 @@
         <v>1</v>
       </c>
       <c r="AE370">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="371" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF370">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="371" spans="1:32">
       <c r="A371">
         <v>228787</v>
       </c>
@@ -35709,10 +36822,13 @@
         <v>1</v>
       </c>
       <c r="AE371">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="372" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF371">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="372" spans="1:32">
       <c r="A372">
         <v>228796</v>
       </c>
@@ -35804,10 +36920,13 @@
         <v>2</v>
       </c>
       <c r="AE372">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="373" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF372">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="373" spans="1:32">
       <c r="A373">
         <v>228875</v>
       </c>
@@ -35899,10 +37018,13 @@
         <v>1</v>
       </c>
       <c r="AE373">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="374" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF373">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="374" spans="1:32">
       <c r="A374">
         <v>228875</v>
       </c>
@@ -35994,10 +37116,13 @@
         <v>1</v>
       </c>
       <c r="AE374">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="375" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF374">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="375" spans="1:32">
       <c r="A375">
         <v>229027</v>
       </c>
@@ -36089,10 +37214,13 @@
         <v>4</v>
       </c>
       <c r="AE375">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="376" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF375">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="376" spans="1:32">
       <c r="A376">
         <v>229027</v>
       </c>
@@ -36184,10 +37312,13 @@
         <v>1</v>
       </c>
       <c r="AE376">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="377" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF376">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="377" spans="1:32">
       <c r="A377">
         <v>229115</v>
       </c>
@@ -36279,10 +37410,13 @@
         <v>3</v>
       </c>
       <c r="AE377">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="378" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF377">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="378" spans="1:32">
       <c r="A378">
         <v>229115</v>
       </c>
@@ -36374,10 +37508,13 @@
         <v>1</v>
       </c>
       <c r="AE378">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="379" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF378">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="379" spans="1:32">
       <c r="A379">
         <v>230038</v>
       </c>
@@ -36469,10 +37606,13 @@
         <v>1</v>
       </c>
       <c r="AE379">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="380" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF379">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="380" spans="1:32">
       <c r="A380">
         <v>230038</v>
       </c>
@@ -36564,10 +37704,13 @@
         <v>0</v>
       </c>
       <c r="AE380">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="381" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF380">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="381" spans="1:32">
       <c r="A381">
         <v>230728</v>
       </c>
@@ -36659,10 +37802,13 @@
         <v>0</v>
       </c>
       <c r="AE381">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="382" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF381">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="382" spans="1:32">
       <c r="A382">
         <v>230728</v>
       </c>
@@ -36754,10 +37900,13 @@
         <v>0</v>
       </c>
       <c r="AE382">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="383" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF382">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="383" spans="1:32">
       <c r="A383">
         <v>230764</v>
       </c>
@@ -36849,10 +37998,13 @@
         <v>1</v>
       </c>
       <c r="AE383">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="384" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF383">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="384" spans="1:32">
       <c r="A384">
         <v>230764</v>
       </c>
@@ -36944,10 +38096,13 @@
         <v>0</v>
       </c>
       <c r="AE384">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="385" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF384">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="385" spans="1:32">
       <c r="A385">
         <v>231174</v>
       </c>
@@ -37039,10 +38194,13 @@
         <v>0</v>
       </c>
       <c r="AE385">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="386" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF385">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="386" spans="1:32">
       <c r="A386">
         <v>231624</v>
       </c>
@@ -37134,10 +38292,13 @@
         <v>0</v>
       </c>
       <c r="AE386">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="387" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF386">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="387" spans="1:32">
       <c r="A387">
         <v>231624</v>
       </c>
@@ -37229,10 +38390,13 @@
         <v>1</v>
       </c>
       <c r="AE387">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="388" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF387">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="388" spans="1:32">
       <c r="A388">
         <v>232186</v>
       </c>
@@ -37324,10 +38488,13 @@
         <v>0</v>
       </c>
       <c r="AE388">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="389" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF388">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="389" spans="1:32">
       <c r="A389">
         <v>232186</v>
       </c>
@@ -37419,10 +38586,13 @@
         <v>0</v>
       </c>
       <c r="AE389">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="390" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF389">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="390" spans="1:32">
       <c r="A390">
         <v>232265</v>
       </c>
@@ -37514,10 +38684,13 @@
         <v>0</v>
       </c>
       <c r="AE390">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="391" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF390">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="391" spans="1:32">
       <c r="A391">
         <v>232265</v>
       </c>
@@ -37609,10 +38782,13 @@
         <v>0</v>
       </c>
       <c r="AE391">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="392" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF391">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="392" spans="1:32">
       <c r="A392">
         <v>232982</v>
       </c>
@@ -37704,10 +38880,13 @@
         <v>1</v>
       </c>
       <c r="AE392">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="393" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF392">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="393" spans="1:32">
       <c r="A393">
         <v>232982</v>
       </c>
@@ -37799,10 +38978,13 @@
         <v>3</v>
       </c>
       <c r="AE393">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="394" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF393">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="394" spans="1:32">
       <c r="A394">
         <v>233921</v>
       </c>
@@ -37894,10 +39076,13 @@
         <v>1</v>
       </c>
       <c r="AE394">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="395" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF394">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="395" spans="1:32">
       <c r="A395">
         <v>233921</v>
       </c>
@@ -37989,10 +39174,13 @@
         <v>2</v>
       </c>
       <c r="AE395">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="396" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF395">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="396" spans="1:32">
       <c r="A396">
         <v>234030</v>
       </c>
@@ -38084,10 +39272,13 @@
         <v>1</v>
       </c>
       <c r="AE396">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="397" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF396">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="397" spans="1:32">
       <c r="A397">
         <v>234076</v>
       </c>
@@ -38179,10 +39370,13 @@
         <v>0</v>
       </c>
       <c r="AE397">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="398" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF397">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="398" spans="1:32">
       <c r="A398">
         <v>234076</v>
       </c>
@@ -38274,10 +39468,13 @@
         <v>5</v>
       </c>
       <c r="AE398">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="399" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF398">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="399" spans="1:32">
       <c r="A399">
         <v>234155</v>
       </c>
@@ -38369,10 +39566,13 @@
         <v>0</v>
       </c>
       <c r="AE399">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="400" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF399">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="400" spans="1:32">
       <c r="A400">
         <v>236939</v>
       </c>
@@ -38464,10 +39664,13 @@
         <v>1</v>
       </c>
       <c r="AE400">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="401" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF400">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="401" spans="1:32">
       <c r="A401">
         <v>236939</v>
       </c>
@@ -38559,10 +39762,13 @@
         <v>0</v>
       </c>
       <c r="AE401">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="402" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF401">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="402" spans="1:32">
       <c r="A402">
         <v>236948</v>
       </c>
@@ -38654,10 +39860,13 @@
         <v>1</v>
       </c>
       <c r="AE402">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="403" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF402">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="403" spans="1:32">
       <c r="A403">
         <v>236948</v>
       </c>
@@ -38749,10 +39958,13 @@
         <v>1</v>
       </c>
       <c r="AE403">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="404" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF403">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="404" spans="1:32">
       <c r="A404">
         <v>236948</v>
       </c>
@@ -38844,10 +40056,13 @@
         <v>0</v>
       </c>
       <c r="AE404">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="405" spans="1:31">
+        <v>2</v>
+      </c>
+      <c r="AF404">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="405" spans="1:32">
       <c r="A405">
         <v>236948</v>
       </c>
@@ -38939,10 +40154,13 @@
         <v>0</v>
       </c>
       <c r="AE405">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="406" spans="1:31">
+        <v>2</v>
+      </c>
+      <c r="AF405">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="406" spans="1:32">
       <c r="A406">
         <v>238032</v>
       </c>
@@ -39034,10 +40252,13 @@
         <v>0</v>
       </c>
       <c r="AE406">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="407" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF406">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="407" spans="1:32">
       <c r="A407">
         <v>238032</v>
       </c>
@@ -39129,10 +40350,13 @@
         <v>0</v>
       </c>
       <c r="AE407">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="408" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF407">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="408" spans="1:32">
       <c r="A408">
         <v>240365</v>
       </c>
@@ -39224,10 +40448,13 @@
         <v>0</v>
       </c>
       <c r="AE408">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="409" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF408">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="409" spans="1:32">
       <c r="A409">
         <v>240444</v>
       </c>
@@ -39319,10 +40546,13 @@
         <v>0</v>
       </c>
       <c r="AE409">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="410" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF409">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="410" spans="1:32">
       <c r="A410">
         <v>240444</v>
       </c>
@@ -39414,10 +40644,13 @@
         <v>1</v>
       </c>
       <c r="AE410">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="411" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF410">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="411" spans="1:32">
       <c r="A411">
         <v>240453</v>
       </c>
@@ -39509,10 +40742,13 @@
         <v>0</v>
       </c>
       <c r="AE411">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="412" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF411">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="412" spans="1:32">
       <c r="A412">
         <v>240453</v>
       </c>
@@ -39604,10 +40840,13 @@
         <v>0</v>
       </c>
       <c r="AE412">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="413" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF412">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="413" spans="1:32">
       <c r="A413">
         <v>240727</v>
       </c>
@@ -39699,10 +40938,13 @@
         <v>2</v>
       </c>
       <c r="AE413">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="414" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF413">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="414" spans="1:32">
       <c r="A414">
         <v>240727</v>
       </c>
@@ -39794,10 +41036,13 @@
         <v>0</v>
       </c>
       <c r="AE414">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="415" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF414">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="415" spans="1:32">
       <c r="A415">
         <v>243197</v>
       </c>
@@ -39889,10 +41134,13 @@
         <v>1</v>
       </c>
       <c r="AE415">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="416" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF415">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="416" spans="1:32">
       <c r="A416">
         <v>243221</v>
       </c>
@@ -39984,10 +41232,13 @@
         <v>0</v>
       </c>
       <c r="AE416">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="417" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF416">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="417" spans="1:32">
       <c r="A417">
         <v>243744</v>
       </c>
@@ -40079,10 +41330,13 @@
         <v>0</v>
       </c>
       <c r="AE417">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="418" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF417">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="418" spans="1:32">
       <c r="A418">
         <v>243744</v>
       </c>
@@ -40174,10 +41428,13 @@
         <v>3</v>
       </c>
       <c r="AE418">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="419" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF418">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="419" spans="1:32">
       <c r="A419">
         <v>243780</v>
       </c>
@@ -40269,10 +41526,13 @@
         <v>1</v>
       </c>
       <c r="AE419">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="420" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF419">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="420" spans="1:32">
       <c r="A420">
         <v>243780</v>
       </c>
@@ -40364,10 +41624,13 @@
         <v>3</v>
       </c>
       <c r="AE420">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="421" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF420">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="421" spans="1:32">
       <c r="A421">
         <v>445188</v>
       </c>
@@ -40459,10 +41722,13 @@
         <v>0</v>
       </c>
       <c r="AE421">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="422" spans="1:31">
+        <v>1</v>
+      </c>
+      <c r="AF421">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="422" spans="1:32">
       <c r="A422">
         <v>445188</v>
       </c>
@@ -40554,6 +41820,9 @@
         <v>0</v>
       </c>
       <c r="AE422">
+        <v>1</v>
+      </c>
+      <c r="AF422">
         <v>2015</v>
       </c>
     </row>

--- a/Excel Files IPEDS/Trimmed/c2015_trimmed_file.xlsx
+++ b/Excel Files IPEDS/Trimmed/c2015_trimmed_file.xlsx
@@ -1,20 +1,61 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/co25936/Desktop/PER/IPEDS/Excel Files IPEDS/Trimmed/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EAB641B-EBF2-CB4F-A432-5A262B7DB56F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="760" windowWidth="30000" windowHeight="7560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>unitid</t>
   </si>
@@ -111,12 +152,15 @@
   <si>
     <t>year</t>
   </si>
+  <si>
+    <t>239 Uniqe UNITIDS</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -128,6 +172,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -168,24 +219,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -223,7 +283,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -257,6 +317,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -291,9 +352,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -466,11 +528,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AF422"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AF662"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:32">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -568,12 +630,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:32">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>100654</v>
       </c>
       <c r="B2">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -666,12 +728,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="3" spans="1:32">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>100663</v>
       </c>
       <c r="B3">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -764,12 +826,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="4" spans="1:32">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>100663</v>
       </c>
       <c r="B4">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -862,12 +924,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="5" spans="1:32">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>100706</v>
       </c>
       <c r="B5">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C5">
         <v>7</v>
@@ -960,12 +1022,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="6" spans="1:32">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>100706</v>
       </c>
       <c r="B6">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1058,12 +1120,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="7" spans="1:32">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>100751</v>
       </c>
       <c r="B7">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1156,12 +1218,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="8" spans="1:32">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>100751</v>
       </c>
       <c r="B8">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -1254,12 +1316,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="9" spans="1:32">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>100858</v>
       </c>
       <c r="B9">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C9">
         <v>14</v>
@@ -1352,12 +1414,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="10" spans="1:32">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>100858</v>
       </c>
       <c r="B10">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1450,12 +1512,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="11" spans="1:32">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>102614</v>
       </c>
       <c r="B11">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1548,12 +1610,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="12" spans="1:32">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>102614</v>
       </c>
       <c r="B12">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -1646,12 +1708,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="13" spans="1:32">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>104151</v>
       </c>
       <c r="B13">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C13">
         <v>5</v>
@@ -1744,12 +1806,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="14" spans="1:32">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>104151</v>
       </c>
       <c r="B14">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C14">
         <v>17</v>
@@ -1842,12 +1904,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="15" spans="1:32">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>104179</v>
       </c>
       <c r="B15">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C15">
         <v>6</v>
@@ -1940,12 +2002,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="16" spans="1:32">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>104179</v>
       </c>
       <c r="B16">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C16">
         <v>8</v>
@@ -2038,12 +2100,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="17" spans="1:32">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>105330</v>
       </c>
       <c r="B17">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C17">
         <v>5</v>
@@ -2136,12 +2198,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="18" spans="1:32">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>106397</v>
       </c>
       <c r="B18">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C18">
         <v>11</v>
@@ -2234,12 +2296,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="19" spans="1:32">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>106397</v>
       </c>
       <c r="B19">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C19">
         <v>3</v>
@@ -2332,12 +2394,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="20" spans="1:32">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>110404</v>
       </c>
       <c r="B20">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C20">
         <v>13</v>
@@ -2430,12 +2492,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="21" spans="1:32">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>110404</v>
       </c>
       <c r="B21">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C21">
         <v>17</v>
@@ -2528,12 +2590,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="22" spans="1:32">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>110422</v>
       </c>
       <c r="B22">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -2626,12 +2688,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="23" spans="1:32">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>110422</v>
       </c>
       <c r="B23">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -2724,12 +2786,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="24" spans="1:32">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>110556</v>
       </c>
       <c r="B24">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C24">
         <v>3</v>
@@ -2822,12 +2884,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="25" spans="1:32">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>110565</v>
       </c>
       <c r="B25">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C25">
         <v>7</v>
@@ -2920,12 +2982,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="26" spans="1:32">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>110583</v>
       </c>
       <c r="B26">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C26">
         <v>9</v>
@@ -3018,12 +3080,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="27" spans="1:32">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>110592</v>
       </c>
       <c r="B27">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C27">
         <v>2</v>
@@ -3116,12 +3178,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="28" spans="1:32">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>110608</v>
       </c>
       <c r="B28">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C28">
         <v>7</v>
@@ -3214,12 +3276,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="29" spans="1:32">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>110635</v>
       </c>
       <c r="B29">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C29">
         <v>31</v>
@@ -3312,12 +3374,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="30" spans="1:32">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>110635</v>
       </c>
       <c r="B30">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C30">
         <v>30</v>
@@ -3410,12 +3472,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="31" spans="1:32">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>110644</v>
       </c>
       <c r="B31">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C31">
         <v>10</v>
@@ -3508,12 +3570,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="32" spans="1:32">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>110644</v>
       </c>
       <c r="B32">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C32">
         <v>22</v>
@@ -3606,12 +3668,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="33" spans="1:32">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>110653</v>
       </c>
       <c r="B33">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C33">
         <v>10</v>
@@ -3704,12 +3766,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="34" spans="1:32">
+    <row r="34" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>110653</v>
       </c>
       <c r="B34">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C34">
         <v>11</v>
@@ -3802,12 +3864,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="35" spans="1:32">
+    <row r="35" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>110662</v>
       </c>
       <c r="B35">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C35">
         <v>30</v>
@@ -3900,12 +3962,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="36" spans="1:32">
+    <row r="36" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>110662</v>
       </c>
       <c r="B36">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C36">
         <v>16</v>
@@ -3998,12 +4060,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="37" spans="1:32">
+    <row r="37" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>110671</v>
       </c>
       <c r="B37">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C37">
         <v>18</v>
@@ -4096,12 +4158,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="38" spans="1:32">
+    <row r="38" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>110671</v>
       </c>
       <c r="B38">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C38">
         <v>13</v>
@@ -4194,12 +4256,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="39" spans="1:32">
+    <row r="39" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>110680</v>
       </c>
       <c r="B39">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C39">
         <v>12</v>
@@ -4292,12 +4354,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="40" spans="1:32">
+    <row r="40" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>110680</v>
       </c>
       <c r="B40">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C40">
         <v>23</v>
@@ -4390,12 +4452,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="41" spans="1:32">
+    <row r="41" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>110705</v>
       </c>
       <c r="B41">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C41">
         <v>27</v>
@@ -4488,12 +4550,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="42" spans="1:32">
+    <row r="42" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>110705</v>
       </c>
       <c r="B42">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C42">
         <v>20</v>
@@ -4586,12 +4648,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="43" spans="1:32">
+    <row r="43" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>110714</v>
       </c>
       <c r="B43">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C43">
         <v>12</v>
@@ -4684,12 +4746,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="44" spans="1:32">
+    <row r="44" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>110714</v>
       </c>
       <c r="B44">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C44">
         <v>8</v>
@@ -4782,12 +4844,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="45" spans="1:32">
+    <row r="45" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>119678</v>
       </c>
       <c r="B45">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C45">
         <v>2</v>
@@ -4880,12 +4942,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="46" spans="1:32">
+    <row r="46" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>119678</v>
       </c>
       <c r="B46">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -4978,12 +5040,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="47" spans="1:32">
+    <row r="47" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>122409</v>
       </c>
       <c r="B47">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C47">
         <v>6</v>
@@ -5076,12 +5138,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="48" spans="1:32">
+    <row r="48" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>122597</v>
       </c>
       <c r="B48">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C48">
         <v>9</v>
@@ -5174,12 +5236,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="49" spans="1:32">
+    <row r="49" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>122755</v>
       </c>
       <c r="B49">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C49">
         <v>10</v>
@@ -5272,12 +5334,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="50" spans="1:32">
+    <row r="50" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>123961</v>
       </c>
       <c r="B50">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C50">
         <v>5</v>
@@ -5370,12 +5432,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="51" spans="1:32">
+    <row r="51" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>123961</v>
       </c>
       <c r="B51">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C51">
         <v>8</v>
@@ -5468,12 +5530,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="52" spans="1:32">
+    <row r="52" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>126614</v>
       </c>
       <c r="B52">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C52">
         <v>24</v>
@@ -5566,12 +5628,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="53" spans="1:32">
+    <row r="53" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>126614</v>
       </c>
       <c r="B53">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C53">
         <v>29</v>
@@ -5664,12 +5726,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="54" spans="1:32">
+    <row r="54" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>126775</v>
       </c>
       <c r="B54">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C54">
         <v>6</v>
@@ -5762,12 +5824,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="55" spans="1:32">
+    <row r="55" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>126818</v>
       </c>
       <c r="B55">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C55">
         <v>9</v>
@@ -5860,12 +5922,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="56" spans="1:32">
+    <row r="56" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>126818</v>
       </c>
       <c r="B56">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C56">
         <v>5</v>
@@ -5958,12 +6020,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="57" spans="1:32">
+    <row r="57" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>127060</v>
       </c>
       <c r="B57">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -6056,12 +6118,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="58" spans="1:32">
+    <row r="58" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>127060</v>
       </c>
       <c r="B58">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -6154,12 +6216,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="59" spans="1:32">
+    <row r="59" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>129020</v>
       </c>
       <c r="B59">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C59">
         <v>13</v>
@@ -6252,12 +6314,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="60" spans="1:32">
+    <row r="60" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>129020</v>
       </c>
       <c r="B60">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C60">
         <v>8</v>
@@ -6350,12 +6412,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="61" spans="1:32">
+    <row r="61" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>130697</v>
       </c>
       <c r="B61">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -6448,12 +6510,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="62" spans="1:32">
+    <row r="62" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>130697</v>
       </c>
       <c r="B62">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -6546,12 +6608,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="63" spans="1:32">
+    <row r="63" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>130794</v>
       </c>
       <c r="B63">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C63">
         <v>26</v>
@@ -6644,12 +6706,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="64" spans="1:32">
+    <row r="64" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>130794</v>
       </c>
       <c r="B64">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C64">
         <v>9</v>
@@ -6742,12 +6804,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="65" spans="1:32">
+    <row r="65" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>130934</v>
       </c>
       <c r="B65">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -6840,12 +6902,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="66" spans="1:32">
+    <row r="66" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>130943</v>
       </c>
       <c r="B66">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C66">
         <v>3</v>
@@ -6938,12 +7000,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="67" spans="1:32">
+    <row r="67" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>130943</v>
       </c>
       <c r="B67">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C67">
         <v>8</v>
@@ -7036,12 +7098,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="68" spans="1:32">
+    <row r="68" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>131283</v>
       </c>
       <c r="B68">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C68">
         <v>6</v>
@@ -7134,12 +7196,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="69" spans="1:32">
+    <row r="69" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>131283</v>
       </c>
       <c r="B69">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C69">
         <v>4</v>
@@ -7232,12 +7294,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="70" spans="1:32">
+    <row r="70" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>131469</v>
       </c>
       <c r="B70">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -7330,12 +7392,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="71" spans="1:32">
+    <row r="71" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>131469</v>
       </c>
       <c r="B71">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C71">
         <v>2</v>
@@ -7428,12 +7490,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="72" spans="1:32">
+    <row r="72" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>131496</v>
       </c>
       <c r="B72">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C72">
         <v>4</v>
@@ -7526,12 +7588,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="73" spans="1:32">
+    <row r="73" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>131496</v>
       </c>
       <c r="B73">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C73">
         <v>5</v>
@@ -7624,12 +7686,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="74" spans="1:32">
+    <row r="74" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>131520</v>
       </c>
       <c r="B74">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -7722,12 +7784,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="75" spans="1:32">
+    <row r="75" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>131520</v>
       </c>
       <c r="B75">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C75">
         <v>2</v>
@@ -7820,12 +7882,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="76" spans="1:32">
+    <row r="76" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>132903</v>
       </c>
       <c r="B76">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C76">
         <v>4</v>
@@ -7918,12 +7980,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="77" spans="1:32">
+    <row r="77" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>132903</v>
       </c>
       <c r="B77">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C77">
         <v>21</v>
@@ -8016,12 +8078,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="78" spans="1:32">
+    <row r="78" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>133650</v>
       </c>
       <c r="B78">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -8114,12 +8176,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="79" spans="1:32">
+    <row r="79" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>133650</v>
       </c>
       <c r="B79">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C79">
         <v>3</v>
@@ -8212,12 +8274,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="80" spans="1:32">
+    <row r="80" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>133669</v>
       </c>
       <c r="B80">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C80">
         <v>4</v>
@@ -8310,12 +8372,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="81" spans="1:32">
+    <row r="81" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>133669</v>
       </c>
       <c r="B81">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -8408,12 +8470,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="82" spans="1:32">
+    <row r="82" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>133881</v>
       </c>
       <c r="B82">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C82">
         <v>3</v>
@@ -8506,12 +8568,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="83" spans="1:32">
+    <row r="83" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>133881</v>
       </c>
       <c r="B83">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C83">
         <v>5</v>
@@ -8604,12 +8666,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="84" spans="1:32">
+    <row r="84" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>133951</v>
       </c>
       <c r="B84">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C84">
         <v>2</v>
@@ -8702,12 +8764,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="85" spans="1:32">
+    <row r="85" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>133951</v>
       </c>
       <c r="B85">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C85">
         <v>4</v>
@@ -8800,12 +8862,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="86" spans="1:32">
+    <row r="86" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>134097</v>
       </c>
       <c r="B86">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C86">
         <v>36</v>
@@ -8898,12 +8960,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="87" spans="1:32">
+    <row r="87" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>134097</v>
       </c>
       <c r="B87">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C87">
         <v>16</v>
@@ -8996,12 +9058,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="88" spans="1:32">
+    <row r="88" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>134130</v>
       </c>
       <c r="B88">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C88">
         <v>9</v>
@@ -9094,12 +9156,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="89" spans="1:32">
+    <row r="89" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>134130</v>
       </c>
       <c r="B89">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C89">
         <v>19</v>
@@ -9192,12 +9254,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="90" spans="1:32">
+    <row r="90" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>135726</v>
       </c>
       <c r="B90">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C90">
         <v>3</v>
@@ -9290,12 +9352,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="91" spans="1:32">
+    <row r="91" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>137351</v>
       </c>
       <c r="B91">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C91">
         <v>14</v>
@@ -9388,12 +9450,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="92" spans="1:32">
+    <row r="92" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>137351</v>
       </c>
       <c r="B92">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C92">
         <v>8</v>
@@ -9486,12 +9548,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="93" spans="1:32">
+    <row r="93" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>138947</v>
       </c>
       <c r="B93">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C93">
         <v>1</v>
@@ -9584,12 +9646,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="94" spans="1:32">
+    <row r="94" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>139658</v>
       </c>
       <c r="B94">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C94">
         <v>1</v>
@@ -9682,12 +9744,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="95" spans="1:32">
+    <row r="95" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>139658</v>
       </c>
       <c r="B95">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C95">
         <v>4</v>
@@ -9780,12 +9842,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="96" spans="1:32">
+    <row r="96" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>139755</v>
       </c>
       <c r="B96">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C96">
         <v>6</v>
@@ -9878,12 +9940,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="97" spans="1:32">
+    <row r="97" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>139755</v>
       </c>
       <c r="B97">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C97">
         <v>13</v>
@@ -9976,12 +10038,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="98" spans="1:32">
+    <row r="98" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>139940</v>
       </c>
       <c r="B98">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C98">
         <v>8</v>
@@ -10074,12 +10136,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="99" spans="1:32">
+    <row r="99" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>139940</v>
       </c>
       <c r="B99">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C99">
         <v>5</v>
@@ -10172,12 +10234,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="100" spans="1:32">
+    <row r="100" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>139959</v>
       </c>
       <c r="B100">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C100">
         <v>4</v>
@@ -10270,12 +10332,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="101" spans="1:32">
+    <row r="101" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>139959</v>
       </c>
       <c r="B101">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C101">
         <v>6</v>
@@ -10368,12 +10430,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="102" spans="1:32">
+    <row r="102" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>141574</v>
       </c>
       <c r="B102">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C102">
         <v>2</v>
@@ -10466,12 +10528,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="103" spans="1:32">
+    <row r="103" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>141574</v>
       </c>
       <c r="B103">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C103">
         <v>3</v>
@@ -10564,12 +10626,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="104" spans="1:32">
+    <row r="104" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>142276</v>
       </c>
       <c r="B104">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C104">
         <v>5</v>
@@ -10662,12 +10724,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="105" spans="1:32">
+    <row r="105" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>142276</v>
       </c>
       <c r="B105">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C105">
         <v>3</v>
@@ -10760,12 +10822,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="106" spans="1:32">
+    <row r="106" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>142285</v>
       </c>
       <c r="B106">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C106">
         <v>3</v>
@@ -10858,12 +10920,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="107" spans="1:32">
+    <row r="107" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>142285</v>
       </c>
       <c r="B107">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C107">
         <v>2</v>
@@ -10956,12 +11018,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="108" spans="1:32">
+    <row r="108" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>142285</v>
       </c>
       <c r="B108">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -11054,12 +11116,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="109" spans="1:32">
+    <row r="109" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>142285</v>
       </c>
       <c r="B109">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -11152,12 +11214,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="110" spans="1:32">
+    <row r="110" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>144050</v>
       </c>
       <c r="B110">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C110">
         <v>11</v>
@@ -11250,12 +11312,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="111" spans="1:32">
+    <row r="111" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>144050</v>
       </c>
       <c r="B111">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C111">
         <v>21</v>
@@ -11348,12 +11410,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="112" spans="1:32">
+    <row r="112" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>144740</v>
       </c>
       <c r="B112">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -11446,12 +11508,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="113" spans="1:32">
+    <row r="113" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>145600</v>
       </c>
       <c r="B113">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C113">
         <v>8</v>
@@ -11544,12 +11606,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="114" spans="1:32">
+    <row r="114" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>145600</v>
       </c>
       <c r="B114">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C114">
         <v>7</v>
@@ -11642,12 +11704,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="115" spans="1:32">
+    <row r="115" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>145637</v>
       </c>
       <c r="B115">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C115">
         <v>15</v>
@@ -11740,12 +11802,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="116" spans="1:32">
+    <row r="116" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>145637</v>
       </c>
       <c r="B116">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C116">
         <v>30</v>
@@ -11838,12 +11900,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="117" spans="1:32">
+    <row r="117" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>145725</v>
       </c>
       <c r="B117">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C117">
         <v>4</v>
@@ -11936,12 +11998,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="118" spans="1:32">
+    <row r="118" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>145725</v>
       </c>
       <c r="B118">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C118">
         <v>9</v>
@@ -12034,12 +12096,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="119" spans="1:32">
+    <row r="119" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>147703</v>
       </c>
       <c r="B119">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C119">
         <v>6</v>
@@ -12132,12 +12194,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="120" spans="1:32">
+    <row r="120" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>147703</v>
       </c>
       <c r="B120">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C120">
         <v>5</v>
@@ -12230,12 +12292,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="121" spans="1:32">
+    <row r="121" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>149222</v>
       </c>
       <c r="B121">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C121">
         <v>8</v>
@@ -12328,12 +12390,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="122" spans="1:32">
+    <row r="122" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>149222</v>
       </c>
       <c r="B122">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C122">
         <v>1</v>
@@ -12426,12 +12488,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="123" spans="1:32">
+    <row r="123" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>149772</v>
       </c>
       <c r="B123">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C123">
         <v>18</v>
@@ -12524,12 +12586,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="124" spans="1:32">
+    <row r="124" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>150136</v>
       </c>
       <c r="B124">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C124">
         <v>5</v>
@@ -12622,12 +12684,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="125" spans="1:32">
+    <row r="125" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>151111</v>
       </c>
       <c r="B125">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C125">
         <v>4</v>
@@ -12720,12 +12782,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="126" spans="1:32">
+    <row r="126" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>151351</v>
       </c>
       <c r="B126">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C126">
         <v>12</v>
@@ -12818,12 +12880,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="127" spans="1:32">
+    <row r="127" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>151351</v>
       </c>
       <c r="B127">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C127">
         <v>16</v>
@@ -12916,12 +12978,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="128" spans="1:32">
+    <row r="128" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>152080</v>
       </c>
       <c r="B128">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C128">
         <v>17</v>
@@ -13014,12 +13076,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="129" spans="1:32">
+    <row r="129" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>152080</v>
       </c>
       <c r="B129">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C129">
         <v>11</v>
@@ -13112,12 +13174,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="130" spans="1:32">
+    <row r="130" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>153603</v>
       </c>
       <c r="B130">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C130">
         <v>1</v>
@@ -13210,12 +13272,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="131" spans="1:32">
+    <row r="131" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>153658</v>
       </c>
       <c r="B131">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C131">
         <v>4</v>
@@ -13308,12 +13370,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="132" spans="1:32">
+    <row r="132" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>153658</v>
       </c>
       <c r="B132">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C132">
         <v>13</v>
@@ -13406,12 +13468,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="133" spans="1:32">
+    <row r="133" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>155317</v>
       </c>
       <c r="B133">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C133">
         <v>4</v>
@@ -13504,12 +13566,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="134" spans="1:32">
+    <row r="134" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>155317</v>
       </c>
       <c r="B134">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C134">
         <v>6</v>
@@ -13602,12 +13664,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="135" spans="1:32">
+    <row r="135" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>155399</v>
       </c>
       <c r="B135">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C135">
         <v>7</v>
@@ -13700,12 +13762,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="136" spans="1:32">
+    <row r="136" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>155399</v>
       </c>
       <c r="B136">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C136">
         <v>8</v>
@@ -13798,12 +13860,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="137" spans="1:32">
+    <row r="137" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>155681</v>
       </c>
       <c r="B137">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C137">
         <v>3</v>
@@ -13896,12 +13958,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="138" spans="1:32">
+    <row r="138" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>157085</v>
       </c>
       <c r="B138">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C138">
         <v>8</v>
@@ -13994,12 +14056,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="139" spans="1:32">
+    <row r="139" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>157085</v>
       </c>
       <c r="B139">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C139">
         <v>10</v>
@@ -14092,12 +14154,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="140" spans="1:32">
+    <row r="140" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>157289</v>
       </c>
       <c r="B140">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C140">
         <v>11</v>
@@ -14190,12 +14252,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="141" spans="1:32">
+    <row r="141" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>157289</v>
       </c>
       <c r="B141">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C141">
         <v>3</v>
@@ -14288,12 +14350,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="142" spans="1:32">
+    <row r="142" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>159391</v>
       </c>
       <c r="B142">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C142">
         <v>4</v>
@@ -14386,12 +14448,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="143" spans="1:32">
+    <row r="143" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>159391</v>
       </c>
       <c r="B143">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C143">
         <v>9</v>
@@ -14484,12 +14546,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="144" spans="1:32">
+    <row r="144" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>159647</v>
       </c>
       <c r="B144">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C144">
         <v>3</v>
@@ -14582,12 +14644,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="145" spans="1:32">
+    <row r="145" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>159939</v>
       </c>
       <c r="B145">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C145">
         <v>6</v>
@@ -14680,12 +14742,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="146" spans="1:32">
+    <row r="146" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>160621</v>
       </c>
       <c r="B146">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -14778,12 +14840,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="147" spans="1:32">
+    <row r="147" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>160658</v>
       </c>
       <c r="B147">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C147">
         <v>1</v>
@@ -14876,12 +14938,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="148" spans="1:32">
+    <row r="148" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>160755</v>
       </c>
       <c r="B148">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C148">
         <v>3</v>
@@ -14974,12 +15036,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="149" spans="1:32">
+    <row r="149" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>160755</v>
       </c>
       <c r="B149">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C149">
         <v>1</v>
@@ -15072,12 +15134,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="150" spans="1:32">
+    <row r="150" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>161253</v>
       </c>
       <c r="B150">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -15170,12 +15232,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="151" spans="1:32">
+    <row r="151" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>161253</v>
       </c>
       <c r="B151">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C151">
         <v>4</v>
@@ -15268,12 +15330,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="152" spans="1:32">
+    <row r="152" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>161253</v>
       </c>
       <c r="B152">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -15366,12 +15428,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="153" spans="1:32">
+    <row r="153" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>162928</v>
       </c>
       <c r="B153">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C153">
         <v>21</v>
@@ -15464,12 +15526,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="154" spans="1:32">
+    <row r="154" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>162928</v>
       </c>
       <c r="B154">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C154">
         <v>15</v>
@@ -15562,12 +15624,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="155" spans="1:32">
+    <row r="155" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>163268</v>
       </c>
       <c r="B155">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C155">
         <v>8</v>
@@ -15660,12 +15722,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="156" spans="1:32">
+    <row r="156" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>163268</v>
       </c>
       <c r="B156">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C156">
         <v>3</v>
@@ -15758,12 +15820,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="157" spans="1:32">
+    <row r="157" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>163286</v>
       </c>
       <c r="B157">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C157">
         <v>7</v>
@@ -15856,12 +15918,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="158" spans="1:32">
+    <row r="158" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>163286</v>
       </c>
       <c r="B158">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C158">
         <v>37</v>
@@ -15954,12 +16016,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="159" spans="1:32">
+    <row r="159" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>164924</v>
       </c>
       <c r="B159">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C159">
         <v>9</v>
@@ -16052,12 +16114,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="160" spans="1:32">
+    <row r="160" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>164924</v>
       </c>
       <c r="B160">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C160">
         <v>8</v>
@@ -16150,12 +16212,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="161" spans="1:32">
+    <row r="161" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>164988</v>
       </c>
       <c r="B161">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C161">
         <v>7</v>
@@ -16248,12 +16310,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="162" spans="1:32">
+    <row r="162" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>164988</v>
       </c>
       <c r="B162">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C162">
         <v>16</v>
@@ -16346,12 +16408,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="163" spans="1:32">
+    <row r="163" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>165015</v>
       </c>
       <c r="B163">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C163">
         <v>3</v>
@@ -16444,12 +16506,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="164" spans="1:32">
+    <row r="164" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>165015</v>
       </c>
       <c r="B164">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C164">
         <v>10</v>
@@ -16542,12 +16604,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="165" spans="1:32">
+    <row r="165" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>165334</v>
       </c>
       <c r="B165">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -16640,12 +16702,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="166" spans="1:32">
+    <row r="166" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>165334</v>
       </c>
       <c r="B166">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -16738,12 +16800,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="167" spans="1:32">
+    <row r="167" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>166027</v>
       </c>
       <c r="B167">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C167">
         <v>25</v>
@@ -16836,12 +16898,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="168" spans="1:32">
+    <row r="168" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>166027</v>
       </c>
       <c r="B168">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C168">
         <v>27</v>
@@ -16934,12 +16996,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="169" spans="1:32">
+    <row r="169" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>166513</v>
       </c>
       <c r="B169">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C169">
         <v>19</v>
@@ -17032,12 +17094,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="170" spans="1:32">
+    <row r="170" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>166513</v>
       </c>
       <c r="B170">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C170">
         <v>9</v>
@@ -17130,12 +17192,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="171" spans="1:32">
+    <row r="171" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>166629</v>
       </c>
       <c r="B171">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C171">
         <v>3</v>
@@ -17228,12 +17290,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="172" spans="1:32">
+    <row r="172" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>166629</v>
       </c>
       <c r="B172">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C172">
         <v>6</v>
@@ -17326,12 +17388,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="173" spans="1:32">
+    <row r="173" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>166638</v>
       </c>
       <c r="B173">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C173">
         <v>8</v>
@@ -17424,12 +17486,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="174" spans="1:32">
+    <row r="174" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>166683</v>
       </c>
       <c r="B174">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C174">
         <v>6</v>
@@ -17522,12 +17584,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="175" spans="1:32">
+    <row r="175" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>166683</v>
       </c>
       <c r="B175">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C175">
         <v>39</v>
@@ -17620,12 +17682,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="176" spans="1:32">
+    <row r="176" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>167358</v>
       </c>
       <c r="B176">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C176">
         <v>9</v>
@@ -17718,12 +17780,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="177" spans="1:32">
+    <row r="177" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>167358</v>
       </c>
       <c r="B177">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C177">
         <v>11</v>
@@ -17816,12 +17878,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="178" spans="1:32">
+    <row r="178" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>167987</v>
       </c>
       <c r="B178">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C178">
         <v>4</v>
@@ -17914,12 +17976,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="179" spans="1:32">
+    <row r="179" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>168148</v>
       </c>
       <c r="B179">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C179">
         <v>5</v>
@@ -18012,12 +18074,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="180" spans="1:32">
+    <row r="180" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>168148</v>
       </c>
       <c r="B180">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C180">
         <v>6</v>
@@ -18110,12 +18172,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="181" spans="1:32">
+    <row r="181" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>168421</v>
       </c>
       <c r="B181">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C181">
         <v>3</v>
@@ -18208,12 +18270,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="182" spans="1:32">
+    <row r="182" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>168421</v>
       </c>
       <c r="B182">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C182">
         <v>1</v>
@@ -18306,12 +18368,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="183" spans="1:32">
+    <row r="183" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A183">
         <v>169248</v>
       </c>
       <c r="B183">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C183">
         <v>5</v>
@@ -18404,12 +18466,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="184" spans="1:32">
+    <row r="184" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>169798</v>
       </c>
       <c r="B184">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C184">
         <v>3</v>
@@ -18502,12 +18564,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="185" spans="1:32">
+    <row r="185" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>170976</v>
       </c>
       <c r="B185">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C185">
         <v>11</v>
@@ -18600,12 +18662,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="186" spans="1:32">
+    <row r="186" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>170976</v>
       </c>
       <c r="B186">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C186">
         <v>34</v>
@@ -18698,12 +18760,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="187" spans="1:32">
+    <row r="187" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>171100</v>
       </c>
       <c r="B187">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C187">
         <v>17</v>
@@ -18796,12 +18858,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="188" spans="1:32">
+    <row r="188" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>171100</v>
       </c>
       <c r="B188">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C188">
         <v>24</v>
@@ -18894,12 +18956,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="189" spans="1:32">
+    <row r="189" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>171128</v>
       </c>
       <c r="B189">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C189">
         <v>2</v>
@@ -18992,12 +19054,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="190" spans="1:32">
+    <row r="190" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>171128</v>
       </c>
       <c r="B190">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C190">
         <v>2</v>
@@ -19090,12 +19152,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="191" spans="1:32">
+    <row r="191" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>171571</v>
       </c>
       <c r="B191">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C191">
         <v>0</v>
@@ -19188,12 +19250,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="192" spans="1:32">
+    <row r="192" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>172644</v>
       </c>
       <c r="B192">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C192">
         <v>13</v>
@@ -19286,12 +19348,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="193" spans="1:32">
+    <row r="193" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>172644</v>
       </c>
       <c r="B193">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C193">
         <v>6</v>
@@ -19384,12 +19446,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="194" spans="1:32">
+    <row r="194" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>172699</v>
       </c>
       <c r="B194">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C194">
         <v>4</v>
@@ -19482,12 +19544,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="195" spans="1:32">
+    <row r="195" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>172699</v>
       </c>
       <c r="B195">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C195">
         <v>3</v>
@@ -19580,12 +19642,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="196" spans="1:32">
+    <row r="196" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>173920</v>
       </c>
       <c r="B196">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C196">
         <v>1</v>
@@ -19678,12 +19740,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="197" spans="1:32">
+    <row r="197" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>174066</v>
       </c>
       <c r="B197">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C197">
         <v>13</v>
@@ -19776,12 +19838,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="198" spans="1:32">
+    <row r="198" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>174066</v>
       </c>
       <c r="B198">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C198">
         <v>20</v>
@@ -19874,12 +19936,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="199" spans="1:32">
+    <row r="199" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>174233</v>
       </c>
       <c r="B199">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C199">
         <v>3</v>
@@ -19972,12 +20034,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="200" spans="1:32">
+    <row r="200" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>176017</v>
       </c>
       <c r="B200">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C200">
         <v>10</v>
@@ -20070,12 +20132,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="201" spans="1:32">
+    <row r="201" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>176017</v>
       </c>
       <c r="B201">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C201">
         <v>3</v>
@@ -20168,12 +20230,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="202" spans="1:32">
+    <row r="202" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>176080</v>
       </c>
       <c r="B202">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C202">
         <v>8</v>
@@ -20266,12 +20328,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="203" spans="1:32">
+    <row r="203" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>176372</v>
       </c>
       <c r="B203">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C203">
         <v>2</v>
@@ -20364,12 +20426,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="204" spans="1:32">
+    <row r="204" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>178396</v>
       </c>
       <c r="B204">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C204">
         <v>11</v>
@@ -20462,12 +20524,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="205" spans="1:32">
+    <row r="205" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>178396</v>
       </c>
       <c r="B205">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C205">
         <v>11</v>
@@ -20560,12 +20622,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="206" spans="1:32">
+    <row r="206" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>178402</v>
       </c>
       <c r="B206">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C206">
         <v>13</v>
@@ -20658,12 +20720,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="207" spans="1:32">
+    <row r="207" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>178411</v>
       </c>
       <c r="B207">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C207">
         <v>8</v>
@@ -20756,12 +20818,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="208" spans="1:32">
+    <row r="208" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>178411</v>
       </c>
       <c r="B208">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C208">
         <v>1</v>
@@ -20854,12 +20916,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="209" spans="1:32">
+    <row r="209" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>178420</v>
       </c>
       <c r="B209">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C209">
         <v>3</v>
@@ -20952,12 +21014,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="210" spans="1:32">
+    <row r="210" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>178420</v>
       </c>
       <c r="B210">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C210">
         <v>0</v>
@@ -21050,12 +21112,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="211" spans="1:32">
+    <row r="211" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>179867</v>
       </c>
       <c r="B211">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C211">
         <v>6</v>
@@ -21148,12 +21210,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="212" spans="1:32">
+    <row r="212" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>179867</v>
       </c>
       <c r="B212">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C212">
         <v>14</v>
@@ -21246,12 +21308,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="213" spans="1:32">
+    <row r="213" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>180461</v>
       </c>
       <c r="B213">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C213">
         <v>8</v>
@@ -21344,12 +21406,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="214" spans="1:32">
+    <row r="214" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>180461</v>
       </c>
       <c r="B214">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C214">
         <v>4</v>
@@ -21442,12 +21504,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="215" spans="1:32">
+    <row r="215" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A215">
         <v>181002</v>
       </c>
       <c r="B215">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C215">
         <v>3</v>
@@ -21540,12 +21602,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="216" spans="1:32">
+    <row r="216" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>181464</v>
       </c>
       <c r="B216">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C216">
         <v>7</v>
@@ -21638,12 +21700,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="217" spans="1:32">
+    <row r="217" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>181464</v>
       </c>
       <c r="B217">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C217">
         <v>4</v>
@@ -21736,12 +21798,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="218" spans="1:32">
+    <row r="218" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>182281</v>
       </c>
       <c r="B218">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C218">
         <v>0</v>
@@ -21834,12 +21896,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="219" spans="1:32">
+    <row r="219" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>182281</v>
       </c>
       <c r="B219">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C219">
         <v>2</v>
@@ -21932,12 +21994,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="220" spans="1:32">
+    <row r="220" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>182290</v>
       </c>
       <c r="B220">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C220">
         <v>6</v>
@@ -22030,12 +22092,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="221" spans="1:32">
+    <row r="221" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>182290</v>
       </c>
       <c r="B221">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C221">
         <v>8</v>
@@ -22128,12 +22190,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="222" spans="1:32">
+    <row r="222" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>182670</v>
       </c>
       <c r="B222">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C222">
         <v>2</v>
@@ -22226,12 +22288,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="223" spans="1:32">
+    <row r="223" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>182670</v>
       </c>
       <c r="B223">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C223">
         <v>7</v>
@@ -22324,12 +22386,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="224" spans="1:32">
+    <row r="224" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>183044</v>
       </c>
       <c r="B224">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C224">
         <v>2</v>
@@ -22422,12 +22484,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="225" spans="1:32">
+    <row r="225" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>183044</v>
       </c>
       <c r="B225">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C225">
         <v>8</v>
@@ -22520,12 +22582,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="226" spans="1:32">
+    <row r="226" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>185828</v>
       </c>
       <c r="B226">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C226">
         <v>2</v>
@@ -22618,12 +22680,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="227" spans="1:32">
+    <row r="227" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>185828</v>
       </c>
       <c r="B227">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C227">
         <v>3</v>
@@ -22716,12 +22778,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="228" spans="1:32">
+    <row r="228" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A228">
         <v>186131</v>
       </c>
       <c r="B228">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C228">
         <v>22</v>
@@ -22814,12 +22876,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="229" spans="1:32">
+    <row r="229" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A229">
         <v>186131</v>
       </c>
       <c r="B229">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C229">
         <v>30</v>
@@ -22912,12 +22974,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="230" spans="1:32">
+    <row r="230" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>186399</v>
       </c>
       <c r="B230">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C230">
         <v>0</v>
@@ -23010,12 +23072,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="231" spans="1:32">
+    <row r="231" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>186399</v>
       </c>
       <c r="B231">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C231">
         <v>1</v>
@@ -23108,12 +23170,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="232" spans="1:32">
+    <row r="232" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A232">
         <v>186867</v>
       </c>
       <c r="B232">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C232">
         <v>2</v>
@@ -23206,12 +23268,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="233" spans="1:32">
+    <row r="233" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>186867</v>
       </c>
       <c r="B233">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C233">
         <v>6</v>
@@ -23304,12 +23366,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="234" spans="1:32">
+    <row r="234" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>187967</v>
       </c>
       <c r="B234">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C234">
         <v>2</v>
@@ -23402,12 +23464,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="235" spans="1:32">
+    <row r="235" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>187967</v>
       </c>
       <c r="B235">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C235">
         <v>4</v>
@@ -23500,12 +23562,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="236" spans="1:32">
+    <row r="236" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A236">
         <v>187985</v>
       </c>
       <c r="B236">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C236">
         <v>12</v>
@@ -23598,12 +23660,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="237" spans="1:32">
+    <row r="237" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>187985</v>
       </c>
       <c r="B237">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C237">
         <v>8</v>
@@ -23696,12 +23758,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="238" spans="1:32">
+    <row r="238" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>188030</v>
       </c>
       <c r="B238">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C238">
         <v>3</v>
@@ -23794,12 +23856,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="239" spans="1:32">
+    <row r="239" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>188030</v>
       </c>
       <c r="B239">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C239">
         <v>5</v>
@@ -23892,12 +23954,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="240" spans="1:32">
+    <row r="240" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>190044</v>
       </c>
       <c r="B240">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C240">
         <v>4</v>
@@ -23990,12 +24052,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="241" spans="1:32">
+    <row r="241" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A241">
         <v>190044</v>
       </c>
       <c r="B241">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C241">
         <v>1</v>
@@ -24088,12 +24150,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="242" spans="1:32">
+    <row r="242" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A242">
         <v>190150</v>
       </c>
       <c r="B242">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C242">
         <v>11</v>
@@ -24186,12 +24248,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="243" spans="1:32">
+    <row r="243" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A243">
         <v>190150</v>
       </c>
       <c r="B243">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C243">
         <v>14</v>
@@ -24284,12 +24346,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="244" spans="1:32">
+    <row r="244" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A244">
         <v>190415</v>
       </c>
       <c r="B244">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C244">
         <v>26</v>
@@ -24382,12 +24444,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="245" spans="1:32">
+    <row r="245" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A245">
         <v>190415</v>
       </c>
       <c r="B245">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C245">
         <v>19</v>
@@ -24480,12 +24542,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="246" spans="1:32">
+    <row r="246" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A246">
         <v>190549</v>
       </c>
       <c r="B246">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C246">
         <v>2</v>
@@ -24578,12 +24640,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="247" spans="1:32">
+    <row r="247" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A247">
         <v>190567</v>
       </c>
       <c r="B247">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C247">
         <v>11</v>
@@ -24676,12 +24738,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="248" spans="1:32">
+    <row r="248" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A248">
         <v>190576</v>
       </c>
       <c r="B248">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C248">
         <v>13</v>
@@ -24774,12 +24836,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="249" spans="1:32">
+    <row r="249" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A249">
         <v>190576</v>
       </c>
       <c r="B249">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C249">
         <v>20</v>
@@ -24872,12 +24934,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="250" spans="1:32">
+    <row r="250" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A250">
         <v>190594</v>
       </c>
       <c r="B250">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C250">
         <v>4</v>
@@ -24970,12 +25032,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="251" spans="1:32">
+    <row r="251" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A251">
         <v>190594</v>
       </c>
       <c r="B251">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C251">
         <v>0</v>
@@ -25068,12 +25130,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="252" spans="1:32">
+    <row r="252" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A252">
         <v>190664</v>
       </c>
       <c r="B252">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C252">
         <v>4</v>
@@ -25166,12 +25228,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="253" spans="1:32">
+    <row r="253" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A253">
         <v>193900</v>
       </c>
       <c r="B253">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C253">
         <v>36</v>
@@ -25264,12 +25326,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="254" spans="1:32">
+    <row r="254" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A254">
         <v>193900</v>
       </c>
       <c r="B254">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C254">
         <v>13</v>
@@ -25362,12 +25424,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="255" spans="1:32">
+    <row r="255" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A255">
         <v>194824</v>
       </c>
       <c r="B255">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C255">
         <v>8</v>
@@ -25460,12 +25522,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="256" spans="1:32">
+    <row r="256" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A256">
         <v>194824</v>
       </c>
       <c r="B256">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C256">
         <v>9</v>
@@ -25558,12 +25620,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="257" spans="1:32">
+    <row r="257" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A257">
         <v>195030</v>
       </c>
       <c r="B257">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C257">
         <v>6</v>
@@ -25656,12 +25718,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="258" spans="1:32">
+    <row r="258" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A258">
         <v>195030</v>
       </c>
       <c r="B258">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C258">
         <v>7</v>
@@ -25754,12 +25816,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="259" spans="1:32">
+    <row r="259" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A259">
         <v>195030</v>
       </c>
       <c r="B259">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C259">
         <v>0</v>
@@ -25852,12 +25914,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="260" spans="1:32">
+    <row r="260" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A260">
         <v>196060</v>
       </c>
       <c r="B260">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C260">
         <v>3</v>
@@ -25950,12 +26012,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="261" spans="1:32">
+    <row r="261" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A261">
         <v>196060</v>
       </c>
       <c r="B261">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C261">
         <v>8</v>
@@ -26048,12 +26110,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="262" spans="1:32">
+    <row r="262" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A262">
         <v>196079</v>
       </c>
       <c r="B262">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C262">
         <v>4</v>
@@ -26146,12 +26208,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="263" spans="1:32">
+    <row r="263" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A263">
         <v>196079</v>
       </c>
       <c r="B263">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C263">
         <v>2</v>
@@ -26244,12 +26306,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="264" spans="1:32">
+    <row r="264" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A264">
         <v>196088</v>
       </c>
       <c r="B264">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C264">
         <v>10</v>
@@ -26342,12 +26404,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="265" spans="1:32">
+    <row r="265" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A265">
         <v>196088</v>
       </c>
       <c r="B265">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C265">
         <v>11</v>
@@ -26440,12 +26502,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="266" spans="1:32">
+    <row r="266" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A266">
         <v>196097</v>
       </c>
       <c r="B266">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C266">
         <v>8</v>
@@ -26538,12 +26600,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="267" spans="1:32">
+    <row r="267" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A267">
         <v>196097</v>
       </c>
       <c r="B267">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C267">
         <v>19</v>
@@ -26636,12 +26698,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="268" spans="1:32">
+    <row r="268" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A268">
         <v>196413</v>
       </c>
       <c r="B268">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C268">
         <v>4</v>
@@ -26734,12 +26796,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="269" spans="1:32">
+    <row r="269" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A269">
         <v>196413</v>
       </c>
       <c r="B269">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C269">
         <v>14</v>
@@ -26832,12 +26894,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="270" spans="1:32">
+    <row r="270" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A270">
         <v>197869</v>
       </c>
       <c r="B270">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C270">
         <v>11</v>
@@ -26930,12 +26992,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="271" spans="1:32">
+    <row r="271" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A271">
         <v>198419</v>
       </c>
       <c r="B271">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C271">
         <v>1</v>
@@ -27028,12 +27090,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="272" spans="1:32">
+    <row r="272" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A272">
         <v>198419</v>
       </c>
       <c r="B272">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C272">
         <v>7</v>
@@ -27126,12 +27188,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="273" spans="1:32">
+    <row r="273" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A273">
         <v>198464</v>
       </c>
       <c r="B273">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C273">
         <v>8</v>
@@ -27224,12 +27286,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="274" spans="1:32">
+    <row r="274" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A274">
         <v>199102</v>
       </c>
       <c r="B274">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C274">
         <v>7</v>
@@ -27322,12 +27384,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="275" spans="1:32">
+    <row r="275" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A275">
         <v>199120</v>
       </c>
       <c r="B275">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C275">
         <v>4</v>
@@ -27420,12 +27482,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="276" spans="1:32">
+    <row r="276" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A276">
         <v>199120</v>
       </c>
       <c r="B276">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C276">
         <v>7</v>
@@ -27518,12 +27580,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="277" spans="1:32">
+    <row r="277" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A277">
         <v>199139</v>
       </c>
       <c r="B277">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C277">
         <v>4</v>
@@ -27616,12 +27678,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="278" spans="1:32">
+    <row r="278" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A278">
         <v>199157</v>
       </c>
       <c r="B278">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C278">
         <v>6</v>
@@ -27714,12 +27776,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="279" spans="1:32">
+    <row r="279" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A279">
         <v>199193</v>
       </c>
       <c r="B279">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C279">
         <v>14</v>
@@ -27812,12 +27874,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="280" spans="1:32">
+    <row r="280" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A280">
         <v>199193</v>
       </c>
       <c r="B280">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C280">
         <v>12</v>
@@ -27910,12 +27972,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="281" spans="1:32">
+    <row r="281" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A281">
         <v>199847</v>
       </c>
       <c r="B281">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C281">
         <v>0</v>
@@ -28008,12 +28070,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="282" spans="1:32">
+    <row r="282" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A282">
         <v>199847</v>
       </c>
       <c r="B282">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C282">
         <v>4</v>
@@ -28106,12 +28168,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="283" spans="1:32">
+    <row r="283" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A283">
         <v>200280</v>
       </c>
       <c r="B283">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C283">
         <v>0</v>
@@ -28204,12 +28266,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="284" spans="1:32">
+    <row r="284" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A284">
         <v>200280</v>
       </c>
       <c r="B284">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C284">
         <v>2</v>
@@ -28302,12 +28364,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="285" spans="1:32">
+    <row r="285" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A285">
         <v>200332</v>
       </c>
       <c r="B285">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C285">
         <v>0</v>
@@ -28400,12 +28462,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="286" spans="1:32">
+    <row r="286" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A286">
         <v>200332</v>
       </c>
       <c r="B286">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C286">
         <v>2</v>
@@ -28498,12 +28560,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="287" spans="1:32">
+    <row r="287" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A287">
         <v>200800</v>
       </c>
       <c r="B287">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C287">
         <v>4</v>
@@ -28596,12 +28658,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="288" spans="1:32">
+    <row r="288" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A288">
         <v>201441</v>
       </c>
       <c r="B288">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C288">
         <v>10</v>
@@ -28694,12 +28756,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="289" spans="1:32">
+    <row r="289" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A289">
         <v>201645</v>
       </c>
       <c r="B289">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C289">
         <v>3</v>
@@ -28792,12 +28854,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="290" spans="1:32">
+    <row r="290" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A290">
         <v>201645</v>
       </c>
       <c r="B290">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C290">
         <v>4</v>
@@ -28890,12 +28952,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="291" spans="1:32">
+    <row r="291" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A291">
         <v>201885</v>
       </c>
       <c r="B291">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C291">
         <v>10</v>
@@ -28988,12 +29050,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="292" spans="1:32">
+    <row r="292" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A292">
         <v>201885</v>
       </c>
       <c r="B292">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C292">
         <v>0</v>
@@ -29086,12 +29148,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="293" spans="1:32">
+    <row r="293" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A293">
         <v>202134</v>
       </c>
       <c r="B293">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C293">
         <v>3</v>
@@ -29184,12 +29246,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="294" spans="1:32">
+    <row r="294" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A294">
         <v>203517</v>
       </c>
       <c r="B294">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C294">
         <v>6</v>
@@ -29282,12 +29344,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="295" spans="1:32">
+    <row r="295" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A295">
         <v>203517</v>
       </c>
       <c r="B295">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C295">
         <v>3</v>
@@ -29380,12 +29442,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="296" spans="1:32">
+    <row r="296" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A296">
         <v>204024</v>
       </c>
       <c r="B296">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C296">
         <v>9</v>
@@ -29478,12 +29540,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="297" spans="1:32">
+    <row r="297" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A297">
         <v>204796</v>
       </c>
       <c r="B297">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C297">
         <v>21</v>
@@ -29576,12 +29638,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="298" spans="1:32">
+    <row r="298" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A298">
         <v>204796</v>
       </c>
       <c r="B298">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C298">
         <v>33</v>
@@ -29674,12 +29736,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="299" spans="1:32">
+    <row r="299" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A299">
         <v>204857</v>
       </c>
       <c r="B299">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C299">
         <v>10</v>
@@ -29772,12 +29834,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="300" spans="1:32">
+    <row r="300" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A300">
         <v>204857</v>
       </c>
       <c r="B300">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C300">
         <v>9</v>
@@ -29870,12 +29932,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="301" spans="1:32">
+    <row r="301" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A301">
         <v>206084</v>
       </c>
       <c r="B301">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C301">
         <v>9</v>
@@ -29968,12 +30030,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="302" spans="1:32">
+    <row r="302" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A302">
         <v>206084</v>
       </c>
       <c r="B302">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C302">
         <v>10</v>
@@ -30066,12 +30128,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="303" spans="1:32">
+    <row r="303" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A303">
         <v>206084</v>
       </c>
       <c r="B303">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C303">
         <v>0</v>
@@ -30164,12 +30226,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="304" spans="1:32">
+    <row r="304" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A304">
         <v>206604</v>
       </c>
       <c r="B304">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C304">
         <v>4</v>
@@ -30262,12 +30324,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="305" spans="1:32">
+    <row r="305" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A305">
         <v>207388</v>
       </c>
       <c r="B305">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C305">
         <v>0</v>
@@ -30360,12 +30422,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="306" spans="1:32">
+    <row r="306" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A306">
         <v>207388</v>
       </c>
       <c r="B306">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C306">
         <v>1</v>
@@ -30458,12 +30520,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="307" spans="1:32">
+    <row r="307" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A307">
         <v>207500</v>
       </c>
       <c r="B307">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C307">
         <v>8</v>
@@ -30556,12 +30618,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="308" spans="1:32">
+    <row r="308" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A308">
         <v>207500</v>
       </c>
       <c r="B308">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C308">
         <v>11</v>
@@ -30654,12 +30716,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="309" spans="1:32">
+    <row r="309" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A309">
         <v>207971</v>
       </c>
       <c r="B309">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C309">
         <v>0</v>
@@ -30752,12 +30814,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="310" spans="1:32">
+    <row r="310" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A310">
         <v>209542</v>
       </c>
       <c r="B310">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C310">
         <v>5</v>
@@ -30850,12 +30912,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="311" spans="1:32">
+    <row r="311" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A311">
         <v>209542</v>
       </c>
       <c r="B311">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C311">
         <v>5</v>
@@ -30948,12 +31010,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="312" spans="1:32">
+    <row r="312" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A312">
         <v>209551</v>
       </c>
       <c r="B312">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C312">
         <v>9</v>
@@ -31046,12 +31108,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="313" spans="1:32">
+    <row r="313" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A313">
         <v>209551</v>
       </c>
       <c r="B313">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C313">
         <v>9</v>
@@ -31144,12 +31206,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="314" spans="1:32">
+    <row r="314" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A314">
         <v>209807</v>
       </c>
       <c r="B314">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C314">
         <v>3</v>
@@ -31242,12 +31304,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="315" spans="1:32">
+    <row r="315" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A315">
         <v>209807</v>
       </c>
       <c r="B315">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C315">
         <v>8</v>
@@ -31340,12 +31402,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="316" spans="1:32">
+    <row r="316" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A316">
         <v>211273</v>
       </c>
       <c r="B316">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C316">
         <v>0</v>
@@ -31438,12 +31500,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="317" spans="1:32">
+    <row r="317" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A317">
         <v>211273</v>
       </c>
       <c r="B317">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C317">
         <v>0</v>
@@ -31536,12 +31598,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="318" spans="1:32">
+    <row r="318" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A318">
         <v>211440</v>
       </c>
       <c r="B318">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C318">
         <v>18</v>
@@ -31634,12 +31696,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="319" spans="1:32">
+    <row r="319" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A319">
         <v>211440</v>
       </c>
       <c r="B319">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C319">
         <v>11</v>
@@ -31732,12 +31794,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="320" spans="1:32">
+    <row r="320" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A320">
         <v>213020</v>
       </c>
       <c r="B320">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C320">
         <v>5</v>
@@ -31830,12 +31892,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="321" spans="1:32">
+    <row r="321" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A321">
         <v>213020</v>
       </c>
       <c r="B321">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C321">
         <v>0</v>
@@ -31928,12 +31990,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="322" spans="1:32">
+    <row r="322" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A322">
         <v>213543</v>
       </c>
       <c r="B322">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C322">
         <v>6</v>
@@ -32026,12 +32088,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="323" spans="1:32">
+    <row r="323" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A323">
         <v>213543</v>
       </c>
       <c r="B323">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C323">
         <v>6</v>
@@ -32124,12 +32186,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="324" spans="1:32">
+    <row r="324" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A324">
         <v>214777</v>
       </c>
       <c r="B324">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C324">
         <v>4</v>
@@ -32222,12 +32284,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="325" spans="1:32">
+    <row r="325" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A325">
         <v>214777</v>
       </c>
       <c r="B325">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C325">
         <v>22</v>
@@ -32320,12 +32382,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="326" spans="1:32">
+    <row r="326" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A326">
         <v>215062</v>
       </c>
       <c r="B326">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C326">
         <v>35</v>
@@ -32418,12 +32480,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="327" spans="1:32">
+    <row r="327" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A327">
         <v>215062</v>
       </c>
       <c r="B327">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C327">
         <v>24</v>
@@ -32516,12 +32578,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="328" spans="1:32">
+    <row r="328" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A328">
         <v>215293</v>
       </c>
       <c r="B328">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C328">
         <v>8</v>
@@ -32614,12 +32676,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="329" spans="1:32">
+    <row r="329" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A329">
         <v>215293</v>
       </c>
       <c r="B329">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C329">
         <v>10</v>
@@ -32712,12 +32774,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="330" spans="1:32">
+    <row r="330" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A330">
         <v>216339</v>
       </c>
       <c r="B330">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C330">
         <v>3</v>
@@ -32810,12 +32872,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="331" spans="1:32">
+    <row r="331" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A331">
         <v>216339</v>
       </c>
       <c r="B331">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C331">
         <v>7</v>
@@ -32908,12 +32970,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="332" spans="1:32">
+    <row r="332" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A332">
         <v>217156</v>
       </c>
       <c r="B332">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C332">
         <v>9</v>
@@ -33006,12 +33068,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="333" spans="1:32">
+    <row r="333" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A333">
         <v>217156</v>
       </c>
       <c r="B333">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C333">
         <v>15</v>
@@ -33104,12 +33166,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="334" spans="1:32">
+    <row r="334" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A334">
         <v>217484</v>
       </c>
       <c r="B334">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C334">
         <v>3</v>
@@ -33202,12 +33264,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="335" spans="1:32">
+    <row r="335" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A335">
         <v>217484</v>
       </c>
       <c r="B335">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C335">
         <v>2</v>
@@ -33300,12 +33362,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="336" spans="1:32">
+    <row r="336" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A336">
         <v>217882</v>
       </c>
       <c r="B336">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C336">
         <v>5</v>
@@ -33398,12 +33460,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="337" spans="1:32">
+    <row r="337" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A337">
         <v>217882</v>
       </c>
       <c r="B337">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C337">
         <v>12</v>
@@ -33496,12 +33558,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="338" spans="1:32">
+    <row r="338" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A338">
         <v>218663</v>
       </c>
       <c r="B338">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C338">
         <v>3</v>
@@ -33594,12 +33656,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="339" spans="1:32">
+    <row r="339" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A339">
         <v>218663</v>
       </c>
       <c r="B339">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C339">
         <v>3</v>
@@ -33692,12 +33754,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="340" spans="1:32">
+    <row r="340" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A340">
         <v>219347</v>
       </c>
       <c r="B340">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C340">
         <v>3</v>
@@ -33790,12 +33852,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="341" spans="1:32">
+    <row r="341" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A341">
         <v>219347</v>
       </c>
       <c r="B341">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C341">
         <v>0</v>
@@ -33888,12 +33950,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="342" spans="1:32">
+    <row r="342" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A342">
         <v>219471</v>
       </c>
       <c r="B342">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C342">
         <v>5</v>
@@ -33986,12 +34048,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="343" spans="1:32">
+    <row r="343" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A343">
         <v>220181</v>
       </c>
       <c r="B343">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C343">
         <v>3</v>
@@ -34084,12 +34146,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="344" spans="1:32">
+    <row r="344" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A344">
         <v>220862</v>
       </c>
       <c r="B344">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C344">
         <v>4</v>
@@ -34182,12 +34244,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="345" spans="1:32">
+    <row r="345" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A345">
         <v>221759</v>
       </c>
       <c r="B345">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C345">
         <v>13</v>
@@ -34280,12 +34342,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="346" spans="1:32">
+    <row r="346" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A346">
         <v>221759</v>
       </c>
       <c r="B346">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C346">
         <v>15</v>
@@ -34378,12 +34440,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="347" spans="1:32">
+    <row r="347" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A347">
         <v>221999</v>
       </c>
       <c r="B347">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C347">
         <v>4</v>
@@ -34476,12 +34538,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="348" spans="1:32">
+    <row r="348" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A348">
         <v>221999</v>
       </c>
       <c r="B348">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C348">
         <v>12</v>
@@ -34574,12 +34636,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="349" spans="1:32">
+    <row r="349" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A349">
         <v>223232</v>
       </c>
       <c r="B349">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C349">
         <v>4</v>
@@ -34672,12 +34734,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="350" spans="1:32">
+    <row r="350" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A350">
         <v>223232</v>
       </c>
       <c r="B350">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C350">
         <v>3</v>
@@ -34770,12 +34832,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="351" spans="1:32">
+    <row r="351" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A351">
         <v>224554</v>
       </c>
       <c r="B351">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C351">
         <v>2</v>
@@ -34868,12 +34930,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="352" spans="1:32">
+    <row r="352" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A352">
         <v>225414</v>
       </c>
       <c r="B352">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C352">
         <v>3</v>
@@ -34966,12 +35028,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="353" spans="1:32">
+    <row r="353" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A353">
         <v>225511</v>
       </c>
       <c r="B353">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C353">
         <v>6</v>
@@ -35064,12 +35126,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="354" spans="1:32">
+    <row r="354" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A354">
         <v>225511</v>
       </c>
       <c r="B354">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C354">
         <v>15</v>
@@ -35162,12 +35224,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="355" spans="1:32">
+    <row r="355" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A355">
         <v>227216</v>
       </c>
       <c r="B355">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C355">
         <v>3</v>
@@ -35260,12 +35322,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="356" spans="1:32">
+    <row r="356" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A356">
         <v>227216</v>
       </c>
       <c r="B356">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C356">
         <v>9</v>
@@ -35358,12 +35420,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="357" spans="1:32">
+    <row r="357" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A357">
         <v>227377</v>
       </c>
       <c r="B357">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C357">
         <v>6</v>
@@ -35456,12 +35518,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="358" spans="1:32">
+    <row r="358" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A358">
         <v>227757</v>
       </c>
       <c r="B358">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C358">
         <v>22</v>
@@ -35554,12 +35616,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="359" spans="1:32">
+    <row r="359" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A359">
         <v>227757</v>
       </c>
       <c r="B359">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C359">
         <v>20</v>
@@ -35652,12 +35714,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="360" spans="1:32">
+    <row r="360" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A360">
         <v>228246</v>
       </c>
       <c r="B360">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C360">
         <v>4</v>
@@ -35750,12 +35812,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="361" spans="1:32">
+    <row r="361" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A361">
         <v>228246</v>
       </c>
       <c r="B361">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C361">
         <v>1</v>
@@ -35848,12 +35910,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="362" spans="1:32">
+    <row r="362" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A362">
         <v>228431</v>
       </c>
       <c r="B362">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C362">
         <v>0</v>
@@ -35946,12 +36008,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="363" spans="1:32">
+    <row r="363" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A363">
         <v>228459</v>
       </c>
       <c r="B363">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C363">
         <v>5</v>
@@ -36044,12 +36106,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="364" spans="1:32">
+    <row r="364" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A364">
         <v>228723</v>
       </c>
       <c r="B364">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C364">
         <v>14</v>
@@ -36142,12 +36204,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="365" spans="1:32">
+    <row r="365" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A365">
         <v>228723</v>
       </c>
       <c r="B365">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C365">
         <v>22</v>
@@ -36240,12 +36302,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="366" spans="1:32">
+    <row r="366" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A366">
         <v>228769</v>
       </c>
       <c r="B366">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C366">
         <v>6</v>
@@ -36338,12 +36400,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="367" spans="1:32">
+    <row r="367" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A367">
         <v>228769</v>
       </c>
       <c r="B367">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C367">
         <v>9</v>
@@ -36436,12 +36498,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="368" spans="1:32">
+    <row r="368" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A368">
         <v>228778</v>
       </c>
       <c r="B368">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C368">
         <v>4</v>
@@ -36534,12 +36596,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="369" spans="1:32">
+    <row r="369" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A369">
         <v>228778</v>
       </c>
       <c r="B369">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C369">
         <v>35</v>
@@ -36632,12 +36694,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="370" spans="1:32">
+    <row r="370" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A370">
         <v>228787</v>
       </c>
       <c r="B370">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C370">
         <v>14</v>
@@ -36730,12 +36792,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="371" spans="1:32">
+    <row r="371" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A371">
         <v>228787</v>
       </c>
       <c r="B371">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C371">
         <v>8</v>
@@ -36828,12 +36890,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="372" spans="1:32">
+    <row r="372" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A372">
         <v>228796</v>
       </c>
       <c r="B372">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C372">
         <v>12</v>
@@ -36926,12 +36988,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="373" spans="1:32">
+    <row r="373" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A373">
         <v>228875</v>
       </c>
       <c r="B373">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C373">
         <v>3</v>
@@ -37024,12 +37086,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="374" spans="1:32">
+    <row r="374" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A374">
         <v>228875</v>
       </c>
       <c r="B374">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C374">
         <v>2</v>
@@ -37122,12 +37184,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="375" spans="1:32">
+    <row r="375" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A375">
         <v>229027</v>
       </c>
       <c r="B375">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C375">
         <v>7</v>
@@ -37220,12 +37282,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="376" spans="1:32">
+    <row r="376" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A376">
         <v>229027</v>
       </c>
       <c r="B376">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C376">
         <v>16</v>
@@ -37318,12 +37380,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="377" spans="1:32">
+    <row r="377" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A377">
         <v>229115</v>
       </c>
       <c r="B377">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C377">
         <v>9</v>
@@ -37416,12 +37478,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="378" spans="1:32">
+    <row r="378" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A378">
         <v>229115</v>
       </c>
       <c r="B378">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C378">
         <v>5</v>
@@ -37514,12 +37576,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="379" spans="1:32">
+    <row r="379" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A379">
         <v>230038</v>
       </c>
       <c r="B379">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C379">
         <v>7</v>
@@ -37612,12 +37674,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="380" spans="1:32">
+    <row r="380" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A380">
         <v>230038</v>
       </c>
       <c r="B380">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C380">
         <v>2</v>
@@ -37710,12 +37772,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="381" spans="1:32">
+    <row r="381" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A381">
         <v>230728</v>
       </c>
       <c r="B381">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C381">
         <v>1</v>
@@ -37808,12 +37870,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="382" spans="1:32">
+    <row r="382" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A382">
         <v>230728</v>
       </c>
       <c r="B382">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C382">
         <v>2</v>
@@ -37906,12 +37968,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="383" spans="1:32">
+    <row r="383" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A383">
         <v>230764</v>
       </c>
       <c r="B383">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C383">
         <v>13</v>
@@ -38004,12 +38066,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="384" spans="1:32">
+    <row r="384" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A384">
         <v>230764</v>
       </c>
       <c r="B384">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C384">
         <v>10</v>
@@ -38102,12 +38164,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="385" spans="1:32">
+    <row r="385" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A385">
         <v>231174</v>
       </c>
       <c r="B385">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C385">
         <v>2</v>
@@ -38200,12 +38262,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="386" spans="1:32">
+    <row r="386" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A386">
         <v>231624</v>
       </c>
       <c r="B386">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C386">
         <v>5</v>
@@ -38298,12 +38360,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="387" spans="1:32">
+    <row r="387" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A387">
         <v>231624</v>
       </c>
       <c r="B387">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C387">
         <v>7</v>
@@ -38396,12 +38458,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="388" spans="1:32">
+    <row r="388" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A388">
         <v>232186</v>
       </c>
       <c r="B388">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C388">
         <v>8</v>
@@ -38494,12 +38556,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="389" spans="1:32">
+    <row r="389" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A389">
         <v>232186</v>
       </c>
       <c r="B389">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C389">
         <v>4</v>
@@ -38592,12 +38654,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="390" spans="1:32">
+    <row r="390" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A390">
         <v>232265</v>
       </c>
       <c r="B390">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C390">
         <v>2</v>
@@ -38690,12 +38752,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="391" spans="1:32">
+    <row r="391" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A391">
         <v>232265</v>
       </c>
       <c r="B391">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C391">
         <v>4</v>
@@ -38788,12 +38850,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="392" spans="1:32">
+    <row r="392" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A392">
         <v>232982</v>
       </c>
       <c r="B392">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C392">
         <v>6</v>
@@ -38886,12 +38948,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="393" spans="1:32">
+    <row r="393" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A393">
         <v>232982</v>
       </c>
       <c r="B393">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C393">
         <v>8</v>
@@ -38984,12 +39046,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="394" spans="1:32">
+    <row r="394" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A394">
         <v>233921</v>
       </c>
       <c r="B394">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C394">
         <v>7</v>
@@ -39082,12 +39144,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="395" spans="1:32">
+    <row r="395" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A395">
         <v>233921</v>
       </c>
       <c r="B395">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C395">
         <v>12</v>
@@ -39180,12 +39242,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="396" spans="1:32">
+    <row r="396" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A396">
         <v>234030</v>
       </c>
       <c r="B396">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C396">
         <v>3</v>
@@ -39278,12 +39340,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="397" spans="1:32">
+    <row r="397" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A397">
         <v>234076</v>
       </c>
       <c r="B397">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C397">
         <v>4</v>
@@ -39376,12 +39438,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="398" spans="1:32">
+    <row r="398" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A398">
         <v>234076</v>
       </c>
       <c r="B398">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C398">
         <v>13</v>
@@ -39474,12 +39536,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="399" spans="1:32">
+    <row r="399" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A399">
         <v>234155</v>
       </c>
       <c r="B399">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C399">
         <v>0</v>
@@ -39572,12 +39634,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="400" spans="1:32">
+    <row r="400" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A400">
         <v>236939</v>
       </c>
       <c r="B400">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C400">
         <v>6</v>
@@ -39670,12 +39732,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="401" spans="1:32">
+    <row r="401" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A401">
         <v>236939</v>
       </c>
       <c r="B401">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C401">
         <v>9</v>
@@ -39768,12 +39830,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="402" spans="1:32">
+    <row r="402" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A402">
         <v>236948</v>
       </c>
       <c r="B402">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C402">
         <v>24</v>
@@ -39866,12 +39928,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="403" spans="1:32">
+    <row r="403" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A403">
         <v>236948</v>
       </c>
       <c r="B403">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C403">
         <v>20</v>
@@ -39964,12 +40026,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="404" spans="1:32">
+    <row r="404" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A404">
         <v>236948</v>
       </c>
       <c r="B404">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C404">
         <v>0</v>
@@ -40062,12 +40124,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="405" spans="1:32">
+    <row r="405" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A405">
         <v>236948</v>
       </c>
       <c r="B405">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C405">
         <v>0</v>
@@ -40160,12 +40222,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="406" spans="1:32">
+    <row r="406" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A406">
         <v>238032</v>
       </c>
       <c r="B406">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C406">
         <v>10</v>
@@ -40258,12 +40320,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="407" spans="1:32">
+    <row r="407" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A407">
         <v>238032</v>
       </c>
       <c r="B407">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C407">
         <v>9</v>
@@ -40356,12 +40418,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="408" spans="1:32">
+    <row r="408" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A408">
         <v>240365</v>
       </c>
       <c r="B408">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C408">
         <v>0</v>
@@ -40454,12 +40516,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="409" spans="1:32">
+    <row r="409" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A409">
         <v>240444</v>
       </c>
       <c r="B409">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C409">
         <v>8</v>
@@ -40552,12 +40614,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="410" spans="1:32">
+    <row r="410" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A410">
         <v>240444</v>
       </c>
       <c r="B410">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C410">
         <v>35</v>
@@ -40650,12 +40712,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="411" spans="1:32">
+    <row r="411" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A411">
         <v>240453</v>
       </c>
       <c r="B411">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C411">
         <v>4</v>
@@ -40748,12 +40810,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="412" spans="1:32">
+    <row r="412" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A412">
         <v>240453</v>
       </c>
       <c r="B412">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C412">
         <v>5</v>
@@ -40846,12 +40908,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="413" spans="1:32">
+    <row r="413" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A413">
         <v>240727</v>
       </c>
       <c r="B413">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C413">
         <v>11</v>
@@ -40944,12 +41006,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="414" spans="1:32">
+    <row r="414" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A414">
         <v>240727</v>
       </c>
       <c r="B414">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C414">
         <v>2</v>
@@ -41042,12 +41104,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="415" spans="1:32">
+    <row r="415" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A415">
         <v>243197</v>
       </c>
       <c r="B415">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C415">
         <v>6</v>
@@ -41140,12 +41202,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="416" spans="1:32">
+    <row r="416" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A416">
         <v>243221</v>
       </c>
       <c r="B416">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C416">
         <v>2</v>
@@ -41238,12 +41300,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="417" spans="1:32">
+    <row r="417" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A417">
         <v>243744</v>
       </c>
       <c r="B417">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C417">
         <v>4</v>
@@ -41336,12 +41398,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="418" spans="1:32">
+    <row r="418" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A418">
         <v>243744</v>
       </c>
       <c r="B418">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C418">
         <v>21</v>
@@ -41434,12 +41496,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="419" spans="1:32">
+    <row r="419" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A419">
         <v>243780</v>
       </c>
       <c r="B419">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C419">
         <v>8</v>
@@ -41532,12 +41594,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="420" spans="1:32">
+    <row r="420" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A420">
         <v>243780</v>
       </c>
       <c r="B420">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C420">
         <v>22</v>
@@ -41630,12 +41692,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="421" spans="1:32">
+    <row r="421" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A421">
         <v>445188</v>
       </c>
       <c r="B421">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C421">
         <v>0</v>
@@ -41728,12 +41790,12 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="422" spans="1:32">
+    <row r="422" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A422">
         <v>445188</v>
       </c>
       <c r="B422">
-        <v>40.0801</v>
+        <v>40.080100000000002</v>
       </c>
       <c r="C422">
         <v>5</v>
@@ -41824,6 +41886,1217 @@
       </c>
       <c r="AF422">
         <v>2015</v>
+      </c>
+    </row>
+    <row r="424" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A424" cm="1">
+        <f t="array" ref="A424:A662">_xlfn.UNIQUE(A2:A422)</f>
+        <v>100654</v>
+      </c>
+      <c r="B424" t="s">
+        <v>32</v>
+      </c>
+      <c r="H424">
+        <f>SUM(H2:H422)</f>
+        <v>43</v>
+      </c>
+      <c r="W424" s="2">
+        <f>SUM(W2:W422)</f>
+        <v>8</v>
+      </c>
+      <c r="Z424">
+        <f>SUM(Z2:Z422)</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="425" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A425">
+        <v>100663</v>
+      </c>
+    </row>
+    <row r="426" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A426">
+        <v>100706</v>
+      </c>
+    </row>
+    <row r="427" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A427">
+        <v>100751</v>
+      </c>
+    </row>
+    <row r="428" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A428">
+        <v>100858</v>
+      </c>
+    </row>
+    <row r="429" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A429">
+        <v>102614</v>
+      </c>
+    </row>
+    <row r="430" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A430">
+        <v>104151</v>
+      </c>
+    </row>
+    <row r="431" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A431">
+        <v>104179</v>
+      </c>
+    </row>
+    <row r="432" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A432">
+        <v>105330</v>
+      </c>
+    </row>
+    <row r="433" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A433">
+        <v>106397</v>
+      </c>
+    </row>
+    <row r="434" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A434">
+        <v>110404</v>
+      </c>
+    </row>
+    <row r="435" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A435">
+        <v>110422</v>
+      </c>
+    </row>
+    <row r="436" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A436">
+        <v>110556</v>
+      </c>
+    </row>
+    <row r="437" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A437">
+        <v>110565</v>
+      </c>
+    </row>
+    <row r="438" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A438">
+        <v>110583</v>
+      </c>
+    </row>
+    <row r="439" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A439">
+        <v>110592</v>
+      </c>
+    </row>
+    <row r="440" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A440">
+        <v>110608</v>
+      </c>
+    </row>
+    <row r="441" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A441">
+        <v>110635</v>
+      </c>
+    </row>
+    <row r="442" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A442">
+        <v>110644</v>
+      </c>
+    </row>
+    <row r="443" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A443">
+        <v>110653</v>
+      </c>
+    </row>
+    <row r="444" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A444">
+        <v>110662</v>
+      </c>
+    </row>
+    <row r="445" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A445">
+        <v>110671</v>
+      </c>
+    </row>
+    <row r="446" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A446">
+        <v>110680</v>
+      </c>
+    </row>
+    <row r="447" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A447">
+        <v>110705</v>
+      </c>
+    </row>
+    <row r="448" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A448">
+        <v>110714</v>
+      </c>
+    </row>
+    <row r="449" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A449">
+        <v>119678</v>
+      </c>
+    </row>
+    <row r="450" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A450">
+        <v>122409</v>
+      </c>
+    </row>
+    <row r="451" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A451">
+        <v>122597</v>
+      </c>
+    </row>
+    <row r="452" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A452">
+        <v>122755</v>
+      </c>
+    </row>
+    <row r="453" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A453">
+        <v>123961</v>
+      </c>
+    </row>
+    <row r="454" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A454">
+        <v>126614</v>
+      </c>
+    </row>
+    <row r="455" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A455">
+        <v>126775</v>
+      </c>
+    </row>
+    <row r="456" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A456">
+        <v>126818</v>
+      </c>
+    </row>
+    <row r="457" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A457">
+        <v>127060</v>
+      </c>
+    </row>
+    <row r="458" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A458">
+        <v>129020</v>
+      </c>
+    </row>
+    <row r="459" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A459">
+        <v>130697</v>
+      </c>
+    </row>
+    <row r="460" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A460">
+        <v>130794</v>
+      </c>
+    </row>
+    <row r="461" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A461">
+        <v>130934</v>
+      </c>
+    </row>
+    <row r="462" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A462">
+        <v>130943</v>
+      </c>
+    </row>
+    <row r="463" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A463">
+        <v>131283</v>
+      </c>
+    </row>
+    <row r="464" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A464">
+        <v>131469</v>
+      </c>
+    </row>
+    <row r="465" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A465">
+        <v>131496</v>
+      </c>
+    </row>
+    <row r="466" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A466">
+        <v>131520</v>
+      </c>
+    </row>
+    <row r="467" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A467">
+        <v>132903</v>
+      </c>
+    </row>
+    <row r="468" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A468">
+        <v>133650</v>
+      </c>
+    </row>
+    <row r="469" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A469">
+        <v>133669</v>
+      </c>
+    </row>
+    <row r="470" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A470">
+        <v>133881</v>
+      </c>
+    </row>
+    <row r="471" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A471">
+        <v>133951</v>
+      </c>
+    </row>
+    <row r="472" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A472">
+        <v>134097</v>
+      </c>
+    </row>
+    <row r="473" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A473">
+        <v>134130</v>
+      </c>
+    </row>
+    <row r="474" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A474">
+        <v>135726</v>
+      </c>
+    </row>
+    <row r="475" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A475">
+        <v>137351</v>
+      </c>
+    </row>
+    <row r="476" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A476">
+        <v>138947</v>
+      </c>
+    </row>
+    <row r="477" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A477">
+        <v>139658</v>
+      </c>
+    </row>
+    <row r="478" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A478">
+        <v>139755</v>
+      </c>
+    </row>
+    <row r="479" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A479">
+        <v>139940</v>
+      </c>
+    </row>
+    <row r="480" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A480">
+        <v>139959</v>
+      </c>
+    </row>
+    <row r="481" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A481">
+        <v>141574</v>
+      </c>
+    </row>
+    <row r="482" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A482">
+        <v>142276</v>
+      </c>
+    </row>
+    <row r="483" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A483">
+        <v>142285</v>
+      </c>
+    </row>
+    <row r="484" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A484">
+        <v>144050</v>
+      </c>
+    </row>
+    <row r="485" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A485">
+        <v>144740</v>
+      </c>
+    </row>
+    <row r="486" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A486">
+        <v>145600</v>
+      </c>
+    </row>
+    <row r="487" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A487">
+        <v>145637</v>
+      </c>
+    </row>
+    <row r="488" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A488">
+        <v>145725</v>
+      </c>
+    </row>
+    <row r="489" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A489">
+        <v>147703</v>
+      </c>
+    </row>
+    <row r="490" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A490">
+        <v>149222</v>
+      </c>
+    </row>
+    <row r="491" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A491">
+        <v>149772</v>
+      </c>
+    </row>
+    <row r="492" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A492">
+        <v>150136</v>
+      </c>
+    </row>
+    <row r="493" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A493">
+        <v>151111</v>
+      </c>
+    </row>
+    <row r="494" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A494">
+        <v>151351</v>
+      </c>
+    </row>
+    <row r="495" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A495">
+        <v>152080</v>
+      </c>
+    </row>
+    <row r="496" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A496">
+        <v>153603</v>
+      </c>
+    </row>
+    <row r="497" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A497">
+        <v>153658</v>
+      </c>
+    </row>
+    <row r="498" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A498">
+        <v>155317</v>
+      </c>
+    </row>
+    <row r="499" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A499">
+        <v>155399</v>
+      </c>
+    </row>
+    <row r="500" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A500">
+        <v>155681</v>
+      </c>
+    </row>
+    <row r="501" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A501">
+        <v>157085</v>
+      </c>
+    </row>
+    <row r="502" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A502">
+        <v>157289</v>
+      </c>
+    </row>
+    <row r="503" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A503">
+        <v>159391</v>
+      </c>
+    </row>
+    <row r="504" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A504">
+        <v>159647</v>
+      </c>
+    </row>
+    <row r="505" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A505">
+        <v>159939</v>
+      </c>
+    </row>
+    <row r="506" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A506">
+        <v>160621</v>
+      </c>
+    </row>
+    <row r="507" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A507">
+        <v>160658</v>
+      </c>
+    </row>
+    <row r="508" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A508">
+        <v>160755</v>
+      </c>
+    </row>
+    <row r="509" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A509">
+        <v>161253</v>
+      </c>
+    </row>
+    <row r="510" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A510">
+        <v>162928</v>
+      </c>
+    </row>
+    <row r="511" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A511">
+        <v>163268</v>
+      </c>
+    </row>
+    <row r="512" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A512">
+        <v>163286</v>
+      </c>
+    </row>
+    <row r="513" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A513">
+        <v>164924</v>
+      </c>
+    </row>
+    <row r="514" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A514">
+        <v>164988</v>
+      </c>
+    </row>
+    <row r="515" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A515">
+        <v>165015</v>
+      </c>
+    </row>
+    <row r="516" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A516">
+        <v>165334</v>
+      </c>
+    </row>
+    <row r="517" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A517">
+        <v>166027</v>
+      </c>
+    </row>
+    <row r="518" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A518">
+        <v>166513</v>
+      </c>
+    </row>
+    <row r="519" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A519">
+        <v>166629</v>
+      </c>
+    </row>
+    <row r="520" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A520">
+        <v>166638</v>
+      </c>
+    </row>
+    <row r="521" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A521">
+        <v>166683</v>
+      </c>
+    </row>
+    <row r="522" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A522">
+        <v>167358</v>
+      </c>
+    </row>
+    <row r="523" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A523">
+        <v>167987</v>
+      </c>
+    </row>
+    <row r="524" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A524">
+        <v>168148</v>
+      </c>
+    </row>
+    <row r="525" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A525">
+        <v>168421</v>
+      </c>
+    </row>
+    <row r="526" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A526">
+        <v>169248</v>
+      </c>
+    </row>
+    <row r="527" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A527">
+        <v>169798</v>
+      </c>
+    </row>
+    <row r="528" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A528">
+        <v>170976</v>
+      </c>
+    </row>
+    <row r="529" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A529">
+        <v>171100</v>
+      </c>
+    </row>
+    <row r="530" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A530">
+        <v>171128</v>
+      </c>
+    </row>
+    <row r="531" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A531">
+        <v>171571</v>
+      </c>
+    </row>
+    <row r="532" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A532">
+        <v>172644</v>
+      </c>
+    </row>
+    <row r="533" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A533">
+        <v>172699</v>
+      </c>
+    </row>
+    <row r="534" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A534">
+        <v>173920</v>
+      </c>
+    </row>
+    <row r="535" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A535">
+        <v>174066</v>
+      </c>
+    </row>
+    <row r="536" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A536">
+        <v>174233</v>
+      </c>
+    </row>
+    <row r="537" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A537">
+        <v>176017</v>
+      </c>
+    </row>
+    <row r="538" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A538">
+        <v>176080</v>
+      </c>
+    </row>
+    <row r="539" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A539">
+        <v>176372</v>
+      </c>
+    </row>
+    <row r="540" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A540">
+        <v>178396</v>
+      </c>
+    </row>
+    <row r="541" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A541">
+        <v>178402</v>
+      </c>
+    </row>
+    <row r="542" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A542">
+        <v>178411</v>
+      </c>
+    </row>
+    <row r="543" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A543">
+        <v>178420</v>
+      </c>
+    </row>
+    <row r="544" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A544">
+        <v>179867</v>
+      </c>
+    </row>
+    <row r="545" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A545">
+        <v>180461</v>
+      </c>
+    </row>
+    <row r="546" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A546">
+        <v>181002</v>
+      </c>
+    </row>
+    <row r="547" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A547">
+        <v>181464</v>
+      </c>
+    </row>
+    <row r="548" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A548">
+        <v>182281</v>
+      </c>
+    </row>
+    <row r="549" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A549">
+        <v>182290</v>
+      </c>
+    </row>
+    <row r="550" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A550">
+        <v>182670</v>
+      </c>
+    </row>
+    <row r="551" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A551">
+        <v>183044</v>
+      </c>
+    </row>
+    <row r="552" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A552">
+        <v>185828</v>
+      </c>
+    </row>
+    <row r="553" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A553">
+        <v>186131</v>
+      </c>
+    </row>
+    <row r="554" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A554">
+        <v>186399</v>
+      </c>
+    </row>
+    <row r="555" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A555">
+        <v>186867</v>
+      </c>
+    </row>
+    <row r="556" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A556">
+        <v>187967</v>
+      </c>
+    </row>
+    <row r="557" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A557">
+        <v>187985</v>
+      </c>
+    </row>
+    <row r="558" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A558">
+        <v>188030</v>
+      </c>
+    </row>
+    <row r="559" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A559">
+        <v>190044</v>
+      </c>
+    </row>
+    <row r="560" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A560">
+        <v>190150</v>
+      </c>
+    </row>
+    <row r="561" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A561">
+        <v>190415</v>
+      </c>
+    </row>
+    <row r="562" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A562">
+        <v>190549</v>
+      </c>
+    </row>
+    <row r="563" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A563">
+        <v>190567</v>
+      </c>
+    </row>
+    <row r="564" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A564">
+        <v>190576</v>
+      </c>
+    </row>
+    <row r="565" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A565">
+        <v>190594</v>
+      </c>
+    </row>
+    <row r="566" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A566">
+        <v>190664</v>
+      </c>
+    </row>
+    <row r="567" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A567">
+        <v>193900</v>
+      </c>
+    </row>
+    <row r="568" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A568">
+        <v>194824</v>
+      </c>
+    </row>
+    <row r="569" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A569">
+        <v>195030</v>
+      </c>
+    </row>
+    <row r="570" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A570">
+        <v>196060</v>
+      </c>
+    </row>
+    <row r="571" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A571">
+        <v>196079</v>
+      </c>
+    </row>
+    <row r="572" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A572">
+        <v>196088</v>
+      </c>
+    </row>
+    <row r="573" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A573">
+        <v>196097</v>
+      </c>
+    </row>
+    <row r="574" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A574">
+        <v>196413</v>
+      </c>
+    </row>
+    <row r="575" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A575">
+        <v>197869</v>
+      </c>
+    </row>
+    <row r="576" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A576">
+        <v>198419</v>
+      </c>
+    </row>
+    <row r="577" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A577">
+        <v>198464</v>
+      </c>
+    </row>
+    <row r="578" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A578">
+        <v>199102</v>
+      </c>
+    </row>
+    <row r="579" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A579">
+        <v>199120</v>
+      </c>
+    </row>
+    <row r="580" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A580">
+        <v>199139</v>
+      </c>
+    </row>
+    <row r="581" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A581">
+        <v>199157</v>
+      </c>
+    </row>
+    <row r="582" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A582">
+        <v>199193</v>
+      </c>
+    </row>
+    <row r="583" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A583">
+        <v>199847</v>
+      </c>
+    </row>
+    <row r="584" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A584">
+        <v>200280</v>
+      </c>
+    </row>
+    <row r="585" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A585">
+        <v>200332</v>
+      </c>
+    </row>
+    <row r="586" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A586">
+        <v>200800</v>
+      </c>
+    </row>
+    <row r="587" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A587">
+        <v>201441</v>
+      </c>
+    </row>
+    <row r="588" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A588">
+        <v>201645</v>
+      </c>
+    </row>
+    <row r="589" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A589">
+        <v>201885</v>
+      </c>
+    </row>
+    <row r="590" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A590">
+        <v>202134</v>
+      </c>
+    </row>
+    <row r="591" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A591">
+        <v>203517</v>
+      </c>
+    </row>
+    <row r="592" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A592">
+        <v>204024</v>
+      </c>
+    </row>
+    <row r="593" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A593">
+        <v>204796</v>
+      </c>
+    </row>
+    <row r="594" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A594">
+        <v>204857</v>
+      </c>
+    </row>
+    <row r="595" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A595">
+        <v>206084</v>
+      </c>
+    </row>
+    <row r="596" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A596">
+        <v>206604</v>
+      </c>
+    </row>
+    <row r="597" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A597">
+        <v>207388</v>
+      </c>
+    </row>
+    <row r="598" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A598">
+        <v>207500</v>
+      </c>
+    </row>
+    <row r="599" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A599">
+        <v>207971</v>
+      </c>
+    </row>
+    <row r="600" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A600">
+        <v>209542</v>
+      </c>
+    </row>
+    <row r="601" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A601">
+        <v>209551</v>
+      </c>
+    </row>
+    <row r="602" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A602">
+        <v>209807</v>
+      </c>
+    </row>
+    <row r="603" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A603">
+        <v>211273</v>
+      </c>
+    </row>
+    <row r="604" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A604">
+        <v>211440</v>
+      </c>
+    </row>
+    <row r="605" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A605">
+        <v>213020</v>
+      </c>
+    </row>
+    <row r="606" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A606">
+        <v>213543</v>
+      </c>
+    </row>
+    <row r="607" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A607">
+        <v>214777</v>
+      </c>
+    </row>
+    <row r="608" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A608">
+        <v>215062</v>
+      </c>
+    </row>
+    <row r="609" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A609">
+        <v>215293</v>
+      </c>
+    </row>
+    <row r="610" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A610">
+        <v>216339</v>
+      </c>
+    </row>
+    <row r="611" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A611">
+        <v>217156</v>
+      </c>
+    </row>
+    <row r="612" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A612">
+        <v>217484</v>
+      </c>
+    </row>
+    <row r="613" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A613">
+        <v>217882</v>
+      </c>
+    </row>
+    <row r="614" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A614">
+        <v>218663</v>
+      </c>
+    </row>
+    <row r="615" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A615">
+        <v>219347</v>
+      </c>
+    </row>
+    <row r="616" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A616">
+        <v>219471</v>
+      </c>
+    </row>
+    <row r="617" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A617">
+        <v>220181</v>
+      </c>
+    </row>
+    <row r="618" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A618">
+        <v>220862</v>
+      </c>
+    </row>
+    <row r="619" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A619">
+        <v>221759</v>
+      </c>
+    </row>
+    <row r="620" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A620">
+        <v>221999</v>
+      </c>
+    </row>
+    <row r="621" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A621">
+        <v>223232</v>
+      </c>
+    </row>
+    <row r="622" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A622">
+        <v>224554</v>
+      </c>
+    </row>
+    <row r="623" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A623">
+        <v>225414</v>
+      </c>
+    </row>
+    <row r="624" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A624">
+        <v>225511</v>
+      </c>
+    </row>
+    <row r="625" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A625">
+        <v>227216</v>
+      </c>
+    </row>
+    <row r="626" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A626">
+        <v>227377</v>
+      </c>
+    </row>
+    <row r="627" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A627">
+        <v>227757</v>
+      </c>
+    </row>
+    <row r="628" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A628">
+        <v>228246</v>
+      </c>
+    </row>
+    <row r="629" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A629">
+        <v>228431</v>
+      </c>
+    </row>
+    <row r="630" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A630">
+        <v>228459</v>
+      </c>
+    </row>
+    <row r="631" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A631">
+        <v>228723</v>
+      </c>
+    </row>
+    <row r="632" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A632">
+        <v>228769</v>
+      </c>
+    </row>
+    <row r="633" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A633">
+        <v>228778</v>
+      </c>
+    </row>
+    <row r="634" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A634">
+        <v>228787</v>
+      </c>
+    </row>
+    <row r="635" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A635">
+        <v>228796</v>
+      </c>
+    </row>
+    <row r="636" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A636">
+        <v>228875</v>
+      </c>
+    </row>
+    <row r="637" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A637">
+        <v>229027</v>
+      </c>
+    </row>
+    <row r="638" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A638">
+        <v>229115</v>
+      </c>
+    </row>
+    <row r="639" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A639">
+        <v>230038</v>
+      </c>
+    </row>
+    <row r="640" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A640">
+        <v>230728</v>
+      </c>
+    </row>
+    <row r="641" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A641">
+        <v>230764</v>
+      </c>
+    </row>
+    <row r="642" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A642">
+        <v>231174</v>
+      </c>
+    </row>
+    <row r="643" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A643">
+        <v>231624</v>
+      </c>
+    </row>
+    <row r="644" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A644">
+        <v>232186</v>
+      </c>
+    </row>
+    <row r="645" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A645">
+        <v>232265</v>
+      </c>
+    </row>
+    <row r="646" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A646">
+        <v>232982</v>
+      </c>
+    </row>
+    <row r="647" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A647">
+        <v>233921</v>
+      </c>
+    </row>
+    <row r="648" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A648">
+        <v>234030</v>
+      </c>
+    </row>
+    <row r="649" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A649">
+        <v>234076</v>
+      </c>
+    </row>
+    <row r="650" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A650">
+        <v>234155</v>
+      </c>
+    </row>
+    <row r="651" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A651">
+        <v>236939</v>
+      </c>
+    </row>
+    <row r="652" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A652">
+        <v>236948</v>
+      </c>
+    </row>
+    <row r="653" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A653">
+        <v>238032</v>
+      </c>
+    </row>
+    <row r="654" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A654">
+        <v>240365</v>
+      </c>
+    </row>
+    <row r="655" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A655">
+        <v>240444</v>
+      </c>
+    </row>
+    <row r="656" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A656">
+        <v>240453</v>
+      </c>
+    </row>
+    <row r="657" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A657">
+        <v>240727</v>
+      </c>
+    </row>
+    <row r="658" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A658">
+        <v>243197</v>
+      </c>
+    </row>
+    <row r="659" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A659">
+        <v>243221</v>
+      </c>
+    </row>
+    <row r="660" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A660">
+        <v>243744</v>
+      </c>
+    </row>
+    <row r="661" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A661">
+        <v>243780</v>
+      </c>
+    </row>
+    <row r="662" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A662">
+        <v>445188</v>
       </c>
     </row>
   </sheetData>
